--- a/database/event/6349/event_6349_evp_summary.xlsx
+++ b/database/event/6349/event_6349_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8668</v>
+        <v>5.8519</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4128</v>
+        <v>2.4067</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9487</v>
+        <v>1.8875</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8668</v>
+        <v>5.8519</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3374</v>
+        <v>1.3225</v>
       </c>
       <c r="G2" t="n">
         <v>4.5294</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3374</v>
+        <v>1.3225</v>
       </c>
       <c r="I2" t="n">
         <v>1.3561</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3569</v>
+        <v>5.3396</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2031</v>
+        <v>2.196</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7427</v>
+        <v>1.6834</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3569</v>
+        <v>5.3396</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5582</v>
+        <v>1.5409</v>
       </c>
       <c r="G3" t="n">
         <v>3.7987</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5582</v>
+        <v>1.5409</v>
       </c>
       <c r="I3" t="n">
         <v>1.5801</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4978</v>
+        <v>4.4869</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8498</v>
+        <v>1.8453</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3956</v>
+        <v>1.3437</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4978</v>
+        <v>4.4869</v>
       </c>
       <c r="F4" t="n">
-        <v>0.978</v>
+        <v>0.9671</v>
       </c>
       <c r="G4" t="n">
         <v>3.5198</v>
       </c>
       <c r="H4" t="n">
-        <v>0.978</v>
+        <v>0.9671</v>
       </c>
       <c r="I4" t="n">
         <v>0.9917</v>
@@ -640,7 +640,7 @@
         <v>1.8442</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3902</v>
+        <v>1.3426</v>
       </c>
       <c r="E5" t="n">
         <v>4.4843</v>
@@ -686,7 +686,7 @@
         <v>1.7987</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3455</v>
+        <v>1.2986</v>
       </c>
       <c r="E6" t="n">
         <v>4.3737</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2086</v>
+        <v>4.1808</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7308</v>
+        <v>1.7194</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2788</v>
+        <v>1.2217</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2086</v>
+        <v>4.1808</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4846</v>
+        <v>2.4568</v>
       </c>
       <c r="G7" t="n">
         <v>1.724</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4846</v>
+        <v>2.4568</v>
       </c>
       <c r="I7" t="n">
         <v>2.5194</v>
@@ -778,7 +778,7 @@
         <v>1.5922</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1426</v>
+        <v>1.0985</v>
       </c>
       <c r="E8" t="n">
         <v>3.8715</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7856</v>
+        <v>3.7862</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5569</v>
+        <v>1.5571</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1079</v>
+        <v>1.0645</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7856</v>
+        <v>3.7862</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0555</v>
+        <v>-0.0549</v>
       </c>
       <c r="G9" t="n">
         <v>3.8411</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0555</v>
+        <v>-0.0549</v>
       </c>
       <c r="I9" t="n">
         <v>-0.0563</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5773</v>
+        <v>3.5829</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4712</v>
+        <v>1.4735</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0238</v>
+        <v>0.9835</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5773</v>
+        <v>3.5829</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5082</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>4.0854</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5082</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>-0.5153</v>
@@ -916,7 +916,7 @@
         <v>1.3435</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8984</v>
+        <v>0.8576</v>
       </c>
       <c r="E11" t="n">
         <v>3.2668</v>
@@ -962,7 +962,7 @@
         <v>1.0884</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6478</v>
+        <v>0.6105</v>
       </c>
       <c r="E12" t="n">
         <v>2.6466</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5894</v>
+        <v>2.5704</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0649</v>
+        <v>1.0571</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6247</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5894</v>
+        <v>2.5704</v>
       </c>
       <c r="F13" t="n">
-        <v>2.553</v>
+        <v>2.534</v>
       </c>
       <c r="G13" t="n">
         <v>0.0364</v>
       </c>
       <c r="H13" t="n">
-        <v>2.553</v>
+        <v>2.534</v>
       </c>
       <c r="I13" t="n">
         <v>2.5768</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.255</v>
+        <v>2.2299</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9274</v>
+        <v>0.9171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4896</v>
+        <v>0.4445</v>
       </c>
       <c r="E14" t="n">
-        <v>2.255</v>
+        <v>2.2299</v>
       </c>
       <c r="F14" t="n">
-        <v>2.255</v>
+        <v>2.2299</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.255</v>
+        <v>2.2299</v>
       </c>
       <c r="I14" t="n">
         <v>2.2866</v>
@@ -1100,7 +1100,7 @@
         <v>0.9133</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4758</v>
+        <v>0.4408</v>
       </c>
       <c r="E15" t="n">
         <v>2.2207</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1307</v>
+        <v>2.1121</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8763</v>
+        <v>0.8686</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4394</v>
+        <v>0.3976</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1307</v>
+        <v>2.1121</v>
       </c>
       <c r="F16" t="n">
-        <v>1.666</v>
+        <v>1.6474</v>
       </c>
       <c r="G16" t="n">
         <v>0.4647</v>
       </c>
       <c r="H16" t="n">
-        <v>1.666</v>
+        <v>1.6474</v>
       </c>
       <c r="I16" t="n">
         <v>1.6893</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9345</v>
+        <v>1.9308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7956</v>
+        <v>0.7941</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3601</v>
+        <v>0.3253</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9345</v>
+        <v>1.9308</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3291</v>
+        <v>0.3254</v>
       </c>
       <c r="G17" t="n">
         <v>1.6054</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3291</v>
+        <v>0.3254</v>
       </c>
       <c r="I17" t="n">
         <v>0.3337</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5127</v>
+        <v>1.5003</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6221</v>
+        <v>0.617</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1897</v>
+        <v>0.1538</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5127</v>
+        <v>1.5003</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1083</v>
+        <v>1.0959</v>
       </c>
       <c r="G18" t="n">
         <v>0.4044</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1083</v>
+        <v>1.0959</v>
       </c>
       <c r="I18" t="n">
         <v>1.1238</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2098</v>
+        <v>1.2054</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4975</v>
+        <v>0.4957</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0674</v>
+        <v>0.0363</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2098</v>
+        <v>1.2054</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2975</v>
+        <v>0.2931</v>
       </c>
       <c r="G19" t="n">
         <v>0.9123</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2975</v>
+        <v>0.2931</v>
       </c>
       <c r="I19" t="n">
         <v>0.3031</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8321</v>
+        <v>0.8289</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3422</v>
+        <v>0.3409</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0852</v>
+        <v>-0.1137</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8321</v>
+        <v>0.8289</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8565</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0244</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8565</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>0.8605</v>
@@ -1376,7 +1376,7 @@
         <v>0.0823</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3405</v>
+        <v>-0.3642</v>
       </c>
       <c r="E21" t="n">
         <v>0.2001</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0494</v>
+        <v>0.0492</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0203</v>
+        <v>0.0202</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4014</v>
+        <v>-0.4243</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0494</v>
+        <v>0.0492</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0494</v>
+        <v>0.0492</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0494</v>
+        <v>0.0492</v>
       </c>
       <c r="I22" t="n">
         <v>0.0496</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0202</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4412</v>
+        <v>-0.4635</v>
       </c>
       <c r="E23" t="n">
         <v>-0.0492</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0698</v>
+        <v>-0.0727</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0287</v>
+        <v>-0.0299</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4496</v>
+        <v>-0.4729</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0698</v>
+        <v>-0.0727</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7924</v>
+        <v>0.7895</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8622</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7924</v>
+        <v>0.7895</v>
       </c>
       <c r="I24" t="n">
         <v>0.7961</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1052</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-0.2559</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1467</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5655</v>
+        <v>-0.5861</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3568</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4957</v>
+        <v>-0.4938</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2039</v>
+        <v>-0.2031</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6216</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4957</v>
+        <v>-0.4938</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4957</v>
+        <v>-0.4938</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4957</v>
+        <v>-0.4938</v>
       </c>
       <c r="I27" t="n">
         <v>-0.498</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5782</v>
+        <v>-0.5724</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2378</v>
+        <v>-0.2354</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6549</v>
+        <v>-0.672</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5782</v>
+        <v>-0.5724</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.5583</v>
+        <v>-1.5525</v>
       </c>
       <c r="G28" t="n">
         <v>0.9801</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5583</v>
+        <v>-1.5525</v>
       </c>
       <c r="I28" t="n">
         <v>-1.5656</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5968</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2454</v>
+        <v>-0.2427</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6625</v>
+        <v>-0.679</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5968</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5968</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5968</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>-0.6052</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2597</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6764</v>
+        <v>-0.6955</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6314</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0167</v>
+        <v>-1.0129</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4181</v>
+        <v>-0.4166</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8321</v>
+        <v>-0.8474</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0167</v>
+        <v>-1.0129</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0167</v>
+        <v>-1.0129</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0167</v>
+        <v>-1.0129</v>
       </c>
       <c r="I31" t="n">
         <v>-1.0214</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0683</v>
+        <v>-1.0643</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4393</v>
+        <v>-0.4377</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8529</v>
+        <v>-0.8679</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0683</v>
+        <v>-1.0643</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0683</v>
+        <v>-1.0643</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0683</v>
+        <v>-1.0643</v>
       </c>
       <c r="I32" t="n">
         <v>-1.0733</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.5018</v>
+        <v>-1.4999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.6176</v>
+        <v>-0.6168</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0281</v>
+        <v>-1.0415</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.5018</v>
+        <v>-1.4999</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5018</v>
+        <v>-0.4999</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5018</v>
+        <v>-0.4999</v>
       </c>
       <c r="I33" t="n">
         <v>-0.5041</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.544</v>
+        <v>-1.5383</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.635</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0451</v>
+        <v>-1.0568</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.544</v>
+        <v>-1.5383</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.544</v>
+        <v>-1.5383</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.544</v>
+        <v>-1.5383</v>
       </c>
       <c r="I34" t="n">
         <v>-1.5512</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.5687</v>
+        <v>-1.557</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6451</v>
+        <v>-0.6403</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0551</v>
+        <v>-1.0642</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.5687</v>
+        <v>-1.557</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.5687</v>
+        <v>-1.557</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.5687</v>
+        <v>-1.557</v>
       </c>
       <c r="I35" t="n">
         <v>-1.5833</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6616</v>
+        <v>-1.6492</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6834</v>
+        <v>-0.6783</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0926</v>
+        <v>-1.101</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6616</v>
+        <v>-1.6492</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6616</v>
+        <v>-1.6492</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.6616</v>
+        <v>-1.6492</v>
       </c>
       <c r="I36" t="n">
         <v>-1.6771</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6678</v>
+        <v>-1.6534</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6859</v>
+        <v>-0.68</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0951</v>
+        <v>-1.1026</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6678</v>
+        <v>-1.6534</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2947</v>
+        <v>-1.2803</v>
       </c>
       <c r="G37" t="n">
         <v>-0.3731</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2947</v>
+        <v>-1.2803</v>
       </c>
       <c r="I37" t="n">
         <v>-1.3129</v>
@@ -2158,7 +2158,7 @@
         <v>-0.7149</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1236</v>
+        <v>-1.1364</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7383</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7972</v>
+        <v>-1.7853</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7391</v>
+        <v>-0.7342</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1474</v>
+        <v>-1.1552</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7972</v>
+        <v>-1.7853</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7972</v>
+        <v>-0.7853</v>
       </c>
       <c r="G39" t="n">
         <v>-1</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7972</v>
+        <v>-0.7853</v>
       </c>
       <c r="I39" t="n">
         <v>-0.8121</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0501</v>
+        <v>-2.0273</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8431</v>
+        <v>-0.8337</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2496</v>
+        <v>-1.2516</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0501</v>
+        <v>-2.0273</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0501</v>
+        <v>-2.0273</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0501</v>
+        <v>-2.0273</v>
       </c>
       <c r="I40" t="n">
         <v>-2.0789</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0799</v>
+        <v>-2.07</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8554</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2616</v>
+        <v>-1.2686</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0799</v>
+        <v>-2.07</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8867</v>
+        <v>-0.8768</v>
       </c>
       <c r="G41" t="n">
         <v>-1.1932</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8867</v>
+        <v>-0.8768</v>
       </c>
       <c r="I41" t="n">
         <v>-0.8991</v>
@@ -2342,7 +2342,7 @@
         <v>-1.1482</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.5492</v>
+        <v>-1.5562</v>
       </c>
       <c r="E42" t="n">
         <v>-2.7918</v>

--- a/database/event/6349/event_6349_evp_summary.xlsx
+++ b/database/event/6349/event_6349_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8519</v>
+        <v>6.9009</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4067</v>
+        <v>2.8381</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8875</v>
+        <v>2.4774</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8519</v>
+        <v>6.9009</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3225</v>
+        <v>2.8136</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5294</v>
+        <v>4.0873</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3225</v>
+        <v>2.8184</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3561</v>
+        <v>3.1806</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5294</v>
+        <v>4.0873</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8855</v>
+        <v>7.2679</v>
       </c>
       <c r="N2" t="n">
         <v>317</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3396</v>
+        <v>5.0186</v>
       </c>
       <c r="C3" t="n">
-        <v>2.196</v>
+        <v>2.064</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6834</v>
+        <v>1.6276</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3396</v>
+        <v>5.0186</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5409</v>
+        <v>1.6623</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7987</v>
+        <v>3.3563</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5409</v>
+        <v>1.6623</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5801</v>
+        <v>1.876</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7987</v>
+        <v>3.3563</v>
       </c>
       <c r="K3" t="n">
         <v>127</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3788</v>
+        <v>5.2323</v>
       </c>
       <c r="N3" t="n">
         <v>317</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4869</v>
+        <v>4.1415</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8453</v>
+        <v>1.7032</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3437</v>
+        <v>1.2317</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4869</v>
+        <v>4.1415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9671</v>
+        <v>1.2487</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5198</v>
+        <v>2.8928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9671</v>
+        <v>1.2487</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9917</v>
+        <v>1.4092</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5198</v>
+        <v>2.8928</v>
       </c>
       <c r="K4" t="n">
         <v>150</v>
@@ -621,7 +621,7 @@
         <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5115</v>
+        <v>4.302</v>
       </c>
       <c r="N4" t="n">
         <v>334</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4843</v>
+        <v>4.0603</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8442</v>
+        <v>1.6698</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3426</v>
+        <v>1.195</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4843</v>
+        <v>4.0603</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7868</v>
+        <v>2.2026</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6975</v>
+        <v>1.8577</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7868</v>
+        <v>2.2026</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0693</v>
+        <v>2.4857</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6975</v>
+        <v>1.8577</v>
       </c>
       <c r="K5" t="n">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="L5" t="n">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7668</v>
+        <v>4.3434</v>
       </c>
       <c r="N5" t="n">
-        <v>225</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3737</v>
+        <v>4.0153</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7987</v>
+        <v>1.6513</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2986</v>
+        <v>1.1747</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3737</v>
+        <v>4.0153</v>
       </c>
       <c r="F6" t="n">
-        <v>4.162</v>
+        <v>3.713</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2117</v>
+        <v>0.3023</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1841</v>
+        <v>7.596</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3914</v>
+        <v>3.9495</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2117</v>
+        <v>0.3023</v>
       </c>
       <c r="K6" t="n">
         <v>158</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6031</v>
+        <v>4.2518</v>
       </c>
       <c r="N6" t="n">
         <v>217</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1808</v>
+        <v>3.8281</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7194</v>
+        <v>1.5743</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2217</v>
+        <v>1.0902</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1808</v>
+        <v>3.8281</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4568</v>
+        <v>3.1766</v>
       </c>
       <c r="G7" t="n">
-        <v>1.724</v>
+        <v>0.6515</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4568</v>
+        <v>5.7061</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5194</v>
+        <v>2.9669</v>
       </c>
       <c r="J7" t="n">
-        <v>1.724</v>
+        <v>0.6515</v>
       </c>
       <c r="K7" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="L7" t="n">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2434</v>
+        <v>3.6184</v>
       </c>
       <c r="N7" t="n">
-        <v>317</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8715</v>
+        <v>3.6555</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5922</v>
+        <v>1.5034</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0985</v>
+        <v>1.0123</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8715</v>
+        <v>3.6555</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2785</v>
+        <v>0.3034</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.407</v>
+        <v>3.3521</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6529</v>
+        <v>0.3034</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7713</v>
+        <v>0.3424</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.407</v>
+        <v>3.3521</v>
       </c>
       <c r="K8" t="n">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3643</v>
+        <v>3.6945</v>
       </c>
       <c r="N8" t="n">
-        <v>217</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7862</v>
+        <v>3.5293</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5571</v>
+        <v>1.4515</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0645</v>
+        <v>0.9553</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7862</v>
+        <v>3.5293</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0549</v>
+        <v>3.7757</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8411</v>
+        <v>-0.2464</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0549</v>
+        <v>7.8168</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0563</v>
+        <v>4.0644</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8411</v>
+        <v>-0.2464</v>
       </c>
       <c r="K9" t="n">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="L9" t="n">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7848</v>
+        <v>3.818</v>
       </c>
       <c r="N9" t="n">
-        <v>317</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5829</v>
+        <v>3.3812</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4735</v>
+        <v>1.3906</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9835</v>
+        <v>0.8884</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5829</v>
+        <v>3.3812</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.0439</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0854</v>
+        <v>3.425</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.0439</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5153</v>
+        <v>-0.0495</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0854</v>
+        <v>3.425</v>
       </c>
       <c r="K10" t="n">
         <v>150</v>
@@ -897,7 +897,7 @@
         <v>264</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5701</v>
+        <v>3.3755</v>
       </c>
       <c r="N10" t="n">
         <v>414</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2668</v>
+        <v>3.136</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3435</v>
+        <v>1.2897</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8576</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2668</v>
+        <v>3.136</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8484</v>
+        <v>2.597</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5816</v>
+        <v>0.539</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8484</v>
+        <v>3.6638</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1193</v>
+        <v>1.905</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5816</v>
+        <v>0.539</v>
       </c>
       <c r="K11" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5377</v>
+        <v>2.444</v>
       </c>
       <c r="N11" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6466</v>
+        <v>3.0522</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0884</v>
+        <v>1.2552</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6105</v>
+        <v>0.7399</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6466</v>
+        <v>3.0522</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1351</v>
+        <v>2.6523</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5115</v>
+        <v>0.3999</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1351</v>
+        <v>3.8586</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7306</v>
+        <v>2.0063</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5115</v>
+        <v>0.3999</v>
       </c>
       <c r="K12" t="n">
         <v>158</v>
@@ -989,7 +989,7 @@
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2421</v>
+        <v>2.4062</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5704</v>
+        <v>2.9242</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0571</v>
+        <v>1.2026</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6821</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5704</v>
+        <v>2.9242</v>
       </c>
       <c r="F13" t="n">
-        <v>2.534</v>
+        <v>3.2156</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0364</v>
+        <v>-0.2914</v>
       </c>
       <c r="H13" t="n">
-        <v>2.534</v>
+        <v>5.8436</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5768</v>
+        <v>3.0384</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0364</v>
+        <v>-0.2914</v>
       </c>
       <c r="K13" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="L13" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6132</v>
+        <v>2.747</v>
       </c>
       <c r="N13" t="n">
-        <v>197</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2299</v>
+        <v>2.7083</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9171</v>
+        <v>1.1138</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4445</v>
+        <v>0.5846</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2299</v>
+        <v>2.7083</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2299</v>
+        <v>2.6917</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0166</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2299</v>
+        <v>2.6917</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2866</v>
+        <v>2.9177</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.0166</v>
       </c>
       <c r="K14" t="n">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2866</v>
+        <v>2.9343</v>
       </c>
       <c r="N14" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2207</v>
+        <v>2.3194</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9133</v>
+        <v>0.9539</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4408</v>
+        <v>0.4091</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2207</v>
+        <v>2.3194</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8376</v>
+        <v>2.3194</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3831</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8376</v>
+        <v>2.3194</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4894</v>
+        <v>2.6175</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3831</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8725</v>
+        <v>2.6175</v>
       </c>
       <c r="N15" t="n">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1121</v>
+        <v>2.285</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8686</v>
+        <v>0.9397</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3976</v>
+        <v>0.3935</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1121</v>
+        <v>2.285</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6474</v>
+        <v>1.8357</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4647</v>
+        <v>0.4493</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6474</v>
+        <v>1.8357</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6893</v>
+        <v>2.0716</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4647</v>
+        <v>0.4493</v>
       </c>
       <c r="K16" t="n">
         <v>150</v>
@@ -1173,7 +1173,7 @@
         <v>179</v>
       </c>
       <c r="M16" t="n">
-        <v>2.154</v>
+        <v>2.5209</v>
       </c>
       <c r="N16" t="n">
         <v>329</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9308</v>
+        <v>2.1233</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7941</v>
+        <v>0.8732</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3253</v>
+        <v>0.3205</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9308</v>
+        <v>2.1233</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3254</v>
+        <v>0.5514</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6054</v>
+        <v>1.5719</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3254</v>
+        <v>0.5514</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3337</v>
+        <v>0.6223</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6054</v>
+        <v>1.5719</v>
       </c>
       <c r="K17" t="n">
         <v>150</v>
@@ -1219,7 +1219,7 @@
         <v>234</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9391</v>
+        <v>2.1942</v>
       </c>
       <c r="N17" t="n">
         <v>384</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5003</v>
+        <v>1.5006</v>
       </c>
       <c r="C18" t="n">
-        <v>0.617</v>
+        <v>0.6171</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1538</v>
+        <v>0.0394</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5003</v>
+        <v>1.5006</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0959</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4044</v>
+        <v>0.9537</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0959</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1238</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4044</v>
+        <v>0.9537</v>
       </c>
       <c r="K18" t="n">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5282</v>
+        <v>1.5963</v>
       </c>
       <c r="N18" t="n">
-        <v>205</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2054</v>
+        <v>1.3802</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4957</v>
+        <v>0.5676</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0363</v>
+        <v>-0.0149</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2054</v>
+        <v>1.3802</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2931</v>
+        <v>1.0414</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9123</v>
+        <v>0.3388</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2931</v>
+        <v>1.0414</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3031</v>
+        <v>1.1752</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9123</v>
+        <v>0.3388</v>
       </c>
       <c r="K19" t="n">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="L19" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2154</v>
+        <v>1.514</v>
       </c>
       <c r="N19" t="n">
-        <v>307</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8289</v>
+        <v>1.232</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3409</v>
+        <v>0.5067</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1137</v>
+        <v>-0.0818</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8289</v>
+        <v>1.232</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0717</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0244</v>
+        <v>0.1603</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0717</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8605</v>
+        <v>1.1158</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0244</v>
+        <v>0.1603</v>
       </c>
       <c r="K20" t="n">
         <v>144</v>
@@ -1357,7 +1357,7 @@
         <v>80</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8361000000000001</v>
+        <v>1.2761</v>
       </c>
       <c r="N20" t="n">
         <v>224</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2001</v>
+        <v>1.1452</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0823</v>
+        <v>0.471</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3642</v>
+        <v>-0.121</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2001</v>
+        <v>1.1452</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6451</v>
+        <v>1.3886</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.445</v>
+        <v>-0.2434</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6451</v>
+        <v>1.3886</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5229</v>
+        <v>0.722</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.445</v>
+        <v>-0.2434</v>
       </c>
       <c r="K21" t="n">
         <v>148</v>
@@ -1403,7 +1403,7 @@
         <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>0.07790000000000002</v>
+        <v>0.4786</v>
       </c>
       <c r="N21" t="n">
         <v>225</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0492</v>
+        <v>0.4935</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0202</v>
+        <v>0.203</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4243</v>
+        <v>-0.4152</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0492</v>
+        <v>0.4935</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0492</v>
+        <v>0.6133</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.1198</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0492</v>
+        <v>0.6133</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0496</v>
+        <v>0.3189</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.1198</v>
       </c>
       <c r="K22" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0496</v>
+        <v>0.1991</v>
       </c>
       <c r="N22" t="n">
-        <v>119</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0492</v>
+        <v>0.4166</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0202</v>
+        <v>0.1713</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4635</v>
+        <v>-0.4499</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0492</v>
+        <v>0.4166</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2179</v>
+        <v>0.9527</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2671</v>
+        <v>-0.5361</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2179</v>
+        <v>0.9527</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1766</v>
+        <v>0.9919</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2671</v>
+        <v>-0.5361</v>
       </c>
       <c r="K23" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="L23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0905</v>
+        <v>0.4558</v>
       </c>
       <c r="N23" t="n">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0727</v>
+        <v>0.384</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0299</v>
+        <v>0.1579</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4729</v>
+        <v>-0.4647</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0727</v>
+        <v>0.384</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7895</v>
+        <v>0.384</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8622</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7895</v>
+        <v>0.384</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7961</v>
+        <v>0.3998</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8622</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.06609999999999994</v>
+        <v>0.3998</v>
       </c>
       <c r="N24" t="n">
-        <v>205</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2559</v>
+        <v>0.0482</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1052</v>
+        <v>0.0198</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.6163</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2559</v>
+        <v>0.0482</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0857</v>
+        <v>0.0031</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1702</v>
+        <v>0.0451</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0857</v>
+        <v>0.0031</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0857</v>
+        <v>0.0016</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1702</v>
+        <v>0.0451</v>
       </c>
       <c r="K25" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="L25" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2559</v>
+        <v>0.0467</v>
       </c>
       <c r="N25" t="n">
-        <v>166</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3568</v>
+        <v>0.0277</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1467</v>
+        <v>0.0114</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5861</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3568</v>
+        <v>0.0277</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3502</v>
+        <v>0.0648</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0066</v>
+        <v>-0.0371</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3502</v>
+        <v>0.0648</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3502</v>
+        <v>0.0648</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0066</v>
+        <v>-0.0371</v>
       </c>
       <c r="K26" t="n">
         <v>117</v>
@@ -1633,7 +1633,7 @@
         <v>80</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3568</v>
+        <v>0.0277</v>
       </c>
       <c r="N26" t="n">
         <v>197</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4938</v>
+        <v>-0.0451</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2031</v>
+        <v>-0.0185</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.6584</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4938</v>
+        <v>-0.0451</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4938</v>
+        <v>-0.0479</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4938</v>
+        <v>-0.0479</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.498</v>
+        <v>-0.0479</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
       <c r="K27" t="n">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.498</v>
+        <v>-0.0451</v>
       </c>
       <c r="N27" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5724</v>
+        <v>-0.134</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2354</v>
+        <v>-0.0551</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.672</v>
+        <v>-0.6985</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5724</v>
+        <v>-0.134</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.5525</v>
+        <v>-0.134</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9801</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5525</v>
+        <v>-0.134</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.5656</v>
+        <v>-0.1395</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9801</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5855000000000001</v>
+        <v>-0.1395</v>
       </c>
       <c r="N28" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4361</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2427</v>
+        <v>-0.1794</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.679</v>
+        <v>-0.8349</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4361</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4361</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4361</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6052</v>
+        <v>-0.4921</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6052</v>
+        <v>-0.4921</v>
       </c>
       <c r="N29" t="n">
         <v>173</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6314</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2597</v>
+        <v>-0.2705</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6955</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6314</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4703</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1611</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4703</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3812</v>
+        <v>-0.6849</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1611</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="L30" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5423</v>
+        <v>-0.6849</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0129</v>
+        <v>-0.6713</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4166</v>
+        <v>-0.2761</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8474</v>
+        <v>-0.9411</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0129</v>
+        <v>-0.6713</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0129</v>
+        <v>-0.6713</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0129</v>
+        <v>-0.6713</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0214</v>
+        <v>-0.6989</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0214</v>
+        <v>-0.6989</v>
       </c>
       <c r="N31" t="n">
         <v>119</v>
@@ -1872,461 +1872,461 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0643</v>
+        <v>-0.7452</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4377</v>
+        <v>-0.3065</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8679</v>
+        <v>-0.9744</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0643</v>
+        <v>-0.7452</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0643</v>
+        <v>-1.4659</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0643</v>
+        <v>-1.4659</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0733</v>
+        <v>-1.5262</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="K32" t="n">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.0733</v>
+        <v>-0.8055</v>
       </c>
       <c r="N32" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.4999</v>
+        <v>-0.9893</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.6168</v>
+        <v>-0.4069</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0415</v>
+        <v>-1.0846</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.4999</v>
+        <v>-0.9893</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4999</v>
+        <v>-0.9893</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4999</v>
+        <v>-0.9893</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5041</v>
+        <v>-1.0723</v>
       </c>
       <c r="J33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="L33" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.5041</v>
+        <v>-1.0723</v>
       </c>
       <c r="N33" t="n">
-        <v>76</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.5383</v>
+        <v>-1.1161</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.459</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0568</v>
+        <v>-1.1419</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.5383</v>
+        <v>-1.1161</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.5383</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.2396</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.5383</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.5512</v>
+        <v>-0.9892</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.2396</v>
       </c>
       <c r="K34" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.5512</v>
+        <v>-1.2288</v>
       </c>
       <c r="N34" t="n">
-        <v>119</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.557</v>
+        <v>-1.1566</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6403</v>
+        <v>-0.4757</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0642</v>
+        <v>-1.1602</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.557</v>
+        <v>-1.1566</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.557</v>
+        <v>-1.1566</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.557</v>
+        <v>-1.1566</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.5833</v>
+        <v>-1.2042</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.5833</v>
+        <v>-1.2042</v>
       </c>
       <c r="N35" t="n">
-        <v>147</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6492</v>
+        <v>-1.2001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6783</v>
+        <v>-0.4936</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.101</v>
+        <v>-1.1798</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6492</v>
+        <v>-1.2001</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6492</v>
+        <v>-0.5074</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.6927</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.6492</v>
+        <v>-0.5074</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6771</v>
+        <v>-0.5726</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.6927</v>
       </c>
       <c r="K36" t="n">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6771</v>
+        <v>-1.2653</v>
       </c>
       <c r="N36" t="n">
-        <v>173</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6534</v>
+        <v>-1.2887</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.68</v>
+        <v>-0.53</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1026</v>
+        <v>-1.2198</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6534</v>
+        <v>-1.2887</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2803</v>
+        <v>-0.2887</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3731</v>
+        <v>-1</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2803</v>
+        <v>-0.2887</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3129</v>
+        <v>-0.3006</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3731</v>
+        <v>-1</v>
       </c>
       <c r="K37" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="L37" t="n">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.686</v>
+        <v>-1.3006</v>
       </c>
       <c r="N37" t="n">
-        <v>317</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7383</v>
+        <v>-1.3312</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7149</v>
+        <v>-0.5475</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1364</v>
+        <v>-1.239</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7383</v>
+        <v>-1.3312</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7383</v>
+        <v>-1.3312</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7383</v>
+        <v>-1.3312</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7383</v>
+        <v>-1.4429</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="L38" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7383</v>
+        <v>-1.4429</v>
       </c>
       <c r="N38" t="n">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7853</v>
+        <v>-1.57</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7342</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1552</v>
+        <v>-1.3468</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7853</v>
+        <v>-1.57</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7853</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-0.9082</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7853</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8121</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.9082</v>
       </c>
       <c r="K39" t="n">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8121</v>
+        <v>-1.57</v>
       </c>
       <c r="N39" t="n">
-        <v>223</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0273</v>
+        <v>-1.5988</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8337</v>
+        <v>-0.6575</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2516</v>
+        <v>-1.3598</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0273</v>
+        <v>-1.5988</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0273</v>
+        <v>-0.5988</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0273</v>
+        <v>-0.5988</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0789</v>
+        <v>-0.7035</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0789</v>
+        <v>-1.7035</v>
       </c>
       <c r="N40" t="n">
-        <v>179</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.07</v>
+        <v>-1.6637</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.6842</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2686</v>
+        <v>-1.3891</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.07</v>
+        <v>-1.6637</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8768</v>
+        <v>-1.6637</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.1932</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8768</v>
+        <v>-1.6637</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8991</v>
+        <v>-1.8775</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.1932</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="L41" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0923</v>
+        <v>-1.8775</v>
       </c>
       <c r="N41" t="n">
-        <v>334</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42">
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.7918</v>
+        <v>-2.5536</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.1482</v>
+        <v>-1.0502</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.5562</v>
+        <v>-1.7908</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.7918</v>
+        <v>-2.5536</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.7918</v>
+        <v>-1.8054</v>
       </c>
       <c r="G42" t="n">
-        <v>-1</v>
+        <v>-0.7482</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.7918</v>
+        <v>-1.8054</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.4523</v>
+        <v>-0.9387</v>
       </c>
       <c r="J42" t="n">
-        <v>-1</v>
+        <v>-0.7482</v>
       </c>
       <c r="K42" t="n">
         <v>158</v>
@@ -2369,7 +2369,7 @@
         <v>59</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.4523</v>
+        <v>-1.6869</v>
       </c>
       <c r="N42" t="n">
         <v>217</v>
@@ -2475,10 +2475,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3041</v>
+        <v>0.32</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9943</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.228</v>
+        <v>-0.1769</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.244</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3956</v>
+        <v>-0.2634</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.098800000000001</v>
+        <v>-6.0582</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.74</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4113</v>
+        <v>-0.273</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.459899999999999</v>
+        <v>-6.279</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6218</v>
+        <v>-0.4146</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.3014</v>
+        <v>-9.5358</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3298</v>
+        <v>1.2217</v>
       </c>
       <c r="J7" t="n">
-        <v>30.5854</v>
+        <v>28.0991</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.41</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>22.0616</v>
+        <v>22.7792</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6776</v>
+        <v>0.7662</v>
       </c>
       <c r="J9" t="n">
-        <v>15.5848</v>
+        <v>17.6226</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6533</v>
+        <v>0.7437</v>
       </c>
       <c r="J10" t="n">
-        <v>15.0259</v>
+        <v>17.1051</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2858</v>
+        <v>0.3783</v>
       </c>
       <c r="J11" t="n">
-        <v>6.5734</v>
+        <v>8.700900000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2529</v>
+        <v>0.2596</v>
       </c>
       <c r="J12" t="n">
-        <v>7.0812</v>
+        <v>7.2688</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0223</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6244</v>
+        <v>-0.238</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2156</v>
+        <v>-0.1443</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.0368</v>
+        <v>-4.0404</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3976</v>
+        <v>-0.2552</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.1328</v>
+        <v>-7.1456</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4692</v>
+        <v>-0.3037</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.1376</v>
+        <v>-8.5036</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8208</v>
+        <v>0.8002</v>
       </c>
       <c r="J17" t="n">
-        <v>22.9824</v>
+        <v>22.4056</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7503</v>
+        <v>0.7281</v>
       </c>
       <c r="J18" t="n">
-        <v>21.0084</v>
+        <v>20.3868</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.19</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5755</v>
+        <v>0.5556</v>
       </c>
       <c r="J19" t="n">
-        <v>16.114</v>
+        <v>15.5568</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1977</v>
+        <v>0.2366</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5356</v>
+        <v>6.6248</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8683</v>
+        <v>-0.8292</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.3124</v>
+        <v>-23.2176</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.333</v>
+        <v>0.3531</v>
       </c>
       <c r="J22" t="n">
-        <v>9.99</v>
+        <v>10.593</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2859</v>
+        <v>0.3063</v>
       </c>
       <c r="J23" t="n">
-        <v>8.577</v>
+        <v>9.189</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2557</v>
+        <v>-0.1593</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.671</v>
+        <v>-4.779</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2724</v>
+        <v>-0.1698</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.172000000000001</v>
+        <v>-5.094</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5467</v>
+        <v>-0.3569</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.401</v>
+        <v>-10.707</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.47</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2003</v>
+        <v>0.8489</v>
       </c>
       <c r="J27" t="n">
-        <v>36.009</v>
+        <v>25.467</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.36</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9692</v>
+        <v>0.7017</v>
       </c>
       <c r="J28" t="n">
-        <v>29.076</v>
+        <v>21.051</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.08</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2191</v>
+        <v>0.2626</v>
       </c>
       <c r="J29" t="n">
-        <v>6.573</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3937</v>
+        <v>-0.3246</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.811</v>
+        <v>-9.738</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7337</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.011</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4841</v>
+        <v>0.4721</v>
       </c>
       <c r="J32" t="n">
-        <v>14.0389</v>
+        <v>13.6909</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1785</v>
+        <v>0.1859</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1765</v>
+        <v>5.3911</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="J34" t="n">
-        <v>2.8188</v>
+        <v>2.7144</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1513</v>
+        <v>-0.0871</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.3877</v>
+        <v>-2.5259</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.64</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5951</v>
+        <v>-0.3913</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.2579</v>
+        <v>-11.3477</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9974</v>
+        <v>0.7153</v>
       </c>
       <c r="J37" t="n">
-        <v>28.9246</v>
+        <v>20.7437</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5982</v>
+        <v>0.4712</v>
       </c>
       <c r="J38" t="n">
-        <v>17.3478</v>
+        <v>13.6648</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3108</v>
+        <v>0.2999</v>
       </c>
       <c r="J39" t="n">
-        <v>9.013199999999999</v>
+        <v>8.697100000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2432</v>
+        <v>-0.1833</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.0528</v>
+        <v>-5.3157</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7893</v>
+        <v>-0.7446</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.8897</v>
+        <v>-21.5934</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4853</v>
+        <v>0.3794</v>
       </c>
       <c r="J42" t="n">
-        <v>13.5884</v>
+        <v>10.6232</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2523</v>
+        <v>0.207</v>
       </c>
       <c r="J43" t="n">
-        <v>7.0644</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.093</v>
+        <v>0.0925</v>
       </c>
       <c r="J44" t="n">
-        <v>2.604</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0002</v>
+        <v>0.0203</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0056</v>
+        <v>0.5684</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3249</v>
+        <v>-0.1954</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.097200000000001</v>
+        <v>-5.4712</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4407</v>
+        <v>0.3666</v>
       </c>
       <c r="J47" t="n">
-        <v>12.3396</v>
+        <v>10.2648</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1762</v>
+        <v>-0.1073</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.9336</v>
+        <v>-3.0044</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.213</v>
+        <v>-0.1296</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.964</v>
+        <v>-3.6288</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2477</v>
+        <v>-0.1514</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.9356</v>
+        <v>-4.2392</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.86</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2808</v>
+        <v>-0.1726</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.8624</v>
+        <v>-4.8328</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2897</v>
+        <v>0.3097</v>
       </c>
       <c r="J52" t="n">
-        <v>7.5322</v>
+        <v>8.052199999999999</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.11</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2734</v>
+        <v>0.2895</v>
       </c>
       <c r="J53" t="n">
-        <v>7.1084</v>
+        <v>7.527</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2046</v>
+        <v>0.204</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3196</v>
+        <v>5.304</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5182</v>
+        <v>-0.3367</v>
       </c>
       <c r="J55" t="n">
-        <v>-13.4732</v>
+        <v>-8.754200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5961</v>
+        <v>-0.3931</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.4986</v>
+        <v>-10.2206</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1807</v>
+        <v>0.8385</v>
       </c>
       <c r="J57" t="n">
-        <v>30.6982</v>
+        <v>21.801</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7428</v>
+        <v>0.5699</v>
       </c>
       <c r="J58" t="n">
-        <v>19.3128</v>
+        <v>14.8174</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2866</v>
+        <v>0.3345</v>
       </c>
       <c r="J59" t="n">
-        <v>7.4516</v>
+        <v>8.696999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.031</v>
+        <v>0.094</v>
       </c>
       <c r="J60" t="n">
-        <v>0.806</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.93</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3777</v>
+        <v>-0.3042</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.8202</v>
+        <v>-7.9092</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1718</v>
+        <v>0.155</v>
       </c>
       <c r="J62" t="n">
-        <v>3.9514</v>
+        <v>3.565</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1509</v>
+        <v>0.1294</v>
       </c>
       <c r="J63" t="n">
-        <v>3.4707</v>
+        <v>2.9762</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.86</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2342</v>
+        <v>-0.1625</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.3866</v>
+        <v>-3.7375</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4613</v>
+        <v>-0.3</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.6099</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5438</v>
+        <v>-0.3571</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.5074</v>
+        <v>-8.2133</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4224</v>
+        <v>1.0039</v>
       </c>
       <c r="J67" t="n">
-        <v>32.7152</v>
+        <v>23.0897</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0228</v>
+        <v>0.7569</v>
       </c>
       <c r="J68" t="n">
-        <v>23.5244</v>
+        <v>17.4087</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.3</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7036</v>
+        <v>0.592</v>
       </c>
       <c r="J69" t="n">
-        <v>16.1828</v>
+        <v>13.616</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>1.27</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5526</v>
       </c>
       <c r="J70" t="n">
-        <v>14.3865</v>
+        <v>12.7098</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4498</v>
+        <v>-0.3705</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3454</v>
+        <v>-8.5215</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>2.06</v>
       </c>
       <c r="I72" t="n">
-        <v>1.9506</v>
+        <v>1.4859</v>
       </c>
       <c r="J72" t="n">
-        <v>37.0614</v>
+        <v>28.2321</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5634</v>
+        <v>0.5302</v>
       </c>
       <c r="J73" t="n">
-        <v>10.7046</v>
+        <v>10.0738</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.54</v>
+        <v>0.5164</v>
       </c>
       <c r="J74" t="n">
-        <v>10.26</v>
+        <v>9.8116</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4692</v>
+        <v>0.4742</v>
       </c>
       <c r="J75" t="n">
-        <v>8.9148</v>
+        <v>9.0098</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2727</v>
+        <v>0.3549</v>
       </c>
       <c r="J76" t="n">
-        <v>5.1813</v>
+        <v>6.7431</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>0.93</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0022</v>
+        <v>-0.0374</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.0418</v>
+        <v>-0.7106</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>0.75</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2985</v>
+        <v>-0.2432</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.6715</v>
+        <v>-4.6208</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.58</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5894</v>
+        <v>-0.4015</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.1986</v>
+        <v>-7.6285</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.55</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6324</v>
+        <v>-0.4295</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.0156</v>
+        <v>-8.160500000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.5</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.701</v>
+        <v>-0.4764</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.319</v>
+        <v>-9.051600000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.02</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0946</v>
+        <v>0.0593</v>
       </c>
       <c r="J82" t="n">
-        <v>3.2164</v>
+        <v>2.0162</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0337</v>
+        <v>0.0073</v>
       </c>
       <c r="J83" t="n">
-        <v>1.1458</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1263</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.2942</v>
+        <v>-2.8254</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1263</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.2942</v>
+        <v>-2.8254</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3392</v>
+        <v>-0.2122</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.5328</v>
+        <v>-7.2148</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.34</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5361</v>
+        <v>0.4091</v>
       </c>
       <c r="J87" t="n">
-        <v>18.2274</v>
+        <v>13.9094</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2669</v>
+        <v>0.2278</v>
       </c>
       <c r="J88" t="n">
-        <v>9.0746</v>
+        <v>7.7452</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1318</v>
+        <v>0.1335</v>
       </c>
       <c r="J89" t="n">
-        <v>4.4812</v>
+        <v>4.539</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0104</v>
+        <v>0.0353</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3536</v>
+        <v>1.2002</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.96</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1501</v>
+        <v>-0.0745</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.1034</v>
+        <v>-2.533</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7417</v>
+        <v>0.5696</v>
       </c>
       <c r="J92" t="n">
-        <v>20.0259</v>
+        <v>15.3792</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.19</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.4565</v>
       </c>
       <c r="J93" t="n">
-        <v>14.4666</v>
+        <v>12.3255</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4758</v>
+        <v>0.4277</v>
       </c>
       <c r="J94" t="n">
-        <v>12.8466</v>
+        <v>11.5479</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.15</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4048</v>
+        <v>0.3988</v>
       </c>
       <c r="J95" t="n">
-        <v>10.9296</v>
+        <v>10.7676</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>1.04</v>
       </c>
       <c r="I96" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1282</v>
       </c>
       <c r="J96" t="n">
-        <v>1.7739</v>
+        <v>3.4614</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.2</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4332</v>
+        <v>0.4283</v>
       </c>
       <c r="J97" t="n">
-        <v>11.6964</v>
+        <v>11.5641</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.068</v>
+        <v>0.032</v>
       </c>
       <c r="J98" t="n">
-        <v>1.836</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.97</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0148</v>
+        <v>-0.035</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.3996</v>
+        <v>-0.945</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.61</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6096</v>
+        <v>-0.4042</v>
       </c>
       <c r="J100" t="n">
-        <v>-16.4592</v>
+        <v>-10.9134</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.54</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6973</v>
+        <v>-0.4688</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.8271</v>
+        <v>-12.6576</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.02</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0655</v>
+        <v>0.0867</v>
       </c>
       <c r="J102" t="n">
-        <v>1.703</v>
+        <v>2.2542</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>-1.0912</v>
+        <v>-1.0784</v>
       </c>
       <c r="J103" t="n">
-        <v>-28.3712</v>
+        <v>-28.0384</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.41</v>
       </c>
       <c r="I104" t="n">
-        <v>-1.5108</v>
+        <v>-1.5637</v>
       </c>
       <c r="J104" t="n">
-        <v>-39.2808</v>
+        <v>-40.6562</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.61</v>
       </c>
       <c r="I105" t="n">
-        <v>1.5199</v>
+        <v>1.0627</v>
       </c>
       <c r="J105" t="n">
-        <v>39.5174</v>
+        <v>27.6302</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>1.54</v>
       </c>
       <c r="I106" t="n">
-        <v>1.385</v>
+        <v>0.97</v>
       </c>
       <c r="J106" t="n">
-        <v>36.01</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.13</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2783</v>
+        <v>0.3066</v>
       </c>
       <c r="J107" t="n">
-        <v>7.2358</v>
+        <v>7.9716</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1346</v>
+        <v>-0.0757</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.4996</v>
+        <v>-1.9682</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4668</v>
+        <v>-0.2977</v>
       </c>
       <c r="J109" t="n">
-        <v>-12.1368</v>
+        <v>-7.7402</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2783</v>
+        <v>0.3066</v>
       </c>
       <c r="J110" t="n">
-        <v>7.2358</v>
+        <v>7.9716</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>1.04</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1154</v>
+        <v>0.1164</v>
       </c>
       <c r="J111" t="n">
-        <v>3.0004</v>
+        <v>3.0264</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>0.85</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2772</v>
+        <v>-0.1768</v>
       </c>
       <c r="J112" t="n">
-        <v>-8.316000000000001</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2772</v>
+        <v>-0.1768</v>
       </c>
       <c r="J113" t="n">
-        <v>-8.316000000000001</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>0.58</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.6551</v>
+        <v>-0.4369</v>
       </c>
       <c r="J114" t="n">
-        <v>-19.653</v>
+        <v>-13.107</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.418</v>
+        <v>0.3513</v>
       </c>
       <c r="J115" t="n">
-        <v>12.54</v>
+        <v>10.539</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>1.04</v>
       </c>
       <c r="I116" t="n">
-        <v>0.155</v>
+        <v>0.1075</v>
       </c>
       <c r="J116" t="n">
-        <v>4.65</v>
+        <v>3.225</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3616</v>
+        <v>0.3177</v>
       </c>
       <c r="J117" t="n">
-        <v>10.848</v>
+        <v>9.531000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3307</v>
+        <v>0.2948</v>
       </c>
       <c r="J118" t="n">
-        <v>9.920999999999999</v>
+        <v>8.843999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4442</v>
+        <v>-0.278</v>
       </c>
       <c r="J119" t="n">
-        <v>-13.326</v>
+        <v>-8.34</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>1.43</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6248</v>
+        <v>0.461</v>
       </c>
       <c r="J120" t="n">
-        <v>18.744</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>1.27</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4194</v>
+        <v>0.353</v>
       </c>
       <c r="J121" t="n">
-        <v>12.582</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2573</v>
+        <v>0.8975</v>
       </c>
       <c r="J122" t="n">
-        <v>31.4325</v>
+        <v>22.4375</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5356</v>
+        <v>0.4999</v>
       </c>
       <c r="J123" t="n">
-        <v>13.39</v>
+        <v>12.4975</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.62</v>
       </c>
       <c r="I124" t="n">
-        <v>-1.1377</v>
+        <v>-1.1322</v>
       </c>
       <c r="J124" t="n">
-        <v>-28.4425</v>
+        <v>-28.305</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.62</v>
       </c>
       <c r="I125" t="n">
-        <v>1.4118</v>
+        <v>0.9958</v>
       </c>
       <c r="J125" t="n">
-        <v>35.295</v>
+        <v>24.895</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>1.45</v>
       </c>
       <c r="I126" t="n">
-        <v>1.0745</v>
+        <v>0.785</v>
       </c>
       <c r="J126" t="n">
-        <v>26.8625</v>
+        <v>19.625</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.31</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5013</v>
+        <v>0.4916</v>
       </c>
       <c r="J127" t="n">
-        <v>12.5325</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.29</v>
       </c>
       <c r="I128" t="n">
-        <v>0.475</v>
+        <v>0.4718</v>
       </c>
       <c r="J128" t="n">
-        <v>11.875</v>
+        <v>11.795</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2373</v>
+        <v>-0.1337</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.9325</v>
+        <v>-3.3425</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>1.06</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0984</v>
+        <v>0.1472</v>
       </c>
       <c r="J130" t="n">
-        <v>2.46</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2204</v>
+        <v>-0.1222</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.51</v>
+        <v>-3.055</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7983</v>
+        <v>0.786</v>
       </c>
       <c r="J132" t="n">
-        <v>23.949</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6529</v>
+        <v>0.6429</v>
       </c>
       <c r="J133" t="n">
-        <v>19.587</v>
+        <v>19.287</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J134" t="n">
-        <v>7.047</v>
+        <v>8.583</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.204</v>
+        <v>0.2572</v>
       </c>
       <c r="J135" t="n">
-        <v>6.12</v>
+        <v>7.716</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1075</v>
+        <v>0.1651</v>
       </c>
       <c r="J136" t="n">
-        <v>3.225</v>
+        <v>4.953</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3926</v>
+        <v>0.4435</v>
       </c>
       <c r="J137" t="n">
-        <v>11.778</v>
+        <v>13.305</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.04</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1429</v>
+        <v>0.1315</v>
       </c>
       <c r="J138" t="n">
-        <v>4.287</v>
+        <v>3.945</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.03</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1217</v>
+        <v>0.1066</v>
       </c>
       <c r="J139" t="n">
-        <v>3.651</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.88</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2385</v>
+        <v>-0.1487</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.155</v>
+        <v>-4.461</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.53</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7204</v>
+        <v>-0.4859</v>
       </c>
       <c r="J141" t="n">
-        <v>-21.612</v>
+        <v>-14.577</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2212</v>
+        <v>1.141</v>
       </c>
       <c r="J142" t="n">
-        <v>30.53</v>
+        <v>28.525</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>1.34</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8829</v>
+        <v>0.8843</v>
       </c>
       <c r="J143" t="n">
-        <v>22.0725</v>
+        <v>22.1075</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>1.3</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7907</v>
+        <v>0.793</v>
       </c>
       <c r="J144" t="n">
-        <v>19.7675</v>
+        <v>19.825</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1241</v>
+        <v>-0.0491</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.1025</v>
+        <v>-1.2275</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5571</v>
+        <v>-0.4889</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.9275</v>
+        <v>-12.2225</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.734</v>
+        <v>0.9153</v>
       </c>
       <c r="J147" t="n">
-        <v>18.35</v>
+        <v>22.8825</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4936</v>
+        <v>0.5766</v>
       </c>
       <c r="J148" t="n">
-        <v>12.34</v>
+        <v>14.415</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>0.62</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.6018</v>
+        <v>-0.3979</v>
       </c>
       <c r="J149" t="n">
-        <v>-15.045</v>
+        <v>-9.9475</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>0.59</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6398</v>
+        <v>-0.4258</v>
       </c>
       <c r="J150" t="n">
-        <v>-15.995</v>
+        <v>-10.645</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7013</v>
+        <v>-0.4717</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.5325</v>
+        <v>-11.7925</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1647</v>
+        <v>-0.1052</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.2822</v>
+        <v>-2.7352</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2217</v>
+        <v>-0.1382</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.7642</v>
+        <v>-3.5932</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.54</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.7088</v>
+        <v>-0.4771</v>
       </c>
       <c r="J154" t="n">
-        <v>-18.4288</v>
+        <v>-12.4046</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3919</v>
+        <v>0.4427</v>
       </c>
       <c r="J155" t="n">
-        <v>10.1894</v>
+        <v>11.5102</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>1.14</v>
       </c>
       <c r="I156" t="n">
-        <v>0.3169</v>
+        <v>0.346</v>
       </c>
       <c r="J156" t="n">
-        <v>8.2394</v>
+        <v>8.996</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8833</v>
+        <v>0.8601</v>
       </c>
       <c r="J157" t="n">
-        <v>22.9658</v>
+        <v>22.3626</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>0.63</v>
       </c>
       <c r="I158" t="n">
-        <v>-1.0788</v>
+        <v>-1.0641</v>
       </c>
       <c r="J158" t="n">
-        <v>-28.0488</v>
+        <v>-27.6666</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.54</v>
       </c>
       <c r="I159" t="n">
-        <v>-1.2636</v>
+        <v>-1.275</v>
       </c>
       <c r="J159" t="n">
-        <v>-32.8536</v>
+        <v>-33.15</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.77</v>
       </c>
       <c r="I160" t="n">
-        <v>1.793</v>
+        <v>1.5261</v>
       </c>
       <c r="J160" t="n">
-        <v>46.618</v>
+        <v>39.6786</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>1.14</v>
       </c>
       <c r="I161" t="n">
-        <v>0.4591</v>
+        <v>0.435</v>
       </c>
       <c r="J161" t="n">
-        <v>11.9366</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1483</v>
+        <v>0.1568</v>
       </c>
       <c r="J162" t="n">
-        <v>3.5592</v>
+        <v>3.7632</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1416</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.3984</v>
+        <v>-1.5864</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2824</v>
+        <v>-0.1624</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.7776</v>
+        <v>-3.8976</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.44</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6438</v>
+        <v>0.5656</v>
       </c>
       <c r="J165" t="n">
-        <v>15.4512</v>
+        <v>13.5744</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.4</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5956</v>
+        <v>0.5204</v>
       </c>
       <c r="J166" t="n">
-        <v>14.2944</v>
+        <v>12.4896</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.17</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3274</v>
+        <v>0.2857</v>
       </c>
       <c r="J167" t="n">
-        <v>7.8576</v>
+        <v>6.8568</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.06</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1395</v>
+        <v>0.1189</v>
       </c>
       <c r="J168" t="n">
-        <v>3.348</v>
+        <v>2.8536</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.74</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4737</v>
+        <v>-0.3018</v>
       </c>
       <c r="J169" t="n">
-        <v>-11.3688</v>
+        <v>-7.2432</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2143</v>
+        <v>0.1826</v>
       </c>
       <c r="J170" t="n">
-        <v>5.1432</v>
+        <v>4.3824</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>1.1</v>
       </c>
       <c r="I171" t="n">
-        <v>0.2143</v>
+        <v>0.1826</v>
       </c>
       <c r="J171" t="n">
-        <v>5.1432</v>
+        <v>4.3824</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>0.88</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1353</v>
+        <v>-0.1253</v>
       </c>
       <c r="J172" t="n">
-        <v>-4.059</v>
+        <v>-3.759</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>0.34</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.9176</v>
+        <v>-0.6387</v>
       </c>
       <c r="J173" t="n">
-        <v>-27.528</v>
+        <v>-19.161</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.27</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.9972</v>
+        <v>-0.7026</v>
       </c>
       <c r="J174" t="n">
-        <v>-29.916</v>
+        <v>-21.078</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.9084</v>
       </c>
       <c r="J175" t="n">
-        <v>21.516</v>
+        <v>27.252</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.0832</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>-2.496</v>
+        <v>-2.709</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>0.65</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.9542</v>
+        <v>-0.9403</v>
       </c>
       <c r="J177" t="n">
-        <v>-28.626</v>
+        <v>-28.209</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.58</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.1139</v>
+        <v>-1.1103</v>
       </c>
       <c r="J178" t="n">
-        <v>-33.417</v>
+        <v>-33.309</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.47</v>
       </c>
       <c r="I179" t="n">
-        <v>-1.3498</v>
+        <v>-1.3733</v>
       </c>
       <c r="J179" t="n">
-        <v>-40.494</v>
+        <v>-41.199</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>1.24</v>
       </c>
       <c r="I180" t="n">
-        <v>0.876</v>
+        <v>0.8364</v>
       </c>
       <c r="J180" t="n">
-        <v>26.28</v>
+        <v>25.092</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>1.2</v>
       </c>
       <c r="I181" t="n">
-        <v>0.7785</v>
+        <v>0.7266</v>
       </c>
       <c r="J181" t="n">
-        <v>23.355</v>
+        <v>21.798</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.58</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8098</v>
+        <v>0.7254</v>
       </c>
       <c r="J182" t="n">
-        <v>24.294</v>
+        <v>21.762</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.21</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3488</v>
+        <v>0.2999</v>
       </c>
       <c r="J183" t="n">
-        <v>10.464</v>
+        <v>8.997</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2097</v>
+        <v>0.1995</v>
       </c>
       <c r="J184" t="n">
-        <v>6.291</v>
+        <v>5.985</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2786</v>
+        <v>-0.1604</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.358000000000001</v>
+        <v>-4.812</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2786</v>
+        <v>-0.1604</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.358000000000001</v>
+        <v>-4.812</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4524</v>
+        <v>0.4013</v>
       </c>
       <c r="J187" t="n">
-        <v>13.572</v>
+        <v>12.039</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3672</v>
+        <v>0.3164</v>
       </c>
       <c r="J188" t="n">
-        <v>11.016</v>
+        <v>9.492000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1393</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.179</v>
+        <v>-2.538</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.86</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2827</v>
+        <v>-0.1733</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.481</v>
+        <v>-5.199</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.6</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6404</v>
+        <v>-0.4254</v>
       </c>
       <c r="J191" t="n">
-        <v>-19.212</v>
+        <v>-12.762</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>0.79</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.2449</v>
+        <v>-0.2061</v>
       </c>
       <c r="J192" t="n">
-        <v>-5.1429</v>
+        <v>-4.3281</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.74</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3248</v>
+        <v>-0.257</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.8208</v>
+        <v>-5.397</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.66</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4736</v>
+        <v>-0.3307</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.945600000000001</v>
+        <v>-6.9447</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.62</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.538</v>
+        <v>-0.3673</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.298</v>
+        <v>-7.7133</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5825</v>
+        <v>-0.3952</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.2325</v>
+        <v>-8.299200000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>1.5541</v>
+        <v>1.3712</v>
       </c>
       <c r="J197" t="n">
-        <v>32.6361</v>
+        <v>28.7952</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.56</v>
       </c>
       <c r="I198" t="n">
-        <v>1.231</v>
+        <v>1.1716</v>
       </c>
       <c r="J198" t="n">
-        <v>25.851</v>
+        <v>24.6036</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.52</v>
       </c>
       <c r="I199" t="n">
-        <v>1.1493</v>
+        <v>1.124</v>
       </c>
       <c r="J199" t="n">
-        <v>24.1353</v>
+        <v>23.604</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.47</v>
       </c>
       <c r="I200" t="n">
-        <v>1.0414</v>
+        <v>1.0642</v>
       </c>
       <c r="J200" t="n">
-        <v>21.8694</v>
+        <v>22.3482</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5828</v>
+        <v>-0.511</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.2388</v>
+        <v>-10.731</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0722</v>
+        <v>0.0354</v>
       </c>
       <c r="J202" t="n">
-        <v>1.805</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.8</v>
+        <v>-1.8225</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1474</v>
+        <v>-0.1197</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.685</v>
+        <v>-2.9925</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2689</v>
+        <v>-0.1816</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.7225</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.59</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.633</v>
+        <v>-0.4214</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.825</v>
+        <v>-10.535</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.73</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6417</v>
+        <v>1.4189</v>
       </c>
       <c r="J207" t="n">
-        <v>41.0425</v>
+        <v>35.4725</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.5</v>
       </c>
       <c r="I208" t="n">
-        <v>1.2055</v>
+        <v>1.1335</v>
       </c>
       <c r="J208" t="n">
-        <v>30.1375</v>
+        <v>28.3375</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1325</v>
+        <v>0.2067</v>
       </c>
       <c r="J209" t="n">
-        <v>3.3125</v>
+        <v>5.1675</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.96</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3066</v>
+        <v>-0.2255</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.665</v>
+        <v>-5.6375</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4582</v>
+        <v>-0.3826</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.455</v>
+        <v>-9.565</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.23</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4233</v>
+        <v>0.4906</v>
       </c>
       <c r="J212" t="n">
-        <v>11.8524</v>
+        <v>13.7368</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.04</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1106</v>
+        <v>0.1146</v>
       </c>
       <c r="J213" t="n">
-        <v>3.0968</v>
+        <v>3.2088</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>1.02</v>
       </c>
       <c r="I214" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0649</v>
       </c>
       <c r="J214" t="n">
-        <v>1.7696</v>
+        <v>1.8172</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0722</v>
+        <v>-0.0367</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.0216</v>
+        <v>-1.0276</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4278</v>
+        <v>-0.2697</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.9784</v>
+        <v>-7.5516</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>1.7718</v>
+        <v>1.5108</v>
       </c>
       <c r="J217" t="n">
-        <v>49.6104</v>
+        <v>42.3024</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5908</v>
+        <v>0.5629</v>
       </c>
       <c r="J218" t="n">
-        <v>16.5424</v>
+        <v>15.7612</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4643</v>
+        <v>-0.4016</v>
       </c>
       <c r="J219" t="n">
-        <v>-13.0004</v>
+        <v>-11.2448</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.88</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4919</v>
+        <v>-0.4299</v>
       </c>
       <c r="J220" t="n">
-        <v>-13.7732</v>
+        <v>-12.0372</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9291</v>
+        <v>-0.8969</v>
       </c>
       <c r="J221" t="n">
-        <v>-26.0148</v>
+        <v>-25.1132</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>0.58</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.4021</v>
+        <v>-0.3352</v>
       </c>
       <c r="J222" t="n">
-        <v>-6.8357</v>
+        <v>-5.6984</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.42</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.6746</v>
+        <v>-0.5018</v>
       </c>
       <c r="J223" t="n">
-        <v>-11.4682</v>
+        <v>-8.5306</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.41</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.7039</v>
+        <v>-0.5102</v>
       </c>
       <c r="J224" t="n">
-        <v>-11.9663</v>
+        <v>-8.673400000000001</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.34</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.5778</v>
       </c>
       <c r="J225" t="n">
-        <v>-14.0607</v>
+        <v>-9.8226</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.34</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.5778</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.0607</v>
+        <v>-9.8226</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>2.23</v>
       </c>
       <c r="I227" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J227" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>2.06</v>
       </c>
       <c r="I228" t="n">
-        <v>1.9804</v>
+        <v>1.693</v>
       </c>
       <c r="J228" t="n">
-        <v>33.6668</v>
+        <v>28.781</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.56</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0844</v>
+        <v>1.1482</v>
       </c>
       <c r="J229" t="n">
-        <v>18.4348</v>
+        <v>19.5194</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>1.43</v>
       </c>
       <c r="I230" t="n">
-        <v>0.8284</v>
+        <v>0.9786</v>
       </c>
       <c r="J230" t="n">
-        <v>14.0828</v>
+        <v>16.6362</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>1.13</v>
       </c>
       <c r="I231" t="n">
-        <v>0.179</v>
+        <v>0.2852</v>
       </c>
       <c r="J231" t="n">
-        <v>3.043</v>
+        <v>4.8484</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.12</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2484</v>
+        <v>0.2782</v>
       </c>
       <c r="J232" t="n">
-        <v>8.694000000000001</v>
+        <v>9.737</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.03</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0669</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>2.3415</v>
+        <v>3.059</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2707</v>
+        <v>-0.16</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.474500000000001</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.16</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3121</v>
+        <v>0.3547</v>
       </c>
       <c r="J235" t="n">
-        <v>10.9235</v>
+        <v>12.4145</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.98</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0834</v>
+        <v>-0.0391</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.919</v>
+        <v>-1.3685</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.022</v>
+        <v>0.0308</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.77</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>0.91</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.4153</v>
+        <v>-0.3491</v>
       </c>
       <c r="J238" t="n">
-        <v>-14.5355</v>
+        <v>-12.2185</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.6795</v>
+        <v>-0.6248</v>
       </c>
       <c r="J239" t="n">
-        <v>-23.7825</v>
+        <v>-21.868</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.4</v>
       </c>
       <c r="I240" t="n">
-        <v>1.0658</v>
+        <v>1.0329</v>
       </c>
       <c r="J240" t="n">
-        <v>37.303</v>
+        <v>36.1515</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>1.39</v>
       </c>
       <c r="I241" t="n">
-        <v>1.0446</v>
+        <v>1.017</v>
       </c>
       <c r="J241" t="n">
-        <v>36.561</v>
+        <v>35.595</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2617</v>
+        <v>0.2958</v>
       </c>
       <c r="J242" t="n">
-        <v>7.0659</v>
+        <v>7.9866</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1352</v>
+        <v>0.1542</v>
       </c>
       <c r="J243" t="n">
-        <v>3.6504</v>
+        <v>4.1634</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.84</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3346</v>
+        <v>-0.2031</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.0342</v>
+        <v>-5.4837</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.21</v>
       </c>
       <c r="I245" t="n">
-        <v>0.3834</v>
+        <v>0.4442</v>
       </c>
       <c r="J245" t="n">
-        <v>10.3518</v>
+        <v>11.9934</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.97</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1092</v>
+        <v>-0.0541</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.9484</v>
+        <v>-1.4607</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>0.83</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.5656</v>
+        <v>-0.5262</v>
       </c>
       <c r="J247" t="n">
-        <v>-15.2712</v>
+        <v>-14.2074</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>0.77</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6823</v>
       </c>
       <c r="J248" t="n">
-        <v>-19.4481</v>
+        <v>-18.4221</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-1.1312</v>
+        <v>-1.1247</v>
       </c>
       <c r="J249" t="n">
-        <v>-30.5424</v>
+        <v>-30.3669</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.8908</v>
+        <v>0.8539</v>
       </c>
       <c r="J250" t="n">
-        <v>24.0516</v>
+        <v>23.0553</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>1.27</v>
       </c>
       <c r="I251" t="n">
-        <v>0.8676</v>
+        <v>0.8286</v>
       </c>
       <c r="J251" t="n">
-        <v>23.4252</v>
+        <v>22.3722</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.2</v>
       </c>
       <c r="I252" t="n">
-        <v>0.402</v>
+        <v>0.4569</v>
       </c>
       <c r="J252" t="n">
-        <v>10.854</v>
+        <v>12.3363</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0319</v>
+        <v>0.0086</v>
       </c>
       <c r="J253" t="n">
-        <v>0.8613</v>
+        <v>0.2322</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.91</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1905</v>
+        <v>-0.1175</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.1435</v>
+        <v>-3.1725</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.84</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3095</v>
+        <v>-0.1922</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.3565</v>
+        <v>-5.1894</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.79</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3851</v>
+        <v>-0.2428</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.3977</v>
+        <v>-6.5556</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.26</v>
       </c>
       <c r="I257" t="n">
-        <v>0.763</v>
+        <v>0.7362</v>
       </c>
       <c r="J257" t="n">
-        <v>20.601</v>
+        <v>19.8774</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.24</v>
       </c>
       <c r="I258" t="n">
-        <v>0.715</v>
+        <v>0.6872</v>
       </c>
       <c r="J258" t="n">
-        <v>19.305</v>
+        <v>18.5544</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.12</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3944</v>
+        <v>0.3795</v>
       </c>
       <c r="J259" t="n">
-        <v>10.6488</v>
+        <v>10.2465</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.92</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3785</v>
+        <v>-0.3143</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.2195</v>
+        <v>-8.4861</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.89</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4651</v>
+        <v>-0.4021</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.5577</v>
+        <v>-10.8567</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9651</v>
+        <v>0.8833</v>
       </c>
       <c r="J262" t="n">
-        <v>24.1275</v>
+        <v>22.0825</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>0.99</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0766</v>
+        <v>-0.0287</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.915</v>
+        <v>-0.7175</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>0.95</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1638</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.095</v>
+        <v>-2.125</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1825</v>
+        <v>-0.0974</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.5625</v>
+        <v>-2.435</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3295</v>
+        <v>-0.1978</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.237500000000001</v>
+        <v>-4.945</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4162</v>
+        <v>0.3667</v>
       </c>
       <c r="J267" t="n">
-        <v>10.405</v>
+        <v>9.1675</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3733</v>
+        <v>0.3245</v>
       </c>
       <c r="J268" t="n">
-        <v>9.3325</v>
+        <v>8.112500000000001</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0607</v>
+        <v>-0.0351</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.5175</v>
+        <v>-0.8774999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.049</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.15</v>
+        <v>-1.225</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6683</v>
+        <v>-0.4462</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.7075</v>
+        <v>-11.155</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>0.98</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.012</v>
+        <v>-0.0275</v>
       </c>
       <c r="J272" t="n">
-        <v>-0.492</v>
+        <v>-1.1275</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>0.97</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0352</v>
+        <v>-0.0419</v>
       </c>
       <c r="J273" t="n">
-        <v>-1.4432</v>
+        <v>-1.7179</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>0.91</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.165</v>
+        <v>-0.1143</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.765</v>
+        <v>-4.6863</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2087</v>
+        <v>-0.1356</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.556699999999999</v>
+        <v>-5.5596</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.8</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3591</v>
+        <v>-0.2281</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.7231</v>
+        <v>-9.3521</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.56</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3755</v>
+        <v>1.2382</v>
       </c>
       <c r="J277" t="n">
-        <v>56.3955</v>
+        <v>50.7662</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>1.17</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5061</v>
+        <v>0.4995</v>
       </c>
       <c r="J278" t="n">
-        <v>20.7501</v>
+        <v>20.4795</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>1.06</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1505</v>
+        <v>0.2011</v>
       </c>
       <c r="J279" t="n">
-        <v>6.1705</v>
+        <v>8.245100000000001</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1537</v>
+        <v>-0.0856</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.3017</v>
+        <v>-3.5096</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.87</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5353</v>
+        <v>-0.4704</v>
       </c>
       <c r="J281" t="n">
-        <v>-21.9473</v>
+        <v>-19.2864</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.439</v>
+        <v>0.3857</v>
       </c>
       <c r="J282" t="n">
-        <v>11.414</v>
+        <v>10.0282</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.92</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.156</v>
+        <v>-0.1043</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.056</v>
+        <v>-2.7118</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.87</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2516</v>
+        <v>-0.1582</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.5416</v>
+        <v>-4.1132</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3014</v>
+        <v>-0.1894</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.8364</v>
+        <v>-4.9244</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4076</v>
+        <v>-0.2596</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.5976</v>
+        <v>-6.7496</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.47</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6774</v>
+        <v>0.5978</v>
       </c>
       <c r="J287" t="n">
-        <v>17.6124</v>
+        <v>15.5428</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.4</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5938</v>
+        <v>0.5193</v>
       </c>
       <c r="J288" t="n">
-        <v>15.4388</v>
+        <v>13.5018</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1462</v>
+        <v>0.1561</v>
       </c>
       <c r="J289" t="n">
-        <v>3.8012</v>
+        <v>4.0586</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1821</v>
+        <v>-0.093</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.7346</v>
+        <v>-2.418</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2515</v>
+        <v>-0.1407</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.539</v>
+        <v>-3.6582</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>1.099</v>
+        <v>1.0514</v>
       </c>
       <c r="J292" t="n">
-        <v>39.564</v>
+        <v>37.8504</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3622</v>
+        <v>0.3178</v>
       </c>
       <c r="J293" t="n">
-        <v>13.0392</v>
+        <v>11.4408</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.91</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3697</v>
+        <v>-0.3215</v>
       </c>
       <c r="J294" t="n">
-        <v>-13.3092</v>
+        <v>-11.574</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4858</v>
+        <v>-0.4354</v>
       </c>
       <c r="J295" t="n">
-        <v>-17.4888</v>
+        <v>-15.6744</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.77</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7436</v>
+        <v>-0.7002</v>
       </c>
       <c r="J296" t="n">
-        <v>-26.7696</v>
+        <v>-25.2072</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.52</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7456</v>
+        <v>0.9285</v>
       </c>
       <c r="J297" t="n">
-        <v>26.8416</v>
+        <v>33.426</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.21</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3525</v>
+        <v>0.4231</v>
       </c>
       <c r="J298" t="n">
-        <v>12.69</v>
+        <v>15.2316</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.14</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2395</v>
+        <v>0.299</v>
       </c>
       <c r="J299" t="n">
-        <v>8.622</v>
+        <v>10.764</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0543</v>
+        <v>-0.0118</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.9548</v>
+        <v>-0.4248</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4362</v>
+        <v>-0.2729</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.7032</v>
+        <v>-9.824400000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.88</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7943</v>
+        <v>1.5308</v>
       </c>
       <c r="J302" t="n">
-        <v>35.886</v>
+        <v>30.616</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.71</v>
       </c>
       <c r="I303" t="n">
-        <v>1.4921</v>
+        <v>1.3377</v>
       </c>
       <c r="J303" t="n">
-        <v>29.842</v>
+        <v>26.754</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.37</v>
       </c>
       <c r="I304" t="n">
-        <v>0.767</v>
+        <v>0.8928</v>
       </c>
       <c r="J304" t="n">
-        <v>15.34</v>
+        <v>17.856</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.32</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6585</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J305" t="n">
-        <v>13.17</v>
+        <v>15.656</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.18</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3411</v>
+        <v>0.4508</v>
       </c>
       <c r="J306" t="n">
-        <v>6.822</v>
+        <v>9.016</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>0.99</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1729</v>
+        <v>0.1762</v>
       </c>
       <c r="J307" t="n">
-        <v>3.458</v>
+        <v>3.524</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.64</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.4191</v>
+        <v>-0.332</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.382</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.48</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.6959</v>
+        <v>-0.4786</v>
       </c>
       <c r="J309" t="n">
-        <v>-13.918</v>
+        <v>-9.571999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.47</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.7103</v>
+        <v>-0.4881</v>
       </c>
       <c r="J310" t="n">
-        <v>-14.206</v>
+        <v>-9.762</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.29</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.6617</v>
       </c>
       <c r="J311" t="n">
-        <v>-18.962</v>
+        <v>-13.234</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.62</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8363</v>
+        <v>0.7532</v>
       </c>
       <c r="J312" t="n">
-        <v>21.7438</v>
+        <v>19.5832</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.22</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3391</v>
+        <v>0.3053</v>
       </c>
       <c r="J313" t="n">
-        <v>8.816599999999999</v>
+        <v>7.9378</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.266</v>
+        <v>0.2577</v>
       </c>
       <c r="J314" t="n">
-        <v>6.916</v>
+        <v>6.7002</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.02</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.0131</v>
+        <v>0.0238</v>
       </c>
       <c r="J315" t="n">
-        <v>-0.3406</v>
+        <v>0.6188</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1699</v>
+        <v>-0.0835</v>
       </c>
       <c r="J316" t="n">
-        <v>-4.4174</v>
+        <v>-2.171</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.15</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3301</v>
+        <v>0.2782</v>
       </c>
       <c r="J317" t="n">
-        <v>8.582599999999999</v>
+        <v>7.2332</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0346</v>
+        <v>0.0076</v>
       </c>
       <c r="J318" t="n">
-        <v>0.8996</v>
+        <v>0.1976</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.3732</v>
+        <v>-2.7508</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.86</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2753</v>
+        <v>-0.1707</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.1578</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.78</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.398</v>
+        <v>-0.252</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.348</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.1</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3017</v>
+        <v>0.3169</v>
       </c>
       <c r="J322" t="n">
-        <v>7.2408</v>
+        <v>7.6056</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>0.92</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.0898</v>
+        <v>-0.0896</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.1552</v>
+        <v>-2.1504</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>0.84</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2316</v>
+        <v>-0.1777</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.5584</v>
+        <v>-4.2648</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>0.68</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.5018</v>
+        <v>-0.3309</v>
       </c>
       <c r="J325" t="n">
-        <v>-12.0432</v>
+        <v>-7.9416</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>0.51</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7242</v>
+        <v>-0.4895</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.3808</v>
+        <v>-11.748</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.43</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0658</v>
+        <v>1.0447</v>
       </c>
       <c r="J327" t="n">
-        <v>25.5792</v>
+        <v>25.0728</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.37</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9368</v>
+        <v>0.9422</v>
       </c>
       <c r="J328" t="n">
-        <v>22.4832</v>
+        <v>22.6128</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>1.35</v>
       </c>
       <c r="I329" t="n">
-        <v>0.8922</v>
+        <v>0.8996</v>
       </c>
       <c r="J329" t="n">
-        <v>21.4128</v>
+        <v>21.5904</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>1.16</v>
       </c>
       <c r="I330" t="n">
-        <v>0.39</v>
+        <v>0.4573</v>
       </c>
       <c r="J330" t="n">
-        <v>9.359999999999999</v>
+        <v>10.9752</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.82</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6884</v>
+        <v>-0.6292</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.5216</v>
+        <v>-15.1008</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.02</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1269</v>
+        <v>0.1008</v>
       </c>
       <c r="J332" t="n">
-        <v>3.0456</v>
+        <v>2.4192</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.116</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J333" t="n">
-        <v>-2.784</v>
+        <v>-2.3664</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>0.84</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2762</v>
+        <v>-0.1828</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.6288</v>
+        <v>-4.3872</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>0.82</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3106</v>
+        <v>-0.2028</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.4544</v>
+        <v>-4.8672</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>0.73</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4483</v>
+        <v>-0.2909</v>
       </c>
       <c r="J336" t="n">
-        <v>-10.7592</v>
+        <v>-6.9816</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.51</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2372</v>
+        <v>1.1518</v>
       </c>
       <c r="J337" t="n">
-        <v>29.6928</v>
+        <v>27.6432</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>1.36</v>
       </c>
       <c r="I338" t="n">
-        <v>0.9232</v>
+        <v>0.926</v>
       </c>
       <c r="J338" t="n">
-        <v>22.1568</v>
+        <v>22.224</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8096</v>
+        <v>0.8137</v>
       </c>
       <c r="J339" t="n">
-        <v>19.4304</v>
+        <v>19.5288</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>1.06</v>
       </c>
       <c r="I340" t="n">
-        <v>0.1114</v>
+        <v>0.1817</v>
       </c>
       <c r="J340" t="n">
-        <v>2.6736</v>
+        <v>4.3608</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7085</v>
+        <v>-0.6516</v>
       </c>
       <c r="J341" t="n">
-        <v>-17.004</v>
+        <v>-15.6384</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6349/event_6349_evp_summary.xlsx
+++ b/database/event/6349/event_6349_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9009</v>
+        <v>6.8504</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8381</v>
+        <v>2.8173</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4774</v>
+        <v>2.4942</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9009</v>
+        <v>6.8504</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8136</v>
+        <v>2.615</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0873</v>
+        <v>4.2354</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8184</v>
+        <v>2.9985</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1806</v>
+        <v>3.2363</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0873</v>
+        <v>4.2354</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>7.2679</v>
+        <v>7.4717</v>
       </c>
       <c r="N2" t="n">
         <v>317</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0186</v>
+        <v>5.1532</v>
       </c>
       <c r="C3" t="n">
-        <v>2.064</v>
+        <v>2.1193</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6276</v>
+        <v>1.7216</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0186</v>
+        <v>5.1532</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6623</v>
+        <v>1.6244</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3563</v>
+        <v>3.5288</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6623</v>
+        <v>1.6244</v>
       </c>
       <c r="I3" t="n">
-        <v>1.876</v>
+        <v>1.7532</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3563</v>
+        <v>3.5288</v>
       </c>
       <c r="K3" t="n">
         <v>127</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2323</v>
+        <v>5.282</v>
       </c>
       <c r="N3" t="n">
         <v>317</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1415</v>
+        <v>4.2707</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7032</v>
+        <v>1.7564</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2317</v>
+        <v>1.3199</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1415</v>
+        <v>4.2707</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2487</v>
+        <v>1.1597</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8928</v>
+        <v>3.111</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2487</v>
+        <v>1.1597</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4092</v>
+        <v>1.2517</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8928</v>
+        <v>3.111</v>
       </c>
       <c r="K4" t="n">
         <v>150</v>
@@ -621,7 +621,7 @@
         <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>4.302</v>
+        <v>4.3627</v>
       </c>
       <c r="N4" t="n">
         <v>334</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0603</v>
+        <v>4.1872</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6698</v>
+        <v>1.722</v>
       </c>
       <c r="D5" t="n">
-        <v>1.195</v>
+        <v>1.2819</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0603</v>
+        <v>4.1872</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2026</v>
+        <v>2.2709</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8577</v>
+        <v>1.9163</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2026</v>
+        <v>2.2709</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4857</v>
+        <v>2.451</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8577</v>
+        <v>1.9163</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>190</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3434</v>
+        <v>4.3673</v>
       </c>
       <c r="N5" t="n">
         <v>317</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0153</v>
+        <v>4.0055</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6513</v>
+        <v>1.6473</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1747</v>
+        <v>1.1992</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0153</v>
+        <v>4.0055</v>
       </c>
       <c r="F6" t="n">
-        <v>3.713</v>
+        <v>3.6679</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3023</v>
+        <v>0.3376</v>
       </c>
       <c r="H6" t="n">
-        <v>7.596</v>
+        <v>7.2077</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9495</v>
+        <v>3.8921</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3023</v>
+        <v>0.3376</v>
       </c>
       <c r="K6" t="n">
         <v>158</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2518</v>
+        <v>4.2297</v>
       </c>
       <c r="N6" t="n">
         <v>217</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8281</v>
+        <v>3.9272</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5743</v>
+        <v>1.6151</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0902</v>
+        <v>1.1635</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8281</v>
+        <v>3.9272</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1766</v>
+        <v>0.3675</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6515</v>
+        <v>3.5597</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7061</v>
+        <v>0.3675</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9669</v>
+        <v>0.3966</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6515</v>
+        <v>3.5597</v>
       </c>
       <c r="K7" t="n">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="L7" t="n">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6184</v>
+        <v>3.9563</v>
       </c>
       <c r="N7" t="n">
-        <v>225</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6555</v>
+        <v>3.7987</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5034</v>
+        <v>1.5623</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0123</v>
+        <v>1.105</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6555</v>
+        <v>3.7987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3034</v>
+        <v>-0.0914</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3521</v>
+        <v>3.8902</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3034</v>
+        <v>-0.0914</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3424</v>
+        <v>-0.0987</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3521</v>
+        <v>3.8902</v>
       </c>
       <c r="K8" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="L8" t="n">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6945</v>
+        <v>3.7915</v>
       </c>
       <c r="N8" t="n">
-        <v>317</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5293</v>
+        <v>3.7695</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4515</v>
+        <v>1.5502</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9553</v>
+        <v>1.0918</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5293</v>
+        <v>3.7695</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7757</v>
+        <v>3.1063</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2464</v>
+        <v>0.6632</v>
       </c>
       <c r="H9" t="n">
-        <v>7.8168</v>
+        <v>5.3547</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0644</v>
+        <v>2.8915</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2464</v>
+        <v>0.6632</v>
       </c>
       <c r="K9" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L9" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.818</v>
+        <v>3.5547</v>
       </c>
       <c r="N9" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3812</v>
+        <v>3.4359</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3906</v>
+        <v>1.413</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8884</v>
+        <v>0.9399</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3812</v>
+        <v>3.4359</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0439</v>
+        <v>3.7085</v>
       </c>
       <c r="G10" t="n">
-        <v>3.425</v>
+        <v>-0.2726</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0439</v>
+        <v>7.3414</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0495</v>
+        <v>3.9643</v>
       </c>
       <c r="J10" t="n">
-        <v>3.425</v>
+        <v>-0.2726</v>
       </c>
       <c r="K10" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="L10" t="n">
-        <v>264</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3755</v>
+        <v>3.6917</v>
       </c>
       <c r="N10" t="n">
-        <v>414</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.136</v>
+        <v>3.0876</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2897</v>
+        <v>1.2698</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7813</v>
       </c>
       <c r="E11" t="n">
-        <v>3.136</v>
+        <v>3.0876</v>
       </c>
       <c r="F11" t="n">
-        <v>2.597</v>
+        <v>2.5325</v>
       </c>
       <c r="G11" t="n">
-        <v>0.539</v>
+        <v>0.5551</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6638</v>
+        <v>3.4615</v>
       </c>
       <c r="I11" t="n">
-        <v>1.905</v>
+        <v>1.8692</v>
       </c>
       <c r="J11" t="n">
-        <v>0.539</v>
+        <v>0.5551</v>
       </c>
       <c r="K11" t="n">
         <v>158</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.444</v>
+        <v>2.4243</v>
       </c>
       <c r="N11" t="n">
         <v>217</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0522</v>
+        <v>2.9677</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2552</v>
+        <v>1.2205</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7399</v>
+        <v>0.7268</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0522</v>
+        <v>2.9677</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6523</v>
+        <v>2.5609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3999</v>
+        <v>0.4068</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8586</v>
+        <v>3.5551</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0063</v>
+        <v>1.9197</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3999</v>
+        <v>0.4068</v>
       </c>
       <c r="K12" t="n">
         <v>158</v>
@@ -989,7 +989,7 @@
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4062</v>
+        <v>2.3265</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9242</v>
+        <v>2.8046</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2026</v>
+        <v>1.1534</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6821</v>
+        <v>0.6525</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9242</v>
+        <v>2.8046</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2156</v>
+        <v>3.1212</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2914</v>
+        <v>-0.3166</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8436</v>
+        <v>5.404</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0384</v>
+        <v>2.9181</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2914</v>
+        <v>-0.3166</v>
       </c>
       <c r="K13" t="n">
         <v>148</v>
@@ -1035,7 +1035,7 @@
         <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.747</v>
+        <v>2.6015</v>
       </c>
       <c r="N13" t="n">
         <v>225</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7083</v>
+        <v>2.4335</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1138</v>
+        <v>1.0008</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5846</v>
+        <v>0.4836</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7083</v>
+        <v>2.4335</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6917</v>
+        <v>2.4327</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0166</v>
+        <v>0.0008</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6917</v>
+        <v>2.5994</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9177</v>
+        <v>2.7351</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0166</v>
+        <v>0.0008</v>
       </c>
       <c r="K14" t="n">
         <v>117</v>
@@ -1081,7 +1081,7 @@
         <v>80</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9343</v>
+        <v>2.7359</v>
       </c>
       <c r="N14" t="n">
         <v>197</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3194</v>
+        <v>2.3334</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9539</v>
+        <v>0.9596</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4091</v>
+        <v>0.438</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3194</v>
+        <v>2.3334</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3194</v>
+        <v>1.8133</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.5201</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3194</v>
+        <v>1.8133</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6175</v>
+        <v>1.9571</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.5201</v>
       </c>
       <c r="K15" t="n">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6175</v>
+        <v>2.4772</v>
       </c>
       <c r="N15" t="n">
-        <v>193</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.285</v>
+        <v>2.3091</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9397</v>
+        <v>0.9496</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3935</v>
+        <v>0.4269</v>
       </c>
       <c r="E16" t="n">
-        <v>2.285</v>
+        <v>2.3091</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8357</v>
+        <v>2.3091</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4493</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8357</v>
+        <v>2.3289</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0716</v>
+        <v>2.5136</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4493</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L16" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5209</v>
+        <v>2.5136</v>
       </c>
       <c r="N16" t="n">
-        <v>329</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1233</v>
+        <v>2.2725</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8732</v>
+        <v>0.9346</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3205</v>
+        <v>0.4103</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1233</v>
+        <v>2.2725</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5514</v>
+        <v>0.5059</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5719</v>
+        <v>1.7666</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5514</v>
+        <v>0.5059</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6223</v>
+        <v>0.546</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5719</v>
+        <v>1.7666</v>
       </c>
       <c r="K17" t="n">
         <v>150</v>
@@ -1219,7 +1219,7 @@
         <v>234</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1942</v>
+        <v>2.3126</v>
       </c>
       <c r="N17" t="n">
         <v>384</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5006</v>
+        <v>1.5939</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6171</v>
+        <v>0.6555</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0394</v>
+        <v>0.1014</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5006</v>
+        <v>1.5939</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5673</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9537</v>
+        <v>1.0266</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5673</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6281</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9537</v>
+        <v>1.0266</v>
       </c>
       <c r="K18" t="n">
         <v>231</v>
@@ -1265,7 +1265,7 @@
         <v>76</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5963</v>
+        <v>1.6547</v>
       </c>
       <c r="N18" t="n">
         <v>307</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3802</v>
+        <v>1.504</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5676</v>
+        <v>0.6185</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0149</v>
+        <v>0.0604</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3802</v>
+        <v>1.504</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0414</v>
+        <v>1.111</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3388</v>
+        <v>0.393</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0414</v>
+        <v>1.111</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1752</v>
+        <v>1.1991</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3388</v>
+        <v>0.393</v>
       </c>
       <c r="K19" t="n">
         <v>150</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.514</v>
+        <v>1.5921</v>
       </c>
       <c r="N19" t="n">
         <v>205</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.232</v>
+        <v>1.2191</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5067</v>
+        <v>0.5014</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0818</v>
+        <v>-0.0692</v>
       </c>
       <c r="E20" t="n">
-        <v>1.232</v>
+        <v>1.2191</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0717</v>
+        <v>1.0242</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1603</v>
+        <v>0.1949</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0717</v>
+        <v>1.0242</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1158</v>
+        <v>1.0506</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1603</v>
+        <v>0.1949</v>
       </c>
       <c r="K20" t="n">
         <v>144</v>
@@ -1357,7 +1357,7 @@
         <v>80</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2761</v>
+        <v>1.2455</v>
       </c>
       <c r="N20" t="n">
         <v>224</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1452</v>
+        <v>1.0747</v>
       </c>
       <c r="C21" t="n">
-        <v>0.471</v>
+        <v>0.442</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.121</v>
+        <v>-0.135</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1452</v>
+        <v>1.0747</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3886</v>
+        <v>1.3241</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2434</v>
+        <v>-0.2494</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3886</v>
+        <v>1.3241</v>
       </c>
       <c r="I21" t="n">
-        <v>0.722</v>
+        <v>0.715</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2434</v>
+        <v>-0.2494</v>
       </c>
       <c r="K21" t="n">
         <v>148</v>
@@ -1403,7 +1403,7 @@
         <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4786</v>
+        <v>0.4656</v>
       </c>
       <c r="N21" t="n">
         <v>225</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4935</v>
+        <v>0.498</v>
       </c>
       <c r="C22" t="n">
-        <v>0.203</v>
+        <v>0.2048</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4152</v>
+        <v>-0.3975</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4935</v>
+        <v>0.498</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6133</v>
+        <v>0.6083</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1198</v>
+        <v>-0.1103</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6133</v>
+        <v>0.6083</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3189</v>
+        <v>0.3285</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1198</v>
+        <v>-0.1103</v>
       </c>
       <c r="K22" t="n">
         <v>148</v>
@@ -1449,7 +1449,7 @@
         <v>77</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1991</v>
+        <v>0.2182</v>
       </c>
       <c r="N22" t="n">
         <v>225</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4166</v>
+        <v>0.405</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1713</v>
+        <v>0.1666</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4499</v>
+        <v>-0.4398</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4166</v>
+        <v>0.405</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9527</v>
+        <v>0.9103</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5361</v>
+        <v>-0.5053</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9527</v>
+        <v>0.9103</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9919</v>
+        <v>0.9338</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5361</v>
+        <v>-0.5053</v>
       </c>
       <c r="K23" t="n">
         <v>125</v>
@@ -1495,7 +1495,7 @@
         <v>80</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4558</v>
+        <v>0.4285</v>
       </c>
       <c r="N23" t="n">
         <v>205</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.384</v>
+        <v>0.3515</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1579</v>
+        <v>0.1446</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4647</v>
+        <v>-0.4642</v>
       </c>
       <c r="E24" t="n">
-        <v>0.384</v>
+        <v>0.3515</v>
       </c>
       <c r="F24" t="n">
-        <v>0.384</v>
+        <v>0.3515</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.384</v>
+        <v>0.3515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3998</v>
+        <v>0.3606</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3998</v>
+        <v>0.3606</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0482</v>
+        <v>0.0335</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0198</v>
+        <v>0.0138</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6163</v>
+        <v>-0.609</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0482</v>
+        <v>0.0335</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0031</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0451</v>
+        <v>0.042</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0031</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0016</v>
+        <v>-0.0046</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0451</v>
+        <v>0.042</v>
       </c>
       <c r="K25" t="n">
         <v>148</v>
@@ -1587,7 +1587,7 @@
         <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0467</v>
+        <v>0.0374</v>
       </c>
       <c r="N25" t="n">
         <v>225</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0277</v>
+        <v>-0.0413</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0114</v>
+        <v>-0.017</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.643</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0277</v>
+        <v>-0.0413</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0648</v>
+        <v>-0.0709</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0371</v>
+        <v>0.0296</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0648</v>
+        <v>-0.0709</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0648</v>
+        <v>-0.0709</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0371</v>
+        <v>0.0296</v>
       </c>
       <c r="K26" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="L26" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0277</v>
+        <v>-0.0413</v>
       </c>
       <c r="N26" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0451</v>
+        <v>-0.0631</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0185</v>
+        <v>-0.026</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6584</v>
+        <v>-0.6529</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0451</v>
+        <v>-0.0631</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0479</v>
+        <v>0.0005</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0028</v>
+        <v>-0.0636</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0479</v>
+        <v>0.0005</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0479</v>
+        <v>0.0005</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0028</v>
+        <v>-0.0636</v>
       </c>
       <c r="K27" t="n">
+        <v>117</v>
+      </c>
+      <c r="L27" t="n">
         <v>80</v>
       </c>
-      <c r="L27" t="n">
-        <v>86</v>
-      </c>
       <c r="M27" t="n">
-        <v>-0.0451</v>
+        <v>-0.0631</v>
       </c>
       <c r="N27" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.134</v>
+        <v>-0.1772</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0551</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6985</v>
+        <v>-0.7049</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.134</v>
+        <v>-0.1772</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.134</v>
+        <v>-0.1772</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.134</v>
+        <v>-0.1772</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1395</v>
+        <v>-0.1818</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1395</v>
+        <v>-0.1818</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4361</v>
+        <v>-0.3894</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1794</v>
+        <v>-0.1601</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8349</v>
+        <v>-0.8015</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4361</v>
+        <v>-0.3894</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4361</v>
+        <v>-0.3894</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4361</v>
+        <v>-0.3894</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4921</v>
+        <v>-0.4203</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4921</v>
+        <v>-0.4203</v>
       </c>
       <c r="N29" t="n">
         <v>173</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2705</v>
+        <v>-0.2748</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9283</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-1.4682</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.8001</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-1.4682</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6849</v>
+        <v>-1.506</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.8001</v>
       </c>
       <c r="K30" t="n">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6849</v>
+        <v>-0.7059</v>
       </c>
       <c r="N30" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6713</v>
+        <v>-0.6989</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2761</v>
+        <v>-0.2874</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9411</v>
+        <v>-0.9424</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6713</v>
+        <v>-0.6989</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6713</v>
+        <v>-0.6989</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6713</v>
+        <v>-0.6989</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6989</v>
+        <v>-0.7169</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6989</v>
+        <v>-0.7169</v>
       </c>
       <c r="N31" t="n">
         <v>119</v>
@@ -1872,139 +1872,139 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7452</v>
+        <v>-0.7304</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3065</v>
+        <v>-0.3004</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9744</v>
+        <v>-0.9567</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7452</v>
+        <v>-0.7304</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.4659</v>
+        <v>-0.7304</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.4659</v>
+        <v>-0.7304</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.5262</v>
+        <v>-0.7492</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="L32" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8055</v>
+        <v>-0.7492</v>
       </c>
       <c r="N32" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9893</v>
+        <v>-1.0164</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4069</v>
+        <v>-0.418</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0846</v>
+        <v>-1.0869</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9893</v>
+        <v>-1.0164</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9893</v>
+        <v>-0.8994</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.117</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9893</v>
+        <v>-0.8994</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0723</v>
+        <v>-0.9707</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.117</v>
       </c>
       <c r="K33" t="n">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0723</v>
+        <v>-1.0877</v>
       </c>
       <c r="N33" t="n">
-        <v>173</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1161</v>
+        <v>-1.0174</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.459</v>
+        <v>-0.4184</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1419</v>
+        <v>-1.0873</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1161</v>
+        <v>-1.0174</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-1.0174</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2396</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-1.0174</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9892</v>
+        <v>-1.0705</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2396</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="L34" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2288</v>
+        <v>-1.0705</v>
       </c>
       <c r="N34" t="n">
-        <v>317</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1566</v>
+        <v>-1.2175</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4757</v>
+        <v>-0.5007</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1602</v>
+        <v>-1.1784</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1566</v>
+        <v>-1.2175</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1566</v>
+        <v>-1.2175</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1566</v>
+        <v>-1.2175</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2042</v>
+        <v>-1.2489</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2042</v>
+        <v>-1.2489</v>
       </c>
       <c r="N35" t="n">
         <v>119</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2001</v>
+        <v>-1.2321</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4936</v>
+        <v>-0.5067</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1798</v>
+        <v>-1.1851</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2001</v>
+        <v>-1.2321</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5074</v>
+        <v>-0.5248</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6927</v>
+        <v>-0.7073</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5074</v>
+        <v>-0.5248</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5726</v>
+        <v>-0.5664</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6927</v>
+        <v>-0.7073</v>
       </c>
       <c r="K36" t="n">
         <v>150</v>
@@ -2093,7 +2093,7 @@
         <v>184</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2653</v>
+        <v>-1.2737</v>
       </c>
       <c r="N36" t="n">
         <v>334</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2887</v>
+        <v>-1.2699</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.53</v>
+        <v>-0.5223</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2198</v>
+        <v>-1.2023</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2887</v>
+        <v>-1.2699</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2887</v>
+        <v>-1.2699</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2887</v>
+        <v>-1.2699</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3006</v>
+        <v>-1.3362</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="L37" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3006</v>
+        <v>-1.3362</v>
       </c>
       <c r="N37" t="n">
-        <v>76</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3312</v>
+        <v>-1.3163</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5475</v>
+        <v>-0.5413</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.239</v>
+        <v>-1.2234</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3312</v>
+        <v>-1.3163</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3312</v>
+        <v>-0.3163</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3312</v>
+        <v>-0.3163</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4429</v>
+        <v>-0.3244</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
-        <v>147</v>
+        <v>50</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4429</v>
+        <v>-1.3244</v>
       </c>
       <c r="N38" t="n">
-        <v>147</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.57</v>
+        <v>-1.6107</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.6624</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3468</v>
+        <v>-1.3574</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.57</v>
+        <v>-1.6107</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6107</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9082</v>
+        <v>-1</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6107</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6761</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9082</v>
+        <v>-1</v>
       </c>
       <c r="K39" t="n">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="L39" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.57</v>
+        <v>-1.6761</v>
       </c>
       <c r="N39" t="n">
-        <v>162</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5988</v>
+        <v>-1.612</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6575</v>
+        <v>-0.663</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3598</v>
+        <v>-1.358</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5988</v>
+        <v>-1.612</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5988</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.9421</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5988</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7035</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.9421</v>
       </c>
       <c r="K40" t="n">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="L40" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7035</v>
+        <v>-1.612</v>
       </c>
       <c r="N40" t="n">
-        <v>223</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6637</v>
+        <v>-1.6401</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6842</v>
+        <v>-0.6745</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3891</v>
+        <v>-1.3708</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6637</v>
+        <v>-1.6401</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6637</v>
+        <v>-1.6401</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6637</v>
+        <v>-1.6401</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8775</v>
+        <v>-1.7702</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8775</v>
+        <v>-1.7702</v>
       </c>
       <c r="N41" t="n">
         <v>179</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.5536</v>
+        <v>-2.4322</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.0502</v>
+        <v>-1.0003</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.7908</v>
+        <v>-1.7314</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.5536</v>
+        <v>-2.4322</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.8054</v>
+        <v>-1.6621</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.7482</v>
+        <v>-0.7701</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.8054</v>
+        <v>-1.6621</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9387</v>
+        <v>-0.8975</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.7482</v>
+        <v>-0.7701</v>
       </c>
       <c r="K42" t="n">
         <v>158</v>
@@ -2369,7 +2369,7 @@
         <v>59</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.6869</v>
+        <v>-1.6676</v>
       </c>
       <c r="N42" t="n">
         <v>217</v>
@@ -2475,10 +2475,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.32</v>
+        <v>0.3065</v>
       </c>
       <c r="J2" t="n">
-        <v>7.36</v>
+        <v>7.0495</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1769</v>
+        <v>-0.1954</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.0687</v>
+        <v>-4.4942</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2634</v>
+        <v>-0.2816</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.0582</v>
+        <v>-6.4768</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.74</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.273</v>
+        <v>-0.2909</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.279</v>
+        <v>-6.6907</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4146</v>
+        <v>-0.4272</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.5358</v>
+        <v>-9.8256</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2217</v>
+        <v>1.2641</v>
       </c>
       <c r="J7" t="n">
-        <v>28.0991</v>
+        <v>29.0743</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.41</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9408</v>
       </c>
       <c r="J8" t="n">
-        <v>22.7792</v>
+        <v>21.6384</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7662</v>
+        <v>0.7343</v>
       </c>
       <c r="J9" t="n">
-        <v>17.6226</v>
+        <v>16.8889</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7437</v>
+        <v>0.7145</v>
       </c>
       <c r="J10" t="n">
-        <v>17.1051</v>
+        <v>16.4335</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3783</v>
+        <v>0.3872</v>
       </c>
       <c r="J11" t="n">
-        <v>8.700900000000001</v>
+        <v>8.9056</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2596</v>
+        <v>0.2573</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2688</v>
+        <v>7.2044</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.238</v>
+        <v>-0.448</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1443</v>
+        <v>-0.1602</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.0404</v>
+        <v>-4.4856</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2552</v>
+        <v>-0.2712</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.1456</v>
+        <v>-7.5936</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3037</v>
+        <v>-0.3186</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.5036</v>
+        <v>-8.9208</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8002</v>
+        <v>0.7533</v>
       </c>
       <c r="J17" t="n">
-        <v>22.4056</v>
+        <v>21.0924</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7281</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>20.3868</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.19</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5556</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>15.5568</v>
+        <v>15.0304</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2366</v>
+        <v>0.2436</v>
       </c>
       <c r="J20" t="n">
-        <v>6.6248</v>
+        <v>6.8208</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8292</v>
+        <v>-0.7653</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.2176</v>
+        <v>-21.4284</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3531</v>
+        <v>0.3619</v>
       </c>
       <c r="J22" t="n">
-        <v>10.593</v>
+        <v>10.857</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3063</v>
+        <v>0.3055</v>
       </c>
       <c r="J23" t="n">
-        <v>9.189</v>
+        <v>9.164999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1593</v>
+        <v>-0.1744</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.779</v>
+        <v>-5.232</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1698</v>
+        <v>-0.185</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.094</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3569</v>
+        <v>-0.369</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.707</v>
+        <v>-11.07</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.47</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8489</v>
+        <v>0.9329</v>
       </c>
       <c r="J27" t="n">
-        <v>25.467</v>
+        <v>27.987</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.36</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7017</v>
+        <v>0.7739</v>
       </c>
       <c r="J28" t="n">
-        <v>21.051</v>
+        <v>23.217</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.08</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2626</v>
+        <v>0.2689</v>
       </c>
       <c r="J29" t="n">
-        <v>7.878</v>
+        <v>8.067</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3246</v>
+        <v>-0.3117</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.738</v>
+        <v>-9.351000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6349</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.46</v>
+        <v>-19.047</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4721</v>
+        <v>0.5226</v>
       </c>
       <c r="J32" t="n">
-        <v>13.6909</v>
+        <v>15.1554</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1859</v>
+        <v>0.1932</v>
       </c>
       <c r="J33" t="n">
-        <v>5.3911</v>
+        <v>5.6028</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0936</v>
+        <v>0.1013</v>
       </c>
       <c r="J34" t="n">
-        <v>2.7144</v>
+        <v>2.9377</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0871</v>
+        <v>-0.0982</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.5259</v>
+        <v>-2.8478</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.64</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3913</v>
+        <v>-0.4011</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.3477</v>
+        <v>-11.6319</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7153</v>
+        <v>0.7859</v>
       </c>
       <c r="J37" t="n">
-        <v>20.7437</v>
+        <v>22.7911</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4712</v>
+        <v>0.517</v>
       </c>
       <c r="J38" t="n">
-        <v>13.6648</v>
+        <v>14.993</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2999</v>
+        <v>0.3015</v>
       </c>
       <c r="J39" t="n">
-        <v>8.697100000000001</v>
+        <v>8.743499999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1833</v>
+        <v>-0.1818</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.3157</v>
+        <v>-5.2722</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7446</v>
+        <v>-0.6927</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.5934</v>
+        <v>-20.0883</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3794</v>
+        <v>0.4189</v>
       </c>
       <c r="J42" t="n">
-        <v>10.6232</v>
+        <v>11.7292</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.207</v>
+        <v>0.2217</v>
       </c>
       <c r="J43" t="n">
-        <v>5.796</v>
+        <v>6.2076</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0925</v>
+        <v>0.1049</v>
       </c>
       <c r="J44" t="n">
-        <v>2.59</v>
+        <v>2.9372</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0203</v>
+        <v>0.0273</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5684</v>
+        <v>0.7644</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1954</v>
+        <v>-0.2073</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.4712</v>
+        <v>-5.8044</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3666</v>
+        <v>0.388</v>
       </c>
       <c r="J47" t="n">
-        <v>10.2648</v>
+        <v>10.864</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1073</v>
+        <v>-0.1203</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.0044</v>
+        <v>-3.3684</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1296</v>
+        <v>-0.1434</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.6288</v>
+        <v>-4.0152</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1514</v>
+        <v>-0.1656</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.2392</v>
+        <v>-4.6368</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.86</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1726</v>
+        <v>-0.1871</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.8328</v>
+        <v>-5.2388</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3097</v>
+        <v>0.308</v>
       </c>
       <c r="J52" t="n">
-        <v>8.052199999999999</v>
+        <v>8.007999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.11</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2895</v>
+        <v>0.2886</v>
       </c>
       <c r="J53" t="n">
-        <v>7.527</v>
+        <v>7.5036</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.204</v>
+        <v>0.2064</v>
       </c>
       <c r="J54" t="n">
-        <v>5.304</v>
+        <v>5.3664</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3367</v>
+        <v>-0.3498</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.754200000000001</v>
+        <v>-9.094799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3931</v>
+        <v>-0.404</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.2206</v>
+        <v>-10.504</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8385</v>
+        <v>0.9238</v>
       </c>
       <c r="J57" t="n">
-        <v>21.801</v>
+        <v>24.0188</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5699</v>
+        <v>0.6311</v>
       </c>
       <c r="J58" t="n">
-        <v>14.8174</v>
+        <v>16.4086</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3345</v>
+        <v>0.3419</v>
       </c>
       <c r="J59" t="n">
-        <v>8.696999999999999</v>
+        <v>8.8894</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.094</v>
+        <v>0.1108</v>
       </c>
       <c r="J60" t="n">
-        <v>2.444</v>
+        <v>2.8808</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.93</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3042</v>
+        <v>-0.2903</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.9092</v>
+        <v>-7.5478</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>0.155</v>
+        <v>0.1529</v>
       </c>
       <c r="J62" t="n">
-        <v>3.565</v>
+        <v>3.5167</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1294</v>
+        <v>0.1273</v>
       </c>
       <c r="J63" t="n">
-        <v>2.9762</v>
+        <v>2.9279</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.86</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1625</v>
+        <v>-0.1794</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.7375</v>
+        <v>-4.1262</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3</v>
+        <v>-0.3157</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.9</v>
+        <v>-7.2611</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3571</v>
+        <v>-0.3709</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.2133</v>
+        <v>-8.5307</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0039</v>
+        <v>1.1073</v>
       </c>
       <c r="J67" t="n">
-        <v>23.0897</v>
+        <v>25.4679</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7569</v>
+        <v>0.8417</v>
       </c>
       <c r="J68" t="n">
-        <v>17.4087</v>
+        <v>19.3591</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.3</v>
       </c>
       <c r="I69" t="n">
-        <v>0.592</v>
+        <v>0.6601</v>
       </c>
       <c r="J69" t="n">
-        <v>13.616</v>
+        <v>15.1823</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>1.27</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5526</v>
+        <v>0.6162</v>
       </c>
       <c r="J70" t="n">
-        <v>12.7098</v>
+        <v>14.1726</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3705</v>
+        <v>-0.3439</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.5215</v>
+        <v>-7.9097</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>2.06</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4859</v>
+        <v>1.6171</v>
       </c>
       <c r="J72" t="n">
-        <v>28.2321</v>
+        <v>30.7249</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5302</v>
+        <v>0.5935</v>
       </c>
       <c r="J73" t="n">
-        <v>10.0738</v>
+        <v>11.2765</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5164</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>9.8116</v>
+        <v>10.9839</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4742</v>
+        <v>0.5309</v>
       </c>
       <c r="J75" t="n">
-        <v>9.0098</v>
+        <v>10.0871</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3549</v>
+        <v>0.381</v>
       </c>
       <c r="J76" t="n">
-        <v>6.7431</v>
+        <v>7.239</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>0.93</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0374</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.7106</v>
+        <v>-1.1913</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>0.75</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2432</v>
+        <v>-0.2661</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.6208</v>
+        <v>-5.0559</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.58</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4015</v>
+        <v>-0.4185</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.6285</v>
+        <v>-7.9515</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.55</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4295</v>
+        <v>-0.445</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.160500000000001</v>
+        <v>-8.455</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.5</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4764</v>
+        <v>-0.489</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.051600000000001</v>
+        <v>-9.291</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.02</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0593</v>
+        <v>0.0639</v>
       </c>
       <c r="J82" t="n">
-        <v>2.0162</v>
+        <v>2.1726</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0073</v>
+        <v>0.0053</v>
       </c>
       <c r="J83" t="n">
-        <v>0.2482</v>
+        <v>0.1802</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.8254</v>
+        <v>-3.2368</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.8254</v>
+        <v>-3.2368</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2122</v>
+        <v>-0.2272</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.2148</v>
+        <v>-7.7248</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.34</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4091</v>
+        <v>0.4611</v>
       </c>
       <c r="J87" t="n">
-        <v>13.9094</v>
+        <v>15.6774</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2278</v>
+        <v>0.2438</v>
       </c>
       <c r="J88" t="n">
-        <v>7.7452</v>
+        <v>8.289199999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1335</v>
+        <v>0.1486</v>
       </c>
       <c r="J89" t="n">
-        <v>4.539</v>
+        <v>5.0524</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0353</v>
+        <v>0.0458</v>
       </c>
       <c r="J90" t="n">
-        <v>1.2002</v>
+        <v>1.5572</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.96</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0745</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.533</v>
+        <v>-2.7608</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5696</v>
+        <v>0.6308</v>
       </c>
       <c r="J92" t="n">
-        <v>15.3792</v>
+        <v>17.0316</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.19</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4565</v>
+        <v>0.5042</v>
       </c>
       <c r="J93" t="n">
-        <v>12.3255</v>
+        <v>13.6134</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4277</v>
+        <v>0.4715</v>
       </c>
       <c r="J94" t="n">
-        <v>11.5479</v>
+        <v>12.7305</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.15</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3988</v>
+        <v>0.4355</v>
       </c>
       <c r="J95" t="n">
-        <v>10.7676</v>
+        <v>11.7585</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>1.04</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1282</v>
+        <v>0.144</v>
       </c>
       <c r="J96" t="n">
-        <v>3.4614</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.2</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4283</v>
+        <v>0.4648</v>
       </c>
       <c r="J97" t="n">
-        <v>11.5641</v>
+        <v>12.5496</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.032</v>
+        <v>0.0231</v>
       </c>
       <c r="J98" t="n">
-        <v>0.864</v>
+        <v>0.6237</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.97</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.035</v>
+        <v>-0.0467</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.945</v>
+        <v>-1.2609</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.61</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4042</v>
+        <v>-0.4159</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.9134</v>
+        <v>-11.2293</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.54</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4688</v>
+        <v>-0.4774</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.6576</v>
+        <v>-12.8898</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.02</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0867</v>
+        <v>0.0948</v>
       </c>
       <c r="J102" t="n">
-        <v>2.2542</v>
+        <v>2.4648</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>-1.0784</v>
+        <v>-0.9841</v>
       </c>
       <c r="J103" t="n">
-        <v>-28.0384</v>
+        <v>-25.5866</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.41</v>
       </c>
       <c r="I104" t="n">
-        <v>-1.5637</v>
+        <v>-1.3964</v>
       </c>
       <c r="J104" t="n">
-        <v>-40.6562</v>
+        <v>-36.3064</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.61</v>
       </c>
       <c r="I105" t="n">
-        <v>1.0627</v>
+        <v>1.1551</v>
       </c>
       <c r="J105" t="n">
-        <v>27.6302</v>
+        <v>30.0326</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>1.54</v>
       </c>
       <c r="I106" t="n">
-        <v>0.97</v>
+        <v>1.0571</v>
       </c>
       <c r="J106" t="n">
-        <v>25.22</v>
+        <v>27.4846</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.13</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3066</v>
+        <v>0.31</v>
       </c>
       <c r="J107" t="n">
-        <v>7.9716</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0757</v>
+        <v>-0.0859</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.9682</v>
+        <v>-2.2334</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2977</v>
+        <v>-0.3102</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.7402</v>
+        <v>-8.065200000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3066</v>
+        <v>0.31</v>
       </c>
       <c r="J110" t="n">
-        <v>7.9716</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>1.04</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1164</v>
+        <v>0.1249</v>
       </c>
       <c r="J111" t="n">
-        <v>3.0264</v>
+        <v>3.2474</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>0.85</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1768</v>
+        <v>-0.1928</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.304</v>
+        <v>-5.784</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1768</v>
+        <v>-0.1928</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.304</v>
+        <v>-5.784</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>0.58</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4369</v>
+        <v>-0.4463</v>
       </c>
       <c r="J114" t="n">
-        <v>-13.107</v>
+        <v>-13.389</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3513</v>
+        <v>0.3606</v>
       </c>
       <c r="J115" t="n">
-        <v>10.539</v>
+        <v>10.818</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>1.04</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1075</v>
+        <v>0.1114</v>
       </c>
       <c r="J116" t="n">
-        <v>3.225</v>
+        <v>3.342</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3177</v>
+        <v>0.3351</v>
       </c>
       <c r="J117" t="n">
-        <v>9.531000000000001</v>
+        <v>10.053</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2948</v>
+        <v>0.3117</v>
       </c>
       <c r="J118" t="n">
-        <v>8.843999999999999</v>
+        <v>9.351000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.278</v>
+        <v>-0.2871</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.34</v>
+        <v>-8.613</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>1.43</v>
       </c>
       <c r="I120" t="n">
-        <v>0.461</v>
+        <v>0.5248</v>
       </c>
       <c r="J120" t="n">
-        <v>13.83</v>
+        <v>15.744</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>1.27</v>
       </c>
       <c r="I121" t="n">
-        <v>0.353</v>
+        <v>0.3811</v>
       </c>
       <c r="J121" t="n">
-        <v>10.59</v>
+        <v>11.433</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8975</v>
+        <v>0.9929</v>
       </c>
       <c r="J122" t="n">
-        <v>22.4375</v>
+        <v>24.8225</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4999</v>
+        <v>0.5568</v>
       </c>
       <c r="J123" t="n">
-        <v>12.4975</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.62</v>
       </c>
       <c r="I124" t="n">
-        <v>-1.1322</v>
+        <v>-1.0222</v>
       </c>
       <c r="J124" t="n">
-        <v>-28.305</v>
+        <v>-25.555</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.62</v>
       </c>
       <c r="I125" t="n">
-        <v>0.9958</v>
+        <v>1.098</v>
       </c>
       <c r="J125" t="n">
-        <v>24.895</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>1.45</v>
       </c>
       <c r="I126" t="n">
-        <v>0.785</v>
+        <v>0.8716</v>
       </c>
       <c r="J126" t="n">
-        <v>19.625</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.31</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4916</v>
+        <v>0.5497</v>
       </c>
       <c r="J127" t="n">
-        <v>12.29</v>
+        <v>13.7425</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.29</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4718</v>
+        <v>0.527</v>
       </c>
       <c r="J128" t="n">
-        <v>11.795</v>
+        <v>13.175</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1337</v>
+        <v>-0.1437</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.3425</v>
+        <v>-3.5925</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>1.06</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1472</v>
+        <v>0.1598</v>
       </c>
       <c r="J130" t="n">
-        <v>3.68</v>
+        <v>3.995</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1222</v>
+        <v>-0.1318</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.055</v>
+        <v>-3.295</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.786</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>23.58</v>
+        <v>22.302</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6429</v>
+        <v>0.617</v>
       </c>
       <c r="J133" t="n">
-        <v>19.287</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J134" t="n">
-        <v>8.583</v>
+        <v>8.766</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2572</v>
+        <v>0.2652</v>
       </c>
       <c r="J135" t="n">
-        <v>7.716</v>
+        <v>7.956</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1651</v>
+        <v>0.1784</v>
       </c>
       <c r="J136" t="n">
-        <v>4.953</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4435</v>
+        <v>0.4337</v>
       </c>
       <c r="J137" t="n">
-        <v>13.305</v>
+        <v>13.011</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.04</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1315</v>
+        <v>0.1358</v>
       </c>
       <c r="J138" t="n">
-        <v>3.945</v>
+        <v>4.074</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.03</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1066</v>
+        <v>0.1106</v>
       </c>
       <c r="J139" t="n">
-        <v>3.198</v>
+        <v>3.318</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.88</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1487</v>
+        <v>-0.1636</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.461</v>
+        <v>-4.908</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.53</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4859</v>
+        <v>-0.4923</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.577</v>
+        <v>-14.769</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>1.141</v>
+        <v>1.1038</v>
       </c>
       <c r="J142" t="n">
-        <v>28.525</v>
+        <v>27.595</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>1.34</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8843</v>
+        <v>0.8326</v>
       </c>
       <c r="J143" t="n">
-        <v>22.1075</v>
+        <v>20.815</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>1.3</v>
       </c>
       <c r="I144" t="n">
-        <v>0.793</v>
+        <v>0.7526</v>
       </c>
       <c r="J144" t="n">
-        <v>19.825</v>
+        <v>18.815</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0491</v>
+        <v>-0.0339</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.2275</v>
+        <v>-0.8475</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4889</v>
+        <v>-0.458</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.2225</v>
+        <v>-11.45</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9153</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>22.8825</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5766</v>
+        <v>0.552</v>
       </c>
       <c r="J148" t="n">
-        <v>14.415</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>0.62</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3979</v>
+        <v>-0.4095</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.9475</v>
+        <v>-10.2375</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>0.59</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4258</v>
+        <v>-0.436</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.645</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4717</v>
+        <v>-0.4796</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.7925</v>
+        <v>-11.99</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1052</v>
+        <v>-0.1187</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.7352</v>
+        <v>-3.0862</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1382</v>
+        <v>-0.1528</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.5932</v>
+        <v>-3.9728</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.54</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4771</v>
+        <v>-0.4839</v>
       </c>
       <c r="J154" t="n">
-        <v>-12.4046</v>
+        <v>-12.5814</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4427</v>
+        <v>0.4331</v>
       </c>
       <c r="J155" t="n">
-        <v>11.5102</v>
+        <v>11.2606</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>1.14</v>
       </c>
       <c r="I156" t="n">
-        <v>0.346</v>
+        <v>0.3428</v>
       </c>
       <c r="J156" t="n">
-        <v>8.996</v>
+        <v>8.912800000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8601</v>
+        <v>0.8035</v>
       </c>
       <c r="J157" t="n">
-        <v>22.3626</v>
+        <v>20.891</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>0.63</v>
       </c>
       <c r="I158" t="n">
-        <v>-1.0641</v>
+        <v>-0.9704</v>
       </c>
       <c r="J158" t="n">
-        <v>-27.6666</v>
+        <v>-25.2304</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.54</v>
       </c>
       <c r="I159" t="n">
-        <v>-1.275</v>
+        <v>-1.151</v>
       </c>
       <c r="J159" t="n">
-        <v>-33.15</v>
+        <v>-29.926</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.77</v>
       </c>
       <c r="I160" t="n">
-        <v>1.5261</v>
+        <v>1.5042</v>
       </c>
       <c r="J160" t="n">
-        <v>39.6786</v>
+        <v>39.1092</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>1.14</v>
       </c>
       <c r="I161" t="n">
-        <v>0.435</v>
+        <v>0.4261</v>
       </c>
       <c r="J161" t="n">
-        <v>11.31</v>
+        <v>11.0786</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1568</v>
+        <v>0.1737</v>
       </c>
       <c r="J162" t="n">
-        <v>3.7632</v>
+        <v>4.1688</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0706</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.5864</v>
+        <v>-1.6944</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1624</v>
+        <v>-0.1716</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.8976</v>
+        <v>-4.1184</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.44</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5656</v>
+        <v>0.5695</v>
       </c>
       <c r="J165" t="n">
-        <v>13.5744</v>
+        <v>13.668</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.4</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5204</v>
+        <v>0.5271</v>
       </c>
       <c r="J166" t="n">
-        <v>12.4896</v>
+        <v>12.6504</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.17</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2857</v>
+        <v>0.2936</v>
       </c>
       <c r="J167" t="n">
-        <v>6.8568</v>
+        <v>7.0464</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.06</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1189</v>
+        <v>0.1297</v>
       </c>
       <c r="J168" t="n">
-        <v>2.8536</v>
+        <v>3.1128</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.74</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3018</v>
+        <v>-0.3134</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.2432</v>
+        <v>-7.5216</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1826</v>
+        <v>0.1934</v>
       </c>
       <c r="J170" t="n">
-        <v>4.3824</v>
+        <v>4.6416</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>1.1</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1826</v>
+        <v>0.1934</v>
       </c>
       <c r="J171" t="n">
-        <v>4.3824</v>
+        <v>4.6416</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>0.88</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1253</v>
+        <v>-0.1456</v>
       </c>
       <c r="J172" t="n">
-        <v>-3.759</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>0.34</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.6387</v>
+        <v>-0.638</v>
       </c>
       <c r="J173" t="n">
-        <v>-19.161</v>
+        <v>-19.14</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.27</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.7026</v>
+        <v>-0.6969</v>
       </c>
       <c r="J174" t="n">
-        <v>-21.078</v>
+        <v>-20.907</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.9084</v>
+        <v>0.836</v>
       </c>
       <c r="J175" t="n">
-        <v>27.252</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.1102</v>
       </c>
       <c r="J176" t="n">
-        <v>-2.709</v>
+        <v>-3.306</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>0.65</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.9403</v>
+        <v>-0.8756</v>
       </c>
       <c r="J177" t="n">
-        <v>-28.209</v>
+        <v>-26.268</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.58</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.1103</v>
+        <v>-1.0209</v>
       </c>
       <c r="J178" t="n">
-        <v>-33.309</v>
+        <v>-30.627</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.47</v>
       </c>
       <c r="I179" t="n">
-        <v>-1.3733</v>
+        <v>-1.2431</v>
       </c>
       <c r="J179" t="n">
-        <v>-41.199</v>
+        <v>-37.293</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>1.24</v>
       </c>
       <c r="I180" t="n">
-        <v>0.8364</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>25.092</v>
+        <v>22.728</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>1.2</v>
       </c>
       <c r="I181" t="n">
-        <v>0.7266</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>21.798</v>
+        <v>19.854</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.58</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7254</v>
+        <v>0.7173</v>
       </c>
       <c r="J182" t="n">
-        <v>21.762</v>
+        <v>21.519</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.21</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2999</v>
+        <v>0.3155</v>
       </c>
       <c r="J183" t="n">
-        <v>8.997</v>
+        <v>9.465</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1995</v>
+        <v>0.2161</v>
       </c>
       <c r="J184" t="n">
-        <v>5.985</v>
+        <v>6.483</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1604</v>
+        <v>-0.17</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.812</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1604</v>
+        <v>-0.17</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.812</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4013</v>
+        <v>0.3998</v>
       </c>
       <c r="J187" t="n">
-        <v>12.039</v>
+        <v>11.994</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3164</v>
+        <v>0.3195</v>
       </c>
       <c r="J188" t="n">
-        <v>9.492000000000001</v>
+        <v>9.585000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.0963</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.538</v>
+        <v>-2.889</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.86</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1733</v>
+        <v>-0.1877</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.199</v>
+        <v>-5.631</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.6</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4254</v>
+        <v>-0.4342</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.762</v>
+        <v>-13.026</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>0.79</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.2061</v>
+        <v>-0.2291</v>
       </c>
       <c r="J192" t="n">
-        <v>-4.3281</v>
+        <v>-4.8111</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.74</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.257</v>
+        <v>-0.2787</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.397</v>
+        <v>-5.8527</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.66</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3307</v>
+        <v>-0.3504</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.9447</v>
+        <v>-7.3584</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.62</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3673</v>
+        <v>-0.3856</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.7133</v>
+        <v>-8.0976</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3952</v>
+        <v>-0.4121</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.299200000000001</v>
+        <v>-8.6541</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3712</v>
+        <v>1.3586</v>
       </c>
       <c r="J197" t="n">
-        <v>28.7952</v>
+        <v>28.5306</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.56</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1716</v>
+        <v>1.1454</v>
       </c>
       <c r="J198" t="n">
-        <v>24.6036</v>
+        <v>24.0534</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.52</v>
       </c>
       <c r="I199" t="n">
-        <v>1.124</v>
+        <v>1.0939</v>
       </c>
       <c r="J199" t="n">
-        <v>23.604</v>
+        <v>22.9719</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.47</v>
       </c>
       <c r="I200" t="n">
-        <v>1.0642</v>
+        <v>1.0263</v>
       </c>
       <c r="J200" t="n">
-        <v>22.3482</v>
+        <v>21.5523</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.511</v>
+        <v>-0.4679</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.731</v>
+        <v>-9.825900000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0354</v>
+        <v>0.0256</v>
       </c>
       <c r="J202" t="n">
-        <v>0.885</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.8225</v>
+        <v>-2.185</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1197</v>
+        <v>-0.1359</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.9925</v>
+        <v>-3.3975</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1816</v>
+        <v>-0.199</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.54</v>
+        <v>-4.975</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.59</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4214</v>
+        <v>-0.4326</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.535</v>
+        <v>-10.815</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.73</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4189</v>
+        <v>1.4008</v>
       </c>
       <c r="J207" t="n">
-        <v>35.4725</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.5</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1335</v>
+        <v>1.0972</v>
       </c>
       <c r="J208" t="n">
-        <v>28.3375</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2067</v>
+        <v>0.2229</v>
       </c>
       <c r="J209" t="n">
-        <v>5.1675</v>
+        <v>5.5725</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.96</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2255</v>
+        <v>-0.2113</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.6375</v>
+        <v>-5.2825</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3826</v>
+        <v>-0.359</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.565</v>
+        <v>-8.975</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.23</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4906</v>
+        <v>0.4822</v>
       </c>
       <c r="J212" t="n">
-        <v>13.7368</v>
+        <v>13.5016</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.04</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1146</v>
+        <v>0.1236</v>
       </c>
       <c r="J213" t="n">
-        <v>3.2088</v>
+        <v>3.4608</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>1.02</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0649</v>
+        <v>0.0726</v>
       </c>
       <c r="J214" t="n">
-        <v>1.8172</v>
+        <v>2.0328</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0367</v>
+        <v>-0.0432</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.0276</v>
+        <v>-1.2096</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2697</v>
+        <v>-0.2825</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.5516</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5108</v>
+        <v>1.4886</v>
       </c>
       <c r="J217" t="n">
-        <v>42.3024</v>
+        <v>41.6808</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5629</v>
+        <v>0.5419</v>
       </c>
       <c r="J218" t="n">
-        <v>15.7612</v>
+        <v>15.1732</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4016</v>
+        <v>-0.385</v>
       </c>
       <c r="J219" t="n">
-        <v>-11.2448</v>
+        <v>-10.78</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.88</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4299</v>
+        <v>-0.4109</v>
       </c>
       <c r="J220" t="n">
-        <v>-12.0372</v>
+        <v>-11.5052</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8969</v>
+        <v>-0.8254</v>
       </c>
       <c r="J221" t="n">
-        <v>-25.1132</v>
+        <v>-23.1112</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>0.58</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.3352</v>
+        <v>-0.367</v>
       </c>
       <c r="J222" t="n">
-        <v>-5.6984</v>
+        <v>-6.239</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.42</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.5018</v>
+        <v>-0.5203</v>
       </c>
       <c r="J223" t="n">
-        <v>-8.5306</v>
+        <v>-8.8451</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.41</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5102</v>
+        <v>-0.5281</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.673400000000001</v>
+        <v>-8.9777</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.34</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5778</v>
+        <v>-0.59</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.8226</v>
+        <v>-10.03</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.34</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5778</v>
+        <v>-0.59</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.8226</v>
+        <v>-10.03</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>2.23</v>
       </c>
       <c r="I227" t="n">
-        <v>1.8338</v>
+        <v>1.8928</v>
       </c>
       <c r="J227" t="n">
-        <v>31.1746</v>
+        <v>32.1776</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>2.06</v>
       </c>
       <c r="I228" t="n">
-        <v>1.693</v>
+        <v>1.7053</v>
       </c>
       <c r="J228" t="n">
-        <v>28.781</v>
+        <v>28.9901</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.56</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1482</v>
+        <v>1.1253</v>
       </c>
       <c r="J229" t="n">
-        <v>19.5194</v>
+        <v>19.1301</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>1.43</v>
       </c>
       <c r="I230" t="n">
-        <v>0.9786</v>
+        <v>0.9375</v>
       </c>
       <c r="J230" t="n">
-        <v>16.6362</v>
+        <v>15.9375</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>1.13</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2852</v>
+        <v>0.3162</v>
       </c>
       <c r="J231" t="n">
-        <v>4.8484</v>
+        <v>5.3754</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.12</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2782</v>
+        <v>0.2849</v>
       </c>
       <c r="J232" t="n">
-        <v>9.737</v>
+        <v>9.971500000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.03</v>
       </c>
       <c r="I233" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0969</v>
       </c>
       <c r="J233" t="n">
-        <v>3.059</v>
+        <v>3.3915</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.16</v>
+        <v>-0.1723</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.6</v>
+        <v>-6.0305</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.16</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3547</v>
+        <v>0.3573</v>
       </c>
       <c r="J235" t="n">
-        <v>12.4145</v>
+        <v>12.5055</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.98</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0391</v>
+        <v>-0.0451</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.3685</v>
+        <v>-1.5785</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>0.0308</v>
+        <v>0.0433</v>
       </c>
       <c r="J237" t="n">
-        <v>1.078</v>
+        <v>1.5155</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>0.91</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3491</v>
+        <v>-0.3355</v>
       </c>
       <c r="J238" t="n">
-        <v>-12.2185</v>
+        <v>-11.7425</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.6248</v>
+        <v>-0.5851</v>
       </c>
       <c r="J239" t="n">
-        <v>-21.868</v>
+        <v>-20.4785</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.4</v>
       </c>
       <c r="I240" t="n">
-        <v>1.0329</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>36.1515</v>
+        <v>34.1005</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>1.39</v>
       </c>
       <c r="I241" t="n">
-        <v>1.017</v>
+        <v>0.956</v>
       </c>
       <c r="J241" t="n">
-        <v>35.595</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2958</v>
+        <v>0.302</v>
       </c>
       <c r="J242" t="n">
-        <v>7.9866</v>
+        <v>8.154</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1542</v>
+        <v>0.1647</v>
       </c>
       <c r="J243" t="n">
-        <v>4.1634</v>
+        <v>4.4469</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.84</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2031</v>
+        <v>-0.2156</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.4837</v>
+        <v>-5.8212</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.21</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4442</v>
+        <v>0.4413</v>
       </c>
       <c r="J245" t="n">
-        <v>11.9934</v>
+        <v>11.9151</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.97</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.0541</v>
+        <v>-0.0613</v>
       </c>
       <c r="J246" t="n">
-        <v>-1.4607</v>
+        <v>-1.6551</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>0.83</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.5262</v>
+        <v>-0.506</v>
       </c>
       <c r="J247" t="n">
-        <v>-14.2074</v>
+        <v>-13.662</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>0.77</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.6823</v>
+        <v>-0.6444</v>
       </c>
       <c r="J248" t="n">
-        <v>-18.4221</v>
+        <v>-17.3988</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-1.1247</v>
+        <v>-1.0276</v>
       </c>
       <c r="J249" t="n">
-        <v>-30.3669</v>
+        <v>-27.7452</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.8539</v>
+        <v>0.7869</v>
       </c>
       <c r="J250" t="n">
-        <v>23.0553</v>
+        <v>21.2463</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>1.27</v>
       </c>
       <c r="I251" t="n">
-        <v>0.8286</v>
+        <v>0.7648</v>
       </c>
       <c r="J251" t="n">
-        <v>22.3722</v>
+        <v>20.6496</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.2</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4569</v>
+        <v>0.4471</v>
       </c>
       <c r="J252" t="n">
-        <v>12.3363</v>
+        <v>12.0717</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0086</v>
+        <v>0.0061</v>
       </c>
       <c r="J253" t="n">
-        <v>0.2322</v>
+        <v>0.1647</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.91</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1175</v>
+        <v>-0.1312</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.1725</v>
+        <v>-3.5424</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.84</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1922</v>
+        <v>-0.2071</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.1894</v>
+        <v>-5.5917</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.79</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2428</v>
+        <v>-0.2574</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.5556</v>
+        <v>-6.9498</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.26</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7362</v>
+        <v>0.6957</v>
       </c>
       <c r="J257" t="n">
-        <v>19.8774</v>
+        <v>18.7839</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.24</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6872</v>
+        <v>0.6525</v>
       </c>
       <c r="J258" t="n">
-        <v>18.5544</v>
+        <v>17.6175</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.12</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3795</v>
+        <v>0.3759</v>
       </c>
       <c r="J259" t="n">
-        <v>10.2465</v>
+        <v>10.1493</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.92</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3143</v>
+        <v>-0.3044</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.4861</v>
+        <v>-8.2188</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.89</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4021</v>
+        <v>-0.3854</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.8567</v>
+        <v>-10.4058</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8833</v>
+        <v>0.8598</v>
       </c>
       <c r="J262" t="n">
-        <v>22.0825</v>
+        <v>21.495</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>0.99</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0287</v>
+        <v>-0.0315</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.7175</v>
+        <v>-0.7875</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>0.95</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0931</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.125</v>
+        <v>-2.3275</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0974</v>
+        <v>-0.1062</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.435</v>
+        <v>-2.655</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1978</v>
+        <v>-0.2091</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.945</v>
+        <v>-5.2275</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3667</v>
+        <v>0.3685</v>
       </c>
       <c r="J267" t="n">
-        <v>9.1675</v>
+        <v>9.2125</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3245</v>
+        <v>0.3285</v>
       </c>
       <c r="J268" t="n">
-        <v>8.112500000000001</v>
+        <v>8.2125</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0351</v>
+        <v>-0.042</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.049</v>
+        <v>-0.0574</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.225</v>
+        <v>-1.435</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4462</v>
+        <v>-0.4537</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.155</v>
+        <v>-11.3425</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>0.98</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0275</v>
+        <v>-0.0362</v>
       </c>
       <c r="J272" t="n">
-        <v>-1.1275</v>
+        <v>-1.4842</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>0.97</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0419</v>
+        <v>-0.052</v>
       </c>
       <c r="J273" t="n">
-        <v>-1.7179</v>
+        <v>-2.132</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>0.91</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1143</v>
+        <v>-0.1288</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.6863</v>
+        <v>-5.2808</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1356</v>
+        <v>-0.1508</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.5596</v>
+        <v>-6.1828</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.8</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2281</v>
+        <v>-0.2439</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.3521</v>
+        <v>-9.9999</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.56</v>
       </c>
       <c r="I277" t="n">
-        <v>1.2382</v>
+        <v>1.204</v>
       </c>
       <c r="J277" t="n">
-        <v>50.7662</v>
+        <v>49.364</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>1.17</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4995</v>
+        <v>0.4875</v>
       </c>
       <c r="J278" t="n">
-        <v>20.4795</v>
+        <v>19.9875</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>1.06</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2011</v>
+        <v>0.2114</v>
       </c>
       <c r="J279" t="n">
-        <v>8.245100000000001</v>
+        <v>8.667400000000001</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0856</v>
+        <v>-0.0808</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.5096</v>
+        <v>-3.3128</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.87</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4704</v>
+        <v>-0.4451</v>
       </c>
       <c r="J281" t="n">
-        <v>-19.2864</v>
+        <v>-18.2491</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3857</v>
+        <v>0.3828</v>
       </c>
       <c r="J282" t="n">
-        <v>10.0282</v>
+        <v>9.9528</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.92</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1043</v>
+        <v>-0.118</v>
       </c>
       <c r="J283" t="n">
-        <v>-2.7118</v>
+        <v>-3.068</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.87</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1582</v>
+        <v>-0.1735</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.1132</v>
+        <v>-4.511</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1894</v>
+        <v>-0.2049</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.9244</v>
+        <v>-5.3274</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2596</v>
+        <v>-0.2746</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.7496</v>
+        <v>-7.1396</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.47</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5978</v>
+        <v>0.5999</v>
       </c>
       <c r="J287" t="n">
-        <v>15.5428</v>
+        <v>15.5974</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.4</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5193</v>
+        <v>0.5262</v>
       </c>
       <c r="J288" t="n">
-        <v>13.5018</v>
+        <v>13.6812</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1561</v>
+        <v>0.1732</v>
       </c>
       <c r="J289" t="n">
-        <v>4.0586</v>
+        <v>4.5032</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.093</v>
+        <v>-0.0993</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.418</v>
+        <v>-2.5818</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1407</v>
+        <v>-0.1491</v>
       </c>
       <c r="J291" t="n">
-        <v>-3.6582</v>
+        <v>-3.8766</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0514</v>
+        <v>0.9893</v>
       </c>
       <c r="J292" t="n">
-        <v>37.8504</v>
+        <v>35.6148</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3178</v>
+        <v>0.3138</v>
       </c>
       <c r="J293" t="n">
-        <v>11.4408</v>
+        <v>11.2968</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.91</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3215</v>
+        <v>-0.3163</v>
       </c>
       <c r="J294" t="n">
-        <v>-11.574</v>
+        <v>-11.3868</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4354</v>
+        <v>-0.4206</v>
       </c>
       <c r="J295" t="n">
-        <v>-15.6744</v>
+        <v>-15.1416</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.77</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7002</v>
+        <v>-0.657</v>
       </c>
       <c r="J296" t="n">
-        <v>-25.2072</v>
+        <v>-23.652</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.52</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9285</v>
+        <v>0.8858</v>
       </c>
       <c r="J297" t="n">
-        <v>33.426</v>
+        <v>31.8888</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.21</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4231</v>
+        <v>0.426</v>
       </c>
       <c r="J298" t="n">
-        <v>15.2316</v>
+        <v>15.336</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.14</v>
       </c>
       <c r="I299" t="n">
-        <v>0.299</v>
+        <v>0.3087</v>
       </c>
       <c r="J299" t="n">
-        <v>10.764</v>
+        <v>11.1132</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0118</v>
+        <v>-0.0091</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.4248</v>
+        <v>-0.3276</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2729</v>
+        <v>-0.283</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.824400000000001</v>
+        <v>-10.188</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.88</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5308</v>
+        <v>1.5293</v>
       </c>
       <c r="J302" t="n">
-        <v>30.616</v>
+        <v>30.586</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.71</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3377</v>
+        <v>1.3249</v>
       </c>
       <c r="J303" t="n">
-        <v>26.754</v>
+        <v>26.498</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.37</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8928</v>
+        <v>0.851</v>
       </c>
       <c r="J304" t="n">
-        <v>17.856</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.32</v>
       </c>
       <c r="I305" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7544</v>
       </c>
       <c r="J305" t="n">
-        <v>15.656</v>
+        <v>15.088</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.18</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4508</v>
+        <v>0.4592</v>
       </c>
       <c r="J306" t="n">
-        <v>9.016</v>
+        <v>9.183999999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>0.99</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1762</v>
+        <v>0.1142</v>
       </c>
       <c r="J307" t="n">
-        <v>3.524</v>
+        <v>2.284</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.64</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.332</v>
+        <v>-0.355</v>
       </c>
       <c r="J308" t="n">
-        <v>-6.64</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.48</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4786</v>
+        <v>-0.4937</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.571999999999999</v>
+        <v>-9.874000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.47</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4881</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.762</v>
+        <v>-10.05</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.29</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6617</v>
+        <v>-0.6622</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.234</v>
+        <v>-13.244</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.62</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7532</v>
+        <v>0.7453</v>
       </c>
       <c r="J312" t="n">
-        <v>19.5832</v>
+        <v>19.3778</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.22</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3053</v>
+        <v>0.3223</v>
       </c>
       <c r="J313" t="n">
-        <v>7.9378</v>
+        <v>8.379799999999999</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2577</v>
+        <v>0.2754</v>
       </c>
       <c r="J314" t="n">
-        <v>6.7002</v>
+        <v>7.1604</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.02</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0238</v>
+        <v>0.0371</v>
       </c>
       <c r="J315" t="n">
-        <v>0.6188</v>
+        <v>0.9646</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0835</v>
+        <v>-0.0882</v>
       </c>
       <c r="J316" t="n">
-        <v>-2.171</v>
+        <v>-2.2932</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.15</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2782</v>
+        <v>0.2818</v>
       </c>
       <c r="J317" t="n">
-        <v>7.2332</v>
+        <v>7.3268</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0076</v>
+        <v>0.0056</v>
       </c>
       <c r="J318" t="n">
-        <v>0.1976</v>
+        <v>0.1456</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.7508</v>
+        <v>-3.0966</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.86</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1707</v>
+        <v>-0.1857</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.4382</v>
+        <v>-4.8282</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.78</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.252</v>
+        <v>-0.2666</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.552</v>
+        <v>-6.9316</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.1</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3169</v>
+        <v>0.3041</v>
       </c>
       <c r="J322" t="n">
-        <v>7.6056</v>
+        <v>7.2984</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>0.92</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.0896</v>
+        <v>-0.1067</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.1504</v>
+        <v>-2.5608</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>0.84</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1777</v>
+        <v>-0.196</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.2648</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>0.68</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3309</v>
+        <v>-0.347</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.9416</v>
+        <v>-8.327999999999999</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>0.51</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4895</v>
+        <v>-0.498</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.748</v>
+        <v>-11.952</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.43</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0447</v>
+        <v>0.9953</v>
       </c>
       <c r="J327" t="n">
-        <v>25.0728</v>
+        <v>23.8872</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.37</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9422</v>
+        <v>0.8863</v>
       </c>
       <c r="J328" t="n">
-        <v>22.6128</v>
+        <v>21.2712</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>1.35</v>
       </c>
       <c r="I329" t="n">
-        <v>0.8996</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J329" t="n">
-        <v>21.5904</v>
+        <v>20.3352</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>1.16</v>
       </c>
       <c r="I330" t="n">
-        <v>0.4573</v>
+        <v>0.4531</v>
       </c>
       <c r="J330" t="n">
-        <v>10.9752</v>
+        <v>10.8744</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.82</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6292</v>
+        <v>-0.5833</v>
       </c>
       <c r="J331" t="n">
-        <v>-15.1008</v>
+        <v>-13.9992</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.02</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1008</v>
+        <v>0.0985</v>
       </c>
       <c r="J332" t="n">
-        <v>2.4192</v>
+        <v>2.364</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1137</v>
       </c>
       <c r="J333" t="n">
-        <v>-2.3664</v>
+        <v>-2.7288</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>0.84</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1828</v>
+        <v>-0.1999</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.3872</v>
+        <v>-4.7976</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>0.82</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2028</v>
+        <v>-0.2199</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.8672</v>
+        <v>-5.2776</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>0.73</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2909</v>
+        <v>-0.3068</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.9816</v>
+        <v>-7.3632</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.51</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1518</v>
+        <v>1.1158</v>
       </c>
       <c r="J337" t="n">
-        <v>27.6432</v>
+        <v>26.7792</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>1.36</v>
       </c>
       <c r="I338" t="n">
-        <v>0.926</v>
+        <v>0.8703</v>
       </c>
       <c r="J338" t="n">
-        <v>22.224</v>
+        <v>20.8872</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8137</v>
+        <v>0.7712</v>
       </c>
       <c r="J339" t="n">
-        <v>19.5288</v>
+        <v>18.5088</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>1.06</v>
       </c>
       <c r="I340" t="n">
-        <v>0.1817</v>
+        <v>0.198</v>
       </c>
       <c r="J340" t="n">
-        <v>4.3608</v>
+        <v>4.752</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6516</v>
+        <v>-0.604</v>
       </c>
       <c r="J341" t="n">
-        <v>-15.6384</v>
+        <v>-14.496</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6349/event_6349_evp_summary.xlsx
+++ b/database/event/6349/event_6349_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8504</v>
+        <v>6.7655</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8173</v>
+        <v>2.7824</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4942</v>
+        <v>2.4762</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8504</v>
+        <v>6.7655</v>
       </c>
       <c r="F2" t="n">
-        <v>2.615</v>
+        <v>2.5999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2354</v>
+        <v>4.1656</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9985</v>
+        <v>3.008</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2363</v>
+        <v>3.2556</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2354</v>
+        <v>4.1656</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4717</v>
+        <v>7.421200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>317</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1532</v>
+        <v>5.0253</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1193</v>
+        <v>2.0667</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7216</v>
+        <v>1.6835</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1532</v>
+        <v>5.0253</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6244</v>
+        <v>1.5934</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5288</v>
+        <v>3.4319</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6244</v>
+        <v>1.5934</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7532</v>
+        <v>1.7245</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5288</v>
+        <v>3.4319</v>
       </c>
       <c r="K3" t="n">
         <v>127</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.282</v>
+        <v>5.1564</v>
       </c>
       <c r="N3" t="n">
         <v>317</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2707</v>
+        <v>4.1869</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7564</v>
+        <v>1.7219</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3199</v>
+        <v>1.3015</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2707</v>
+        <v>4.1869</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1597</v>
+        <v>1.1764</v>
       </c>
       <c r="G4" t="n">
-        <v>3.111</v>
+        <v>3.0104</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1597</v>
+        <v>1.1764</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2517</v>
+        <v>1.2733</v>
       </c>
       <c r="J4" t="n">
-        <v>3.111</v>
+        <v>3.0104</v>
       </c>
       <c r="K4" t="n">
         <v>150</v>
@@ -621,7 +621,7 @@
         <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3627</v>
+        <v>4.283700000000001</v>
       </c>
       <c r="N4" t="n">
         <v>334</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1872</v>
+        <v>4.0554</v>
       </c>
       <c r="C5" t="n">
-        <v>1.722</v>
+        <v>1.6678</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2819</v>
+        <v>1.2416</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1872</v>
+        <v>4.0554</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2709</v>
+        <v>2.2373</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9163</v>
+        <v>1.8181</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2709</v>
+        <v>2.2373</v>
       </c>
       <c r="I5" t="n">
-        <v>2.451</v>
+        <v>2.4215</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9163</v>
+        <v>1.8181</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>190</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3673</v>
+        <v>4.2396</v>
       </c>
       <c r="N5" t="n">
         <v>317</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0055</v>
+        <v>3.9228</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6473</v>
+        <v>1.6133</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1992</v>
+        <v>1.1812</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0055</v>
+        <v>3.9228</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6679</v>
+        <v>3.5959</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3376</v>
+        <v>0.3269</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2077</v>
+        <v>7.0579</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8921</v>
+        <v>3.9628</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3376</v>
+        <v>0.3269</v>
       </c>
       <c r="K6" t="n">
         <v>158</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2297</v>
+        <v>4.2897</v>
       </c>
       <c r="N6" t="n">
         <v>217</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9272</v>
+        <v>3.859</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6151</v>
+        <v>1.5871</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1635</v>
+        <v>1.1522</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9272</v>
+        <v>3.859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3675</v>
+        <v>0.3232</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5597</v>
+        <v>3.5358</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3675</v>
+        <v>0.3232</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3966</v>
+        <v>0.3498</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5597</v>
+        <v>3.5358</v>
       </c>
       <c r="K7" t="n">
         <v>127</v>
@@ -759,7 +759,7 @@
         <v>190</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9563</v>
+        <v>3.8856</v>
       </c>
       <c r="N7" t="n">
         <v>317</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7987</v>
+        <v>3.7041</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5623</v>
+        <v>1.5233</v>
       </c>
       <c r="D8" t="n">
-        <v>1.105</v>
+        <v>1.0816</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7987</v>
+        <v>3.7041</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0914</v>
+        <v>-0.1111</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8902</v>
+        <v>3.8151</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0914</v>
+        <v>-0.1111</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0987</v>
+        <v>-0.1202</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8902</v>
+        <v>3.8151</v>
       </c>
       <c r="K8" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>264</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7915</v>
+        <v>3.6949</v>
       </c>
       <c r="N8" t="n">
         <v>414</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7695</v>
+        <v>3.6056</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5502</v>
+        <v>1.4828</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0918</v>
+        <v>1.0367</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7695</v>
+        <v>3.6056</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1063</v>
+        <v>3.0727</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6632</v>
+        <v>0.5329</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3547</v>
+        <v>5.0936</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8915</v>
+        <v>2.8599</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6632</v>
+        <v>0.5329</v>
       </c>
       <c r="K9" t="n">
         <v>148</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5547</v>
+        <v>3.3928</v>
       </c>
       <c r="N9" t="n">
         <v>225</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4359</v>
+        <v>3.3708</v>
       </c>
       <c r="C10" t="n">
-        <v>1.413</v>
+        <v>1.3863</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9399</v>
+        <v>0.9298</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4359</v>
+        <v>3.3708</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7085</v>
+        <v>3.607</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2726</v>
+        <v>-0.2362</v>
       </c>
       <c r="H10" t="n">
-        <v>7.3414</v>
+        <v>7.0996</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9643</v>
+        <v>3.9862</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2726</v>
+        <v>-0.2362</v>
       </c>
       <c r="K10" t="n">
         <v>158</v>
@@ -897,7 +897,7 @@
         <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6917</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
         <v>217</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0876</v>
+        <v>3.0985</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2698</v>
+        <v>1.2743</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7813</v>
+        <v>0.8057</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0876</v>
+        <v>3.0985</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5325</v>
+        <v>2.6378</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5551</v>
+        <v>0.4607</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4615</v>
+        <v>3.4607</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8692</v>
+        <v>1.9431</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5551</v>
+        <v>0.4607</v>
       </c>
       <c r="K11" t="n">
         <v>158</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4243</v>
+        <v>2.4038</v>
       </c>
       <c r="N11" t="n">
         <v>217</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9677</v>
+        <v>2.9923</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2205</v>
+        <v>1.2306</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7268</v>
+        <v>0.7573</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9677</v>
+        <v>2.9923</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5609</v>
+        <v>2.663</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4068</v>
+        <v>0.3293</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5551</v>
+        <v>3.5555</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9197</v>
+        <v>1.9963</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4068</v>
+        <v>0.3293</v>
       </c>
       <c r="K12" t="n">
         <v>158</v>
@@ -989,7 +989,7 @@
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3265</v>
+        <v>2.3256</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8046</v>
+        <v>2.7122</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1534</v>
+        <v>1.1154</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6525</v>
+        <v>0.6297</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8046</v>
+        <v>2.7122</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1212</v>
+        <v>3.0332</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3166</v>
+        <v>-0.321</v>
       </c>
       <c r="H13" t="n">
-        <v>5.404</v>
+        <v>4.9454</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9181</v>
+        <v>2.7767</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3166</v>
+        <v>-0.321</v>
       </c>
       <c r="K13" t="n">
         <v>148</v>
@@ -1035,7 +1035,7 @@
         <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6015</v>
+        <v>2.4557</v>
       </c>
       <c r="N13" t="n">
         <v>225</v>
@@ -1044,53 +1044,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4335</v>
+        <v>2.3359</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0008</v>
+        <v>0.9607</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4836</v>
+        <v>0.4583</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4335</v>
+        <v>2.3359</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4327</v>
+        <v>1.7747</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008</v>
+        <v>0.5612</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5994</v>
+        <v>1.7747</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7351</v>
+        <v>1.9208</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0008</v>
+        <v>0.5612</v>
       </c>
       <c r="K14" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L14" t="n">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7359</v>
+        <v>2.482</v>
       </c>
       <c r="N14" t="n">
-        <v>197</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1100,221 +1100,221 @@
         <v>0.9596</v>
       </c>
       <c r="D15" t="n">
-        <v>0.438</v>
+        <v>0.4572</v>
       </c>
       <c r="E15" t="n">
         <v>2.3334</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8133</v>
+        <v>2.373</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5201</v>
+        <v>-0.0396</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8133</v>
+        <v>2.4881</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9571</v>
+        <v>2.6228</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5201</v>
+        <v>-0.0396</v>
       </c>
       <c r="K15" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="L15" t="n">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4772</v>
+        <v>2.5832</v>
       </c>
       <c r="N15" t="n">
-        <v>329</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3091</v>
+        <v>2.1982</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9496</v>
+        <v>0.904</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4269</v>
+        <v>0.3956</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3091</v>
+        <v>2.1982</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3091</v>
+        <v>0.4925</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.7057</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3289</v>
+        <v>0.4925</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5136</v>
+        <v>0.5331</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.7057</v>
       </c>
       <c r="K16" t="n">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5136</v>
+        <v>2.2388</v>
       </c>
       <c r="N16" t="n">
-        <v>193</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2725</v>
+        <v>2.126</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9346</v>
+        <v>0.8743</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4103</v>
+        <v>0.3627</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2725</v>
+        <v>2.126</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5059</v>
+        <v>2.126</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7666</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5059</v>
+        <v>2.126</v>
       </c>
       <c r="I17" t="n">
-        <v>0.546</v>
+        <v>2.301</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7666</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L17" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3126</v>
+        <v>2.301</v>
       </c>
       <c r="N17" t="n">
-        <v>384</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5939</v>
+        <v>1.5043</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6555</v>
+        <v>0.6187</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1014</v>
+        <v>0.0795</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5939</v>
+        <v>1.5043</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5673</v>
+        <v>1.1351</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0266</v>
+        <v>0.3691</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5673</v>
+        <v>1.1351</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6281</v>
+        <v>1.2286</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0266</v>
+        <v>0.3691</v>
       </c>
       <c r="K18" t="n">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="L18" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6547</v>
+        <v>1.5977</v>
       </c>
       <c r="N18" t="n">
-        <v>307</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.504</v>
+        <v>1.3648</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6185</v>
+        <v>0.5613</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0604</v>
+        <v>0.0159</v>
       </c>
       <c r="E19" t="n">
-        <v>1.504</v>
+        <v>1.3648</v>
       </c>
       <c r="F19" t="n">
-        <v>1.111</v>
+        <v>0.4328</v>
       </c>
       <c r="G19" t="n">
-        <v>0.393</v>
+        <v>0.9319</v>
       </c>
       <c r="H19" t="n">
-        <v>1.111</v>
+        <v>0.4328</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1991</v>
+        <v>0.481</v>
       </c>
       <c r="J19" t="n">
-        <v>0.393</v>
+        <v>0.9319</v>
       </c>
       <c r="K19" t="n">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="L19" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5921</v>
+        <v>1.4129</v>
       </c>
       <c r="N19" t="n">
-        <v>205</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2191</v>
+        <v>1.0129</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5014</v>
+        <v>0.4166</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0692</v>
+        <v>-0.1444</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2191</v>
+        <v>1.0129</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0242</v>
+        <v>0.8884</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1949</v>
+        <v>0.1245</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0242</v>
+        <v>0.8884</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0506</v>
+        <v>0.9121</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1949</v>
+        <v>0.1245</v>
       </c>
       <c r="K20" t="n">
         <v>144</v>
@@ -1357,7 +1357,7 @@
         <v>80</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2455</v>
+        <v>1.0366</v>
       </c>
       <c r="N20" t="n">
         <v>224</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0747</v>
+        <v>0.9393</v>
       </c>
       <c r="C21" t="n">
-        <v>0.442</v>
+        <v>0.3863</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.135</v>
+        <v>-0.1779</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0747</v>
+        <v>0.9393</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3241</v>
+        <v>1.2179</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2494</v>
+        <v>-0.2786</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3241</v>
+        <v>1.2179</v>
       </c>
       <c r="I21" t="n">
-        <v>0.715</v>
+        <v>0.6838</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2494</v>
+        <v>-0.2786</v>
       </c>
       <c r="K21" t="n">
         <v>148</v>
@@ -1403,7 +1403,7 @@
         <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4656</v>
+        <v>0.4051999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>225</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.498</v>
+        <v>0.5393</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2048</v>
+        <v>0.2218</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3975</v>
+        <v>-0.3601</v>
       </c>
       <c r="E22" t="n">
-        <v>0.498</v>
+        <v>0.5393</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6083</v>
+        <v>0.68</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1103</v>
+        <v>-0.1407</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6083</v>
+        <v>0.68</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3285</v>
+        <v>0.3818</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1103</v>
+        <v>-0.1407</v>
       </c>
       <c r="K22" t="n">
         <v>148</v>
@@ -1449,7 +1449,7 @@
         <v>77</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2182</v>
+        <v>0.2411</v>
       </c>
       <c r="N22" t="n">
         <v>225</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.405</v>
+        <v>0.2677</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1666</v>
+        <v>0.1101</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4398</v>
+        <v>-0.4838</v>
       </c>
       <c r="E23" t="n">
-        <v>0.405</v>
+        <v>0.2677</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9103</v>
+        <v>0.8256</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5053</v>
+        <v>-0.5579</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9103</v>
+        <v>0.8256</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9338</v>
+        <v>0.8477</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5053</v>
+        <v>-0.5579</v>
       </c>
       <c r="K23" t="n">
         <v>125</v>
@@ -1495,7 +1495,7 @@
         <v>80</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4285</v>
+        <v>0.2898000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>205</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3515</v>
+        <v>0.2074</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1446</v>
+        <v>0.0853</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4642</v>
+        <v>-0.5113</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3515</v>
+        <v>0.2074</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3515</v>
+        <v>0.2074</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3515</v>
+        <v>0.2074</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3606</v>
+        <v>0.213</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3606</v>
+        <v>0.213</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0335</v>
+        <v>-0.0335</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0138</v>
+        <v>-0.0138</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.609</v>
+        <v>-0.621</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0335</v>
+        <v>-0.0335</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="G25" t="n">
-        <v>0.042</v>
+        <v>-0.0225</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0046</v>
+        <v>-0.0062</v>
       </c>
       <c r="J25" t="n">
-        <v>0.042</v>
+        <v>-0.0225</v>
       </c>
       <c r="K25" t="n">
         <v>148</v>
@@ -1587,7 +1587,7 @@
         <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0374</v>
+        <v>-0.0287</v>
       </c>
       <c r="N25" t="n">
         <v>225</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0413</v>
+        <v>-0.0464</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.017</v>
+        <v>-0.0191</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.643</v>
+        <v>-0.6269</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0413</v>
+        <v>-0.0464</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0709</v>
+        <v>0.0038</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0296</v>
+        <v>-0.0502</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0709</v>
+        <v>0.0038</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0709</v>
+        <v>0.0038</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0296</v>
+        <v>-0.0502</v>
       </c>
       <c r="K26" t="n">
+        <v>117</v>
+      </c>
+      <c r="L26" t="n">
         <v>80</v>
       </c>
-      <c r="L26" t="n">
-        <v>86</v>
-      </c>
       <c r="M26" t="n">
-        <v>-0.0413</v>
+        <v>-0.0464</v>
       </c>
       <c r="N26" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0631</v>
+        <v>-0.0999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.026</v>
+        <v>-0.0411</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6529</v>
+        <v>-0.6513</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0631</v>
+        <v>-0.0999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0005</v>
+        <v>-0.0546</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0636</v>
+        <v>-0.0453</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0005</v>
+        <v>-0.0546</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0005</v>
+        <v>-0.0546</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0636</v>
+        <v>-0.0453</v>
       </c>
       <c r="K27" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="L27" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0631</v>
+        <v>-0.0999</v>
       </c>
       <c r="N27" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1772</v>
+        <v>-0.2572</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7049</v>
+        <v>-0.723</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1772</v>
+        <v>-0.2572</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1772</v>
+        <v>-0.2572</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1772</v>
+        <v>-0.2572</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1818</v>
+        <v>-0.2641</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1818</v>
+        <v>-0.2641</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3894</v>
+        <v>-0.4725</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1601</v>
+        <v>-0.1943</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8015</v>
+        <v>-0.821</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3894</v>
+        <v>-0.4725</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3894</v>
+        <v>-0.4725</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3894</v>
+        <v>-0.4725</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4203</v>
+        <v>-0.5114</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4203</v>
+        <v>-0.5114</v>
       </c>
       <c r="N29" t="n">
         <v>173</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6681</v>
+        <v>-0.6192</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2748</v>
+        <v>-0.2547</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9283</v>
+        <v>-0.8879</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6681</v>
+        <v>-0.6192</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4682</v>
+        <v>-1.4264</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8001</v>
+        <v>0.8072</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4682</v>
+        <v>-1.4264</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.506</v>
+        <v>-1.4645</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8001</v>
+        <v>0.8072</v>
       </c>
       <c r="K30" t="n">
         <v>83</v>
@@ -1817,7 +1817,7 @@
         <v>55</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7059</v>
+        <v>-0.6572999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>138</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6989</v>
+        <v>-0.7177</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2874</v>
+        <v>-0.2952</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9424</v>
+        <v>-0.9327</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6989</v>
+        <v>-0.7177</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6989</v>
+        <v>-0.7177</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6989</v>
+        <v>-0.7177</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7169</v>
+        <v>-0.7369</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7169</v>
+        <v>-0.7369</v>
       </c>
       <c r="N31" t="n">
         <v>119</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7304</v>
+        <v>-0.7395</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3004</v>
+        <v>-0.3041</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9567</v>
+        <v>-0.9427</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7304</v>
+        <v>-0.7395</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7304</v>
+        <v>-0.7395</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7304</v>
+        <v>-0.7395</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7492</v>
+        <v>-0.7593</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7492</v>
+        <v>-0.7593</v>
       </c>
       <c r="N32" t="n">
         <v>119</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0164</v>
+        <v>-0.9827</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.418</v>
+        <v>-0.4041</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0869</v>
+        <v>-1.0535</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0164</v>
+        <v>-0.9827</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8994</v>
+        <v>-0.9827</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.117</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8994</v>
+        <v>-0.9827</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9707</v>
+        <v>-1.0359</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.117</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="L33" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0877</v>
+        <v>-1.0359</v>
       </c>
       <c r="N33" t="n">
-        <v>317</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0174</v>
+        <v>-0.9926</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4184</v>
+        <v>-0.4082</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0873</v>
+        <v>-1.058</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0174</v>
+        <v>-0.9926</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0174</v>
+        <v>-0.8579</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.1347</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0174</v>
+        <v>-0.8579</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0705</v>
+        <v>-0.9285</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.1347</v>
       </c>
       <c r="K34" t="n">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0705</v>
+        <v>-1.0632</v>
       </c>
       <c r="N34" t="n">
-        <v>173</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2175</v>
+        <v>-1.1753</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5007</v>
+        <v>-0.4834</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1784</v>
+        <v>-1.1412</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2175</v>
+        <v>-1.1753</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2175</v>
+        <v>-0.5164</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.6589</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2175</v>
+        <v>-0.5164</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2489</v>
+        <v>-0.5589</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.6589</v>
       </c>
       <c r="K35" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2489</v>
+        <v>-1.2178</v>
       </c>
       <c r="N35" t="n">
-        <v>119</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2321</v>
+        <v>-1.1883</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5067</v>
+        <v>-0.4887</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1851</v>
+        <v>-1.1471</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2321</v>
+        <v>-1.1883</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5248</v>
+        <v>-1.1883</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7073</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5248</v>
+        <v>-1.1883</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5664</v>
+        <v>-1.2201</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7073</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="L36" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2737</v>
+        <v>-1.2201</v>
       </c>
       <c r="N36" t="n">
-        <v>334</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2699</v>
+        <v>-1.2617</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5223</v>
+        <v>-0.5189</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2023</v>
+        <v>-1.1806</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2699</v>
+        <v>-1.2617</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2699</v>
+        <v>-1.2617</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2699</v>
+        <v>-1.2617</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3362</v>
+        <v>-1.33</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3362</v>
+        <v>-1.33</v>
       </c>
       <c r="N37" t="n">
         <v>147</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3163</v>
+        <v>-1.2781</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5413</v>
+        <v>-0.5256</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2234</v>
+        <v>-1.188</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3163</v>
+        <v>-1.2781</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3163</v>
+        <v>-0.2781</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3163</v>
+        <v>-0.2781</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3244</v>
+        <v>-0.2855</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>26</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3244</v>
+        <v>-1.2855</v>
       </c>
       <c r="N38" t="n">
         <v>76</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6107</v>
+        <v>-1.5736</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6624</v>
+        <v>-0.6472</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3574</v>
+        <v>-1.3226</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6107</v>
+        <v>-1.5736</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6107</v>
+        <v>-0.5736</v>
       </c>
       <c r="G39" t="n">
         <v>-1</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6107</v>
+        <v>-0.5736</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6761</v>
+        <v>-0.6374</v>
       </c>
       <c r="J39" t="n">
         <v>-1</v>
@@ -2231,7 +2231,7 @@
         <v>107</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6761</v>
+        <v>-1.6374</v>
       </c>
       <c r="N39" t="n">
         <v>223</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.612</v>
+        <v>-1.6238</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.663</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.358</v>
+        <v>-1.3455</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.612</v>
+        <v>-1.6238</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-1.6238</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-1.6238</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-1.7575</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="L40" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.612</v>
+        <v>-1.7575</v>
       </c>
       <c r="N40" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6401</v>
+        <v>-1.6282</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6745</v>
+        <v>-0.6696</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3708</v>
+        <v>-1.3475</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6401</v>
+        <v>-1.6282</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6401</v>
+        <v>-0.7188</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.9094</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6401</v>
+        <v>-0.7188</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7702</v>
+        <v>-0.7188</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.9094</v>
       </c>
       <c r="K41" t="n">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7702</v>
+        <v>-1.6282</v>
       </c>
       <c r="N41" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42">
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.4322</v>
+        <v>-2.135</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.0003</v>
+        <v>-0.878</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.7314</v>
+        <v>-1.5784</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.4322</v>
+        <v>-2.135</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.6621</v>
+        <v>-1.3887</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.7701</v>
+        <v>-0.7463</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.6621</v>
+        <v>-1.3887</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8975</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.7701</v>
+        <v>-0.7463</v>
       </c>
       <c r="K42" t="n">
         <v>158</v>
@@ -2369,7 +2369,7 @@
         <v>59</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.6676</v>
+        <v>-1.526</v>
       </c>
       <c r="N42" t="n">
         <v>217</v>
@@ -2475,10 +2475,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3065</v>
+        <v>0.2613</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0495</v>
+        <v>6.0099</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1954</v>
+        <v>-0.1785</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.4942</v>
+        <v>-4.1055</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2816</v>
+        <v>-0.264</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.4768</v>
+        <v>-6.072</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.74</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2909</v>
+        <v>-0.2736</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.6907</v>
+        <v>-6.2928</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4272</v>
+        <v>-0.4181</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.8256</v>
+        <v>-9.616300000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.59</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2641</v>
+        <v>1.2884</v>
       </c>
       <c r="J7" t="n">
-        <v>29.0743</v>
+        <v>29.6332</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.41</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9408</v>
+        <v>0.9326</v>
       </c>
       <c r="J8" t="n">
-        <v>21.6384</v>
+        <v>21.4498</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7343</v>
+        <v>0.7135</v>
       </c>
       <c r="J9" t="n">
-        <v>16.8889</v>
+        <v>16.4105</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7145</v>
+        <v>0.6928</v>
       </c>
       <c r="J10" t="n">
-        <v>16.4335</v>
+        <v>15.9344</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3872</v>
+        <v>0.3553</v>
       </c>
       <c r="J11" t="n">
-        <v>8.9056</v>
+        <v>8.171900000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2573</v>
+        <v>0.2109</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2044</v>
+        <v>5.9052</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.016</v>
+        <v>-0.0114</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.448</v>
+        <v>-0.3192</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1602</v>
+        <v>-0.142</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.4856</v>
+        <v>-3.976</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2712</v>
+        <v>-0.2522</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.5936</v>
+        <v>-7.0616</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.72</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3186</v>
+        <v>-0.3015</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.9208</v>
+        <v>-8.442</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7533</v>
+        <v>0.7235</v>
       </c>
       <c r="J17" t="n">
-        <v>21.0924</v>
+        <v>20.258</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6565</v>
       </c>
       <c r="J18" t="n">
-        <v>19.32</v>
+        <v>18.382</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.19</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.4979</v>
       </c>
       <c r="J19" t="n">
-        <v>15.0304</v>
+        <v>13.9412</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2436</v>
+        <v>0.211</v>
       </c>
       <c r="J20" t="n">
-        <v>6.8208</v>
+        <v>5.908</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7653</v>
+        <v>-0.7393</v>
       </c>
       <c r="J21" t="n">
-        <v>-21.4284</v>
+        <v>-20.7004</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3619</v>
+        <v>0.3078</v>
       </c>
       <c r="J22" t="n">
-        <v>10.857</v>
+        <v>9.234</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3055</v>
+        <v>0.2546</v>
       </c>
       <c r="J23" t="n">
-        <v>9.164999999999999</v>
+        <v>7.638</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.87</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1744</v>
+        <v>-0.1546</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.232</v>
+        <v>-4.638</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.185</v>
+        <v>-0.165</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.55</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.369</v>
+        <v>-0.3554</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.07</v>
+        <v>-10.662</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.47</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9329</v>
+        <v>0.919</v>
       </c>
       <c r="J27" t="n">
-        <v>27.987</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.36</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7739</v>
+        <v>0.7577</v>
       </c>
       <c r="J28" t="n">
-        <v>23.217</v>
+        <v>22.731</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.08</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2689</v>
+        <v>0.2355</v>
       </c>
       <c r="J29" t="n">
-        <v>8.067</v>
+        <v>7.065</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3117</v>
+        <v>-0.2704</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.351000000000001</v>
+        <v>-8.112</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6349</v>
+        <v>-0.5998</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.047</v>
+        <v>-17.994</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5226</v>
+        <v>0.4919</v>
       </c>
       <c r="J32" t="n">
-        <v>15.1554</v>
+        <v>14.2651</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1932</v>
+        <v>0.1529</v>
       </c>
       <c r="J33" t="n">
-        <v>5.6028</v>
+        <v>4.4341</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1013</v>
+        <v>0.0747</v>
       </c>
       <c r="J34" t="n">
-        <v>2.9377</v>
+        <v>2.1663</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0982</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.8478</v>
+        <v>-2.3664</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.64</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4011</v>
+        <v>-0.3909</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.6319</v>
+        <v>-11.3361</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7859</v>
+        <v>0.77</v>
       </c>
       <c r="J37" t="n">
-        <v>22.7911</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.517</v>
+        <v>0.5021</v>
       </c>
       <c r="J38" t="n">
-        <v>14.993</v>
+        <v>14.5609</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3015</v>
+        <v>0.264</v>
       </c>
       <c r="J39" t="n">
-        <v>8.743499999999999</v>
+        <v>7.656</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1818</v>
+        <v>-0.1478</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.2722</v>
+        <v>-4.2862</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6927</v>
+        <v>-0.6602</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.0883</v>
+        <v>-19.1458</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4189</v>
+        <v>0.3552</v>
       </c>
       <c r="J42" t="n">
-        <v>11.7292</v>
+        <v>9.945600000000001</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2217</v>
+        <v>0.1753</v>
       </c>
       <c r="J43" t="n">
-        <v>6.2076</v>
+        <v>4.9084</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1049</v>
+        <v>0.0775</v>
       </c>
       <c r="J44" t="n">
-        <v>2.9372</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0273</v>
+        <v>0.0181</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7644</v>
+        <v>0.5068</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2073</v>
+        <v>-0.1867</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.8044</v>
+        <v>-5.2276</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.388</v>
+        <v>0.3844</v>
       </c>
       <c r="J47" t="n">
-        <v>10.864</v>
+        <v>10.7632</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1203</v>
+        <v>-0.1026</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.3684</v>
+        <v>-2.8728</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.9</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1434</v>
+        <v>-0.1244</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.0152</v>
+        <v>-3.4832</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1656</v>
+        <v>-0.1458</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.6368</v>
+        <v>-4.0824</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.86</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1871</v>
+        <v>-0.1668</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.2388</v>
+        <v>-4.6704</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.308</v>
+        <v>0.2571</v>
       </c>
       <c r="J52" t="n">
-        <v>8.007999999999999</v>
+        <v>6.6846</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.11</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2886</v>
+        <v>0.239</v>
       </c>
       <c r="J53" t="n">
-        <v>7.5036</v>
+        <v>6.214</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2064</v>
+        <v>0.1642</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3664</v>
+        <v>4.2692</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3498</v>
+        <v>-0.3347</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.094799999999999</v>
+        <v>-8.702199999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.404</v>
+        <v>-0.3935</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.504</v>
+        <v>-10.231</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9238</v>
+        <v>0.9092</v>
       </c>
       <c r="J57" t="n">
-        <v>24.0188</v>
+        <v>23.6392</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.27</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6311</v>
+        <v>0.6186</v>
       </c>
       <c r="J58" t="n">
-        <v>16.4086</v>
+        <v>16.0836</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3419</v>
+        <v>0.3071</v>
       </c>
       <c r="J59" t="n">
-        <v>8.8894</v>
+        <v>7.9846</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1108</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>2.8808</v>
+        <v>2.3374</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.93</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2903</v>
+        <v>-0.2503</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.5478</v>
+        <v>-6.5078</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1529</v>
+        <v>0.1186</v>
       </c>
       <c r="J62" t="n">
-        <v>3.5167</v>
+        <v>2.7278</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1273</v>
+        <v>0.0968</v>
       </c>
       <c r="J63" t="n">
-        <v>2.9279</v>
+        <v>2.2264</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.86</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1794</v>
+        <v>-0.1612</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.1262</v>
+        <v>-3.7076</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3157</v>
+        <v>-0.2985</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.2611</v>
+        <v>-6.8655</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3709</v>
+        <v>-0.3571</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.5307</v>
+        <v>-8.2133</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1073</v>
+        <v>1.0989</v>
       </c>
       <c r="J67" t="n">
-        <v>25.4679</v>
+        <v>25.2747</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8417</v>
+        <v>0.8282</v>
       </c>
       <c r="J68" t="n">
-        <v>19.3591</v>
+        <v>19.0486</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.3</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6601</v>
+        <v>0.6513</v>
       </c>
       <c r="J69" t="n">
-        <v>15.1823</v>
+        <v>14.9799</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>1.27</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6162</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>14.1726</v>
+        <v>14.0162</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3439</v>
+        <v>-0.3063</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.9097</v>
+        <v>-7.0449</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>2.06</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6171</v>
+        <v>1.648</v>
       </c>
       <c r="J72" t="n">
-        <v>30.7249</v>
+        <v>31.312</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5935</v>
+        <v>0.5896</v>
       </c>
       <c r="J73" t="n">
-        <v>11.2765</v>
+        <v>11.2024</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.25</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5748</v>
       </c>
       <c r="J74" t="n">
-        <v>10.9839</v>
+        <v>10.9212</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.22</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5309</v>
+        <v>0.5282</v>
       </c>
       <c r="J75" t="n">
-        <v>10.0871</v>
+        <v>10.0358</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.381</v>
+        <v>0.3491</v>
       </c>
       <c r="J76" t="n">
-        <v>7.239</v>
+        <v>6.6329</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>0.93</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0447</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.1913</v>
+        <v>-0.8493000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>0.75</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2661</v>
+        <v>-0.2527</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.0559</v>
+        <v>-4.8013</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.58</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4185</v>
+        <v>-0.4095</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.9515</v>
+        <v>-7.7805</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.55</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.445</v>
+        <v>-0.4378</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.455</v>
+        <v>-8.318199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.5</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.489</v>
+        <v>-0.4859</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.291</v>
+        <v>-9.232100000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.02</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0639</v>
+        <v>0.051</v>
       </c>
       <c r="J82" t="n">
-        <v>2.1726</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0053</v>
+        <v>0.0035</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1802</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.2368</v>
+        <v>-2.7098</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.2368</v>
+        <v>-2.7098</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2272</v>
+        <v>-0.2069</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.7248</v>
+        <v>-7.0346</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.34</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4611</v>
+        <v>0.4023</v>
       </c>
       <c r="J87" t="n">
-        <v>15.6774</v>
+        <v>13.6782</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2438</v>
+        <v>0.1955</v>
       </c>
       <c r="J88" t="n">
-        <v>8.289199999999999</v>
+        <v>6.647</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1486</v>
+        <v>0.1143</v>
       </c>
       <c r="J89" t="n">
-        <v>5.0524</v>
+        <v>3.8862</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0458</v>
+        <v>0.0318</v>
       </c>
       <c r="J90" t="n">
-        <v>1.5572</v>
+        <v>1.0812</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.96</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0655</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.7608</v>
+        <v>-2.227</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6308</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>17.0316</v>
+        <v>16.6968</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.19</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5042</v>
+        <v>0.4899</v>
       </c>
       <c r="J93" t="n">
-        <v>13.6134</v>
+        <v>13.2273</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4715</v>
+        <v>0.4466</v>
       </c>
       <c r="J94" t="n">
-        <v>12.7305</v>
+        <v>12.0582</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.15</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4355</v>
+        <v>0.4019</v>
       </c>
       <c r="J95" t="n">
-        <v>11.7585</v>
+        <v>10.8513</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>1.04</v>
       </c>
       <c r="I96" t="n">
-        <v>0.144</v>
+        <v>0.1199</v>
       </c>
       <c r="J96" t="n">
-        <v>3.888</v>
+        <v>3.2373</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.2</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4648</v>
+        <v>0.4206</v>
       </c>
       <c r="J97" t="n">
-        <v>12.5496</v>
+        <v>11.3562</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0231</v>
+        <v>0.0176</v>
       </c>
       <c r="J98" t="n">
-        <v>0.6237</v>
+        <v>0.4752</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.97</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0467</v>
+        <v>-0.0373</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.2609</v>
+        <v>-1.0071</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.61</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4159</v>
+        <v>-0.4061</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.2293</v>
+        <v>-10.9647</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.54</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4774</v>
+        <v>-0.4743</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.8898</v>
+        <v>-12.8061</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.02</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0948</v>
+        <v>0.0743</v>
       </c>
       <c r="J102" t="n">
-        <v>2.4648</v>
+        <v>1.9318</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.9841</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>-25.5866</v>
+        <v>-25.4618</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.41</v>
       </c>
       <c r="I104" t="n">
-        <v>-1.3964</v>
+        <v>-1.4563</v>
       </c>
       <c r="J104" t="n">
-        <v>-36.3064</v>
+        <v>-37.8638</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.61</v>
       </c>
       <c r="I105" t="n">
-        <v>1.1551</v>
+        <v>1.1573</v>
       </c>
       <c r="J105" t="n">
-        <v>30.0326</v>
+        <v>30.0898</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>1.54</v>
       </c>
       <c r="I106" t="n">
-        <v>1.0571</v>
+        <v>1.052</v>
       </c>
       <c r="J106" t="n">
-        <v>27.4846</v>
+        <v>27.352</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.13</v>
       </c>
       <c r="I107" t="n">
-        <v>0.31</v>
+        <v>0.2587</v>
       </c>
       <c r="J107" t="n">
-        <v>8.06</v>
+        <v>6.7262</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0859</v>
+        <v>-0.0703</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.2334</v>
+        <v>-1.8278</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3102</v>
+        <v>-0.2929</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.065200000000001</v>
+        <v>-7.6154</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.31</v>
+        <v>0.2587</v>
       </c>
       <c r="J110" t="n">
-        <v>8.06</v>
+        <v>6.7262</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>1.04</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1249</v>
+        <v>0.0944</v>
       </c>
       <c r="J111" t="n">
-        <v>3.2474</v>
+        <v>2.4544</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>0.85</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1928</v>
+        <v>-0.1732</v>
       </c>
       <c r="J112" t="n">
-        <v>-5.784</v>
+        <v>-5.196</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>0.85</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1928</v>
+        <v>-0.1732</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.784</v>
+        <v>-5.196</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>0.58</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4463</v>
+        <v>-0.44</v>
       </c>
       <c r="J114" t="n">
-        <v>-13.389</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3606</v>
+        <v>0.3556</v>
       </c>
       <c r="J115" t="n">
-        <v>10.818</v>
+        <v>10.668</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>1.04</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1114</v>
+        <v>0.0953</v>
       </c>
       <c r="J116" t="n">
-        <v>3.342</v>
+        <v>2.859</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3351</v>
+        <v>0.2785</v>
       </c>
       <c r="J117" t="n">
-        <v>10.053</v>
+        <v>8.355</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3117</v>
+        <v>0.2575</v>
       </c>
       <c r="J118" t="n">
-        <v>9.351000000000001</v>
+        <v>7.725</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.78</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2871</v>
+        <v>-0.2701</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.613</v>
+        <v>-8.103</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>1.43</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5248</v>
+        <v>0.4843</v>
       </c>
       <c r="J120" t="n">
-        <v>15.744</v>
+        <v>14.529</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>1.27</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3811</v>
+        <v>0.3204</v>
       </c>
       <c r="J121" t="n">
-        <v>11.433</v>
+        <v>9.612</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9929</v>
+        <v>0.9804</v>
       </c>
       <c r="J122" t="n">
-        <v>24.8225</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5568</v>
+        <v>0.5525</v>
       </c>
       <c r="J123" t="n">
-        <v>13.92</v>
+        <v>13.8125</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.62</v>
       </c>
       <c r="I124" t="n">
-        <v>-1.0222</v>
+        <v>-1.0299</v>
       </c>
       <c r="J124" t="n">
-        <v>-25.555</v>
+        <v>-25.7475</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.62</v>
       </c>
       <c r="I125" t="n">
-        <v>1.098</v>
+        <v>1.0891</v>
       </c>
       <c r="J125" t="n">
-        <v>27.45</v>
+        <v>27.2275</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>1.45</v>
       </c>
       <c r="I126" t="n">
-        <v>0.8716</v>
+        <v>0.8576</v>
       </c>
       <c r="J126" t="n">
-        <v>21.79</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.31</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5497</v>
+        <v>0.5226</v>
       </c>
       <c r="J127" t="n">
-        <v>13.7425</v>
+        <v>13.065</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.29</v>
       </c>
       <c r="I128" t="n">
-        <v>0.527</v>
+        <v>0.4967</v>
       </c>
       <c r="J128" t="n">
-        <v>13.175</v>
+        <v>12.4175</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1437</v>
+        <v>-0.124</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.5925</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>1.06</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1598</v>
+        <v>0.1272</v>
       </c>
       <c r="J130" t="n">
-        <v>3.995</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.92</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1318</v>
+        <v>-0.1126</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.295</v>
+        <v>-2.815</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7139</v>
       </c>
       <c r="J132" t="n">
-        <v>22.302</v>
+        <v>21.417</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.617</v>
+        <v>0.5818</v>
       </c>
       <c r="J133" t="n">
-        <v>18.51</v>
+        <v>17.454</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2922</v>
+        <v>0.2586</v>
       </c>
       <c r="J134" t="n">
-        <v>8.766</v>
+        <v>7.758</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2652</v>
+        <v>0.2328</v>
       </c>
       <c r="J135" t="n">
-        <v>7.956</v>
+        <v>6.984</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1784</v>
+        <v>0.1513</v>
       </c>
       <c r="J136" t="n">
-        <v>5.352</v>
+        <v>4.539</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.19</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4337</v>
+        <v>0.3771</v>
       </c>
       <c r="J137" t="n">
-        <v>13.011</v>
+        <v>11.313</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.04</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1358</v>
+        <v>0.1027</v>
       </c>
       <c r="J138" t="n">
-        <v>4.074</v>
+        <v>3.081</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.03</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1106</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>3.318</v>
+        <v>2.448</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.88</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1636</v>
+        <v>-0.1442</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.908</v>
+        <v>-4.326</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.53</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4923</v>
+        <v>-0.492</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.769</v>
+        <v>-14.76</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1038</v>
+        <v>1.1152</v>
       </c>
       <c r="J142" t="n">
-        <v>27.595</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>1.34</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8326</v>
+        <v>0.8105</v>
       </c>
       <c r="J143" t="n">
-        <v>20.815</v>
+        <v>20.2625</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>1.3</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7526</v>
+        <v>0.7255</v>
       </c>
       <c r="J144" t="n">
-        <v>18.815</v>
+        <v>18.1375</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0339</v>
+        <v>-0.0283</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.8475</v>
+        <v>-0.7075</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.458</v>
+        <v>-0.4176</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.45</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.44</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8184</v>
       </c>
       <c r="J147" t="n">
-        <v>21.41</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.25</v>
       </c>
       <c r="I148" t="n">
-        <v>0.552</v>
+        <v>0.4973</v>
       </c>
       <c r="J148" t="n">
-        <v>13.8</v>
+        <v>12.4325</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>0.62</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4095</v>
+        <v>-0.3991</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.2375</v>
+        <v>-9.977499999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>0.59</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.436</v>
+        <v>-0.4284</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.9</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4796</v>
+        <v>-0.4771</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.99</v>
+        <v>-11.9275</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1187</v>
+        <v>-0.1016</v>
       </c>
       <c r="J152" t="n">
-        <v>-3.0862</v>
+        <v>-2.6416</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1528</v>
+        <v>-0.1338</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.9728</v>
+        <v>-3.4788</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.54</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4839</v>
+        <v>-0.4825</v>
       </c>
       <c r="J154" t="n">
-        <v>-12.5814</v>
+        <v>-12.545</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4331</v>
+        <v>0.3765</v>
       </c>
       <c r="J155" t="n">
-        <v>11.2606</v>
+        <v>9.789</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>1.14</v>
       </c>
       <c r="I156" t="n">
-        <v>0.3428</v>
+        <v>0.2897</v>
       </c>
       <c r="J156" t="n">
-        <v>8.912800000000001</v>
+        <v>7.5322</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.31</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8035</v>
+        <v>0.7772</v>
       </c>
       <c r="J157" t="n">
-        <v>20.891</v>
+        <v>20.2072</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>0.63</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.9704</v>
+        <v>-0.965</v>
       </c>
       <c r="J158" t="n">
-        <v>-25.2304</v>
+        <v>-25.09</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.54</v>
       </c>
       <c r="I159" t="n">
-        <v>-1.151</v>
+        <v>-1.1704</v>
       </c>
       <c r="J159" t="n">
-        <v>-29.926</v>
+        <v>-30.4304</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.77</v>
       </c>
       <c r="I160" t="n">
-        <v>1.5042</v>
+        <v>1.5486</v>
       </c>
       <c r="J160" t="n">
-        <v>39.1092</v>
+        <v>40.2636</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>1.14</v>
       </c>
       <c r="I161" t="n">
-        <v>0.4261</v>
+        <v>0.3855</v>
       </c>
       <c r="J161" t="n">
-        <v>11.0786</v>
+        <v>10.023</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1737</v>
+        <v>0.1363</v>
       </c>
       <c r="J162" t="n">
-        <v>4.1688</v>
+        <v>3.2712</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0706</v>
+        <v>-0.0563</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.6944</v>
+        <v>-1.3512</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1716</v>
+        <v>-0.1517</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.1184</v>
+        <v>-3.6408</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.44</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5695</v>
+        <v>0.4989</v>
       </c>
       <c r="J165" t="n">
-        <v>13.668</v>
+        <v>11.9736</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.4</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5271</v>
+        <v>0.4577</v>
       </c>
       <c r="J166" t="n">
-        <v>12.6504</v>
+        <v>10.9848</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.17</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2936</v>
+        <v>0.2812</v>
       </c>
       <c r="J167" t="n">
-        <v>7.0464</v>
+        <v>6.7488</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.06</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1297</v>
+        <v>0.1143</v>
       </c>
       <c r="J168" t="n">
-        <v>3.1128</v>
+        <v>2.7432</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.74</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3134</v>
+        <v>-0.2965</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.5216</v>
+        <v>-7.116</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1934</v>
+        <v>0.1772</v>
       </c>
       <c r="J170" t="n">
-        <v>4.6416</v>
+        <v>4.2528</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>1.1</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1934</v>
+        <v>0.1772</v>
       </c>
       <c r="J171" t="n">
-        <v>4.6416</v>
+        <v>4.2528</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>0.88</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1456</v>
+        <v>-0.1302</v>
       </c>
       <c r="J172" t="n">
-        <v>-4.368</v>
+        <v>-3.906</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>0.34</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.638</v>
+        <v>-0.6585</v>
       </c>
       <c r="J173" t="n">
-        <v>-19.14</v>
+        <v>-19.755</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.27</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.6969</v>
+        <v>-0.7292</v>
       </c>
       <c r="J174" t="n">
-        <v>-20.907</v>
+        <v>-21.876</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>1.38</v>
       </c>
       <c r="I175" t="n">
-        <v>0.836</v>
+        <v>0.8178</v>
       </c>
       <c r="J175" t="n">
-        <v>25.08</v>
+        <v>24.534</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1102</v>
+        <v>-0.0955</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.306</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>0.65</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.8756</v>
+        <v>-0.8552</v>
       </c>
       <c r="J177" t="n">
-        <v>-26.268</v>
+        <v>-25.656</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.58</v>
       </c>
       <c r="I178" t="n">
-        <v>-1.0209</v>
+        <v>-1.0156</v>
       </c>
       <c r="J178" t="n">
-        <v>-30.627</v>
+        <v>-30.468</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.47</v>
       </c>
       <c r="I179" t="n">
-        <v>-1.2431</v>
+        <v>-1.2689</v>
       </c>
       <c r="J179" t="n">
-        <v>-37.293</v>
+        <v>-38.067</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>1.24</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7428</v>
       </c>
       <c r="J180" t="n">
-        <v>22.728</v>
+        <v>22.284</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>1.2</v>
       </c>
       <c r="I181" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6378</v>
       </c>
       <c r="J181" t="n">
-        <v>19.854</v>
+        <v>19.134</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.58</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7173</v>
+        <v>0.6464</v>
       </c>
       <c r="J182" t="n">
-        <v>21.519</v>
+        <v>19.392</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.21</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3155</v>
+        <v>0.2598</v>
       </c>
       <c r="J183" t="n">
-        <v>9.465</v>
+        <v>7.794</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2161</v>
+        <v>0.1722</v>
       </c>
       <c r="J184" t="n">
-        <v>6.483</v>
+        <v>5.166</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.17</v>
+        <v>-0.1499</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.1</v>
+        <v>-4.497</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.17</v>
+        <v>-0.1499</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.1</v>
+        <v>-4.497</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3998</v>
+        <v>0.3974</v>
       </c>
       <c r="J187" t="n">
-        <v>11.994</v>
+        <v>11.922</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3195</v>
+        <v>0.3091</v>
       </c>
       <c r="J188" t="n">
-        <v>9.585000000000001</v>
+        <v>9.273</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0963</v>
+        <v>-0.0803</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.889</v>
+        <v>-2.409</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.86</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1877</v>
+        <v>-0.1673</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.631</v>
+        <v>-5.019</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.6</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4342</v>
+        <v>-0.4272</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.026</v>
+        <v>-12.816</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>0.79</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.2291</v>
+        <v>-0.2145</v>
       </c>
       <c r="J192" t="n">
-        <v>-4.8111</v>
+        <v>-4.5045</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.74</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2787</v>
+        <v>-0.2652</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.8527</v>
+        <v>-5.5692</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.66</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3504</v>
+        <v>-0.338</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.3584</v>
+        <v>-7.098</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.62</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3856</v>
+        <v>-0.3743</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.0976</v>
+        <v>-7.8603</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.59</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4121</v>
+        <v>-0.4023</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.6541</v>
+        <v>-8.4483</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3586</v>
+        <v>1.3815</v>
       </c>
       <c r="J197" t="n">
-        <v>28.5306</v>
+        <v>29.0115</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.56</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1454</v>
+        <v>1.1614</v>
       </c>
       <c r="J198" t="n">
-        <v>24.0534</v>
+        <v>24.3894</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.52</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0939</v>
+        <v>1.109</v>
       </c>
       <c r="J199" t="n">
-        <v>22.9719</v>
+        <v>23.289</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.47</v>
       </c>
       <c r="I200" t="n">
-        <v>1.0263</v>
+        <v>1.0348</v>
       </c>
       <c r="J200" t="n">
-        <v>21.5523</v>
+        <v>21.7308</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4679</v>
+        <v>-0.4346</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.825900000000001</v>
+        <v>-9.1266</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0256</v>
+        <v>0.02</v>
       </c>
       <c r="J202" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.185</v>
+        <v>-1.855</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1359</v>
+        <v>-0.1197</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.3975</v>
+        <v>-2.9925</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.199</v>
+        <v>-0.1805</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.975</v>
+        <v>-4.5125</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.59</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4326</v>
+        <v>-0.4243</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.815</v>
+        <v>-10.6075</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.73</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4008</v>
+        <v>1.4273</v>
       </c>
       <c r="J207" t="n">
-        <v>35.02</v>
+        <v>35.6825</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.5</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0972</v>
+        <v>1.1083</v>
       </c>
       <c r="J208" t="n">
-        <v>27.43</v>
+        <v>27.7075</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2229</v>
+        <v>0.1937</v>
       </c>
       <c r="J209" t="n">
-        <v>5.5725</v>
+        <v>4.8425</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.96</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2113</v>
+        <v>-0.1774</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.2825</v>
+        <v>-4.435</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.359</v>
+        <v>-0.319</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.975</v>
+        <v>-7.975</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.23</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4822</v>
+        <v>0.4234</v>
       </c>
       <c r="J212" t="n">
-        <v>13.5016</v>
+        <v>11.8552</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.04</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1236</v>
+        <v>0.0936</v>
       </c>
       <c r="J213" t="n">
-        <v>3.4608</v>
+        <v>2.6208</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>1.02</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0726</v>
+        <v>0.052</v>
       </c>
       <c r="J214" t="n">
-        <v>2.0328</v>
+        <v>1.456</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.98</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0432</v>
+        <v>-0.0327</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.2096</v>
+        <v>-0.9156</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2825</v>
+        <v>-0.2638</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.91</v>
+        <v>-7.3864</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.76</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4886</v>
+        <v>1.5308</v>
       </c>
       <c r="J217" t="n">
-        <v>41.6808</v>
+        <v>42.8624</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5419</v>
+        <v>0.5022</v>
       </c>
       <c r="J218" t="n">
-        <v>15.1732</v>
+        <v>14.0616</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.385</v>
+        <v>-0.3421</v>
       </c>
       <c r="J219" t="n">
-        <v>-10.78</v>
+        <v>-9.578799999999999</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.88</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4109</v>
+        <v>-0.3679</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.5052</v>
+        <v>-10.3012</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8254</v>
+        <v>-0.8043</v>
       </c>
       <c r="J221" t="n">
-        <v>-23.1112</v>
+        <v>-22.5204</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>0.58</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.367</v>
+        <v>-0.359</v>
       </c>
       <c r="J222" t="n">
-        <v>-6.239</v>
+        <v>-6.103</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.42</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.5203</v>
+        <v>-0.5256</v>
       </c>
       <c r="J223" t="n">
-        <v>-8.8451</v>
+        <v>-8.9352</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.41</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5281</v>
+        <v>-0.5336</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.9777</v>
+        <v>-9.071199999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.34</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.59</v>
+        <v>-0.5994</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.03</v>
+        <v>-10.1898</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.34</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.59</v>
+        <v>-0.5994</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.03</v>
+        <v>-10.1898</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>2.23</v>
       </c>
       <c r="I227" t="n">
-        <v>1.8928</v>
+        <v>1.9589</v>
       </c>
       <c r="J227" t="n">
-        <v>32.1776</v>
+        <v>33.3013</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>2.06</v>
       </c>
       <c r="I228" t="n">
-        <v>1.7053</v>
+        <v>1.754</v>
       </c>
       <c r="J228" t="n">
-        <v>28.9901</v>
+        <v>29.818</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.56</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1253</v>
+        <v>1.1487</v>
       </c>
       <c r="J229" t="n">
-        <v>19.1301</v>
+        <v>19.5279</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>1.43</v>
       </c>
       <c r="I230" t="n">
-        <v>0.9375</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>15.9375</v>
+        <v>16.014</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>1.13</v>
       </c>
       <c r="I231" t="n">
-        <v>0.3162</v>
+        <v>0.2787</v>
       </c>
       <c r="J231" t="n">
-        <v>5.3754</v>
+        <v>4.7379</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.12</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2849</v>
+        <v>0.2361</v>
       </c>
       <c r="J232" t="n">
-        <v>9.971500000000001</v>
+        <v>8.263500000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.03</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0969</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>3.3915</v>
+        <v>2.534</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.88</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1723</v>
+        <v>-0.1518</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.0305</v>
+        <v>-5.313</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.16</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3573</v>
+        <v>0.3033</v>
       </c>
       <c r="J235" t="n">
-        <v>12.5055</v>
+        <v>10.6155</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.98</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0451</v>
+        <v>-0.034</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.5785</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.01</v>
       </c>
       <c r="I237" t="n">
-        <v>0.0433</v>
+        <v>0.0323</v>
       </c>
       <c r="J237" t="n">
-        <v>1.5155</v>
+        <v>1.1305</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>0.91</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3355</v>
+        <v>-0.2935</v>
       </c>
       <c r="J238" t="n">
-        <v>-11.7425</v>
+        <v>-10.2725</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.5851</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>-20.4785</v>
+        <v>-19.1415</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.4</v>
       </c>
       <c r="I240" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9667</v>
       </c>
       <c r="J240" t="n">
-        <v>34.1005</v>
+        <v>33.8345</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>1.39</v>
       </c>
       <c r="I241" t="n">
-        <v>0.956</v>
+        <v>0.9453</v>
       </c>
       <c r="J241" t="n">
-        <v>33.46</v>
+        <v>33.0855</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.302</v>
+        <v>0.252</v>
       </c>
       <c r="J242" t="n">
-        <v>8.154</v>
+        <v>6.804</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1647</v>
+        <v>0.1295</v>
       </c>
       <c r="J243" t="n">
-        <v>4.4469</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.84</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2156</v>
+        <v>-0.1951</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.8212</v>
+        <v>-5.2677</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.21</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4413</v>
+        <v>0.3836</v>
       </c>
       <c r="J245" t="n">
-        <v>11.9151</v>
+        <v>10.3572</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.97</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.0613</v>
+        <v>-0.0479</v>
       </c>
       <c r="J246" t="n">
-        <v>-1.6551</v>
+        <v>-1.2933</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>0.83</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.506</v>
+        <v>-0.4645</v>
       </c>
       <c r="J247" t="n">
-        <v>-13.662</v>
+        <v>-12.5415</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>0.77</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.6444</v>
+        <v>-0.6077</v>
       </c>
       <c r="J248" t="n">
-        <v>-17.3988</v>
+        <v>-16.4079</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-1.0276</v>
+        <v>-1.0257</v>
       </c>
       <c r="J249" t="n">
-        <v>-27.7452</v>
+        <v>-27.6939</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>1.28</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7869</v>
+        <v>0.7628</v>
       </c>
       <c r="J250" t="n">
-        <v>21.2463</v>
+        <v>20.5956</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>1.27</v>
       </c>
       <c r="I251" t="n">
-        <v>0.7648</v>
+        <v>0.7387</v>
       </c>
       <c r="J251" t="n">
-        <v>20.6496</v>
+        <v>19.9449</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.2</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4471</v>
+        <v>0.3899</v>
       </c>
       <c r="J252" t="n">
-        <v>12.0717</v>
+        <v>10.5273</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0061</v>
+        <v>0.0035</v>
       </c>
       <c r="J253" t="n">
-        <v>0.1647</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.91</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1312</v>
+        <v>-0.113</v>
       </c>
       <c r="J254" t="n">
-        <v>-3.5424</v>
+        <v>-3.051</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.84</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2071</v>
+        <v>-0.1868</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.5917</v>
+        <v>-5.0436</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.79</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2574</v>
+        <v>-0.2377</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.9498</v>
+        <v>-6.4179</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.26</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6957</v>
+        <v>0.6621</v>
       </c>
       <c r="J257" t="n">
-        <v>18.7839</v>
+        <v>17.8767</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.24</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6525</v>
+        <v>0.6167</v>
       </c>
       <c r="J258" t="n">
-        <v>17.6175</v>
+        <v>16.6509</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.12</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3759</v>
+        <v>0.3364</v>
       </c>
       <c r="J259" t="n">
-        <v>10.1493</v>
+        <v>9.082800000000001</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.92</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3044</v>
+        <v>-0.2631</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.2188</v>
+        <v>-7.1037</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.89</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3854</v>
+        <v>-0.3425</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.4058</v>
+        <v>-9.2475</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.71</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8598</v>
+        <v>0.7956</v>
       </c>
       <c r="J262" t="n">
-        <v>21.495</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>0.99</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0315</v>
+        <v>-0.0226</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.7875</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>0.95</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0931</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.3275</v>
+        <v>-1.9075</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1062</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.655</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2091</v>
+        <v>-0.1887</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.2275</v>
+        <v>-4.7175</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3685</v>
+        <v>0.3623</v>
       </c>
       <c r="J267" t="n">
-        <v>9.2125</v>
+        <v>9.057499999999999</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3285</v>
+        <v>0.3186</v>
       </c>
       <c r="J268" t="n">
-        <v>8.2125</v>
+        <v>7.965</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.042</v>
+        <v>-0.0321</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.05</v>
+        <v>-0.8025</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0574</v>
+        <v>-0.0452</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.435</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4537</v>
+        <v>-0.4492</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.3425</v>
+        <v>-11.23</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>0.98</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0362</v>
+        <v>-0.0283</v>
       </c>
       <c r="J272" t="n">
-        <v>-1.4842</v>
+        <v>-1.1603</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>0.97</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.052</v>
+        <v>-0.0419</v>
       </c>
       <c r="J273" t="n">
-        <v>-2.132</v>
+        <v>-1.7179</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>0.91</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1288</v>
+        <v>-0.1116</v>
       </c>
       <c r="J274" t="n">
-        <v>-5.2808</v>
+        <v>-4.5756</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1508</v>
+        <v>-0.1325</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.1828</v>
+        <v>-5.4325</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.8</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2439</v>
+        <v>-0.2241</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.9999</v>
+        <v>-9.1881</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.56</v>
       </c>
       <c r="I277" t="n">
-        <v>1.204</v>
+        <v>1.2207</v>
       </c>
       <c r="J277" t="n">
-        <v>49.364</v>
+        <v>50.0487</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>1.17</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4875</v>
+        <v>0.4491</v>
       </c>
       <c r="J278" t="n">
-        <v>19.9875</v>
+        <v>18.4131</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>1.06</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2114</v>
+        <v>0.1816</v>
       </c>
       <c r="J279" t="n">
-        <v>8.667400000000001</v>
+        <v>7.4456</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0808</v>
+        <v>-0.0601</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.3128</v>
+        <v>-2.4641</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.87</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4451</v>
+        <v>-0.403</v>
       </c>
       <c r="J281" t="n">
-        <v>-18.2491</v>
+        <v>-16.523</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3828</v>
+        <v>0.3795</v>
       </c>
       <c r="J282" t="n">
-        <v>9.9528</v>
+        <v>9.867000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.92</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.118</v>
+        <v>-0.1013</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.068</v>
+        <v>-2.6338</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.87</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1735</v>
+        <v>-0.154</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.511</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2049</v>
+        <v>-0.1849</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.3274</v>
+        <v>-4.8074</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2746</v>
+        <v>-0.2555</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.1396</v>
+        <v>-6.643</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.47</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5999</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J287" t="n">
-        <v>15.5974</v>
+        <v>13.7462</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.4</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5262</v>
+        <v>0.4569</v>
       </c>
       <c r="J288" t="n">
-        <v>13.6812</v>
+        <v>11.8794</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1732</v>
+        <v>0.136</v>
       </c>
       <c r="J289" t="n">
-        <v>4.5032</v>
+        <v>3.536</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0993</v>
+        <v>-0.0824</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.5818</v>
+        <v>-2.1424</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1491</v>
+        <v>-0.1297</v>
       </c>
       <c r="J291" t="n">
-        <v>-3.8766</v>
+        <v>-3.3722</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9893</v>
+        <v>0.9878</v>
       </c>
       <c r="J292" t="n">
-        <v>35.6148</v>
+        <v>35.5608</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.09</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3138</v>
+        <v>0.2729</v>
       </c>
       <c r="J293" t="n">
-        <v>11.2968</v>
+        <v>9.824400000000001</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.91</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3163</v>
+        <v>-0.2751</v>
       </c>
       <c r="J294" t="n">
-        <v>-11.3868</v>
+        <v>-9.903600000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.87</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4206</v>
+        <v>-0.3776</v>
       </c>
       <c r="J295" t="n">
-        <v>-15.1416</v>
+        <v>-13.5936</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.77</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.657</v>
+        <v>-0.6212</v>
       </c>
       <c r="J296" t="n">
-        <v>-23.652</v>
+        <v>-22.3632</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.52</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8858</v>
+        <v>0.8347</v>
       </c>
       <c r="J297" t="n">
-        <v>31.8888</v>
+        <v>30.0492</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.21</v>
       </c>
       <c r="I298" t="n">
-        <v>0.426</v>
+        <v>0.3706</v>
       </c>
       <c r="J298" t="n">
-        <v>15.336</v>
+        <v>13.3416</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.14</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3087</v>
+        <v>0.261</v>
       </c>
       <c r="J299" t="n">
-        <v>11.1132</v>
+        <v>9.396000000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0091</v>
+        <v>-0.0068</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.3276</v>
+        <v>-0.2448</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.283</v>
+        <v>-0.2653</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.188</v>
+        <v>-9.550800000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.88</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5293</v>
+        <v>1.5629</v>
       </c>
       <c r="J302" t="n">
-        <v>30.586</v>
+        <v>31.258</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.71</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3249</v>
+        <v>1.3472</v>
       </c>
       <c r="J303" t="n">
-        <v>26.498</v>
+        <v>26.944</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.37</v>
       </c>
       <c r="I304" t="n">
-        <v>0.851</v>
+        <v>0.843</v>
       </c>
       <c r="J304" t="n">
-        <v>17.02</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>1.32</v>
       </c>
       <c r="I305" t="n">
-        <v>0.7544</v>
+        <v>0.7396</v>
       </c>
       <c r="J305" t="n">
-        <v>15.088</v>
+        <v>14.792</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>1.18</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4592</v>
+        <v>0.4287</v>
       </c>
       <c r="J306" t="n">
-        <v>9.183999999999999</v>
+        <v>8.574</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>0.99</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1142</v>
+        <v>0.151</v>
       </c>
       <c r="J307" t="n">
-        <v>2.284</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>0.64</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.355</v>
+        <v>-0.3468</v>
       </c>
       <c r="J308" t="n">
-        <v>-7.1</v>
+        <v>-6.936</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>0.48</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4937</v>
+        <v>-0.4916</v>
       </c>
       <c r="J309" t="n">
-        <v>-9.874000000000001</v>
+        <v>-9.832000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>0.47</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.5012</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.05</v>
+        <v>-10.024</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.29</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6622</v>
+        <v>-0.6842</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.244</v>
+        <v>-13.684</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.62</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7453</v>
+        <v>0.6738</v>
       </c>
       <c r="J312" t="n">
-        <v>19.3778</v>
+        <v>17.5188</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.22</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3223</v>
+        <v>0.2674</v>
       </c>
       <c r="J313" t="n">
-        <v>8.379799999999999</v>
+        <v>6.9524</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2754</v>
+        <v>0.2256</v>
       </c>
       <c r="J314" t="n">
-        <v>7.1604</v>
+        <v>5.8656</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>1.02</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0371</v>
+        <v>0.0248</v>
       </c>
       <c r="J315" t="n">
-        <v>0.9646</v>
+        <v>0.6448</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0882</v>
+        <v>-0.0726</v>
       </c>
       <c r="J316" t="n">
-        <v>-2.2932</v>
+        <v>-1.8876</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.15</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2818</v>
+        <v>0.2687</v>
       </c>
       <c r="J317" t="n">
-        <v>7.3268</v>
+        <v>6.9862</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0056</v>
+        <v>0.0037</v>
       </c>
       <c r="J318" t="n">
-        <v>0.1456</v>
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.0966</v>
+        <v>-2.6468</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.86</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1857</v>
+        <v>-0.1656</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.8282</v>
+        <v>-4.3056</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.78</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2666</v>
+        <v>-0.2472</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.9316</v>
+        <v>-6.4272</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.1</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3041</v>
+        <v>0.2587</v>
       </c>
       <c r="J322" t="n">
-        <v>7.2984</v>
+        <v>6.2088</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>0.92</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1067</v>
+        <v>-0.0925</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.5608</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>0.84</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.196</v>
+        <v>-0.1789</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.704</v>
+        <v>-4.2936</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>0.68</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.347</v>
+        <v>-0.3318</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.327999999999999</v>
+        <v>-7.9632</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>0.51</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.498</v>
+        <v>-0.4969</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.952</v>
+        <v>-11.9256</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.43</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9953</v>
+        <v>0.9919</v>
       </c>
       <c r="J327" t="n">
-        <v>23.8872</v>
+        <v>23.8056</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.37</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8863</v>
+        <v>0.8689</v>
       </c>
       <c r="J328" t="n">
-        <v>21.2712</v>
+        <v>20.8536</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>1.35</v>
       </c>
       <c r="I329" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J329" t="n">
-        <v>20.3352</v>
+        <v>19.8504</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>1.16</v>
       </c>
       <c r="I330" t="n">
-        <v>0.4531</v>
+        <v>0.4195</v>
       </c>
       <c r="J330" t="n">
-        <v>10.8744</v>
+        <v>10.068</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.82</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5833</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.9992</v>
+        <v>-13.1496</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.02</v>
       </c>
       <c r="I332" t="n">
-        <v>0.0985</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J332" t="n">
-        <v>2.364</v>
+        <v>1.7496</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.1137</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J333" t="n">
-        <v>-2.7288</v>
+        <v>-2.3664</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>0.84</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1999</v>
+        <v>-0.181</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.7976</v>
+        <v>-4.344</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>0.82</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2199</v>
+        <v>-0.2007</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.2776</v>
+        <v>-4.8168</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>0.73</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3068</v>
+        <v>-0.2892</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.3632</v>
+        <v>-6.9408</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.51</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1158</v>
+        <v>1.1278</v>
       </c>
       <c r="J337" t="n">
-        <v>26.7792</v>
+        <v>27.0672</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>1.36</v>
       </c>
       <c r="I338" t="n">
-        <v>0.8703</v>
+        <v>0.8511</v>
       </c>
       <c r="J338" t="n">
-        <v>20.8872</v>
+        <v>20.4264</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>1.31</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7712</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="J339" t="n">
-        <v>18.5088</v>
+        <v>17.892</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>1.06</v>
       </c>
       <c r="I340" t="n">
-        <v>0.198</v>
+        <v>0.17</v>
       </c>
       <c r="J340" t="n">
-        <v>4.752</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.604</v>
+        <v>-0.5692</v>
       </c>
       <c r="J341" t="n">
-        <v>-14.496</v>
+        <v>-13.6608</v>
       </c>
     </row>
   </sheetData>
